--- a/data/sdb-1h-2026.xlsx
+++ b/data/sdb-1h-2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gccprod-my.sharepoint.com/personal/muhammad_ridzwan_md_ali_ica_gov_sg/Documents/Reports/2026/Half Yearly Reports/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mtalverniasg.sharepoint.com/sites/BASPTest/Shared Documents/02. Projects/20261007 Script for Private-Public Dataset/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8D708ED7-84ED-4B90-975C-47282A8D23B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{8D708ED7-84ED-4B90-975C-47282A8D23B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00B4AA99-8643-49FE-9094-EFCA105ECE6B}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="693" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" tabRatio="693" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TITLE" sheetId="66" r:id="rId1"/>
@@ -4392,202 +4392,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="41" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="7" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="7" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="7" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="55" xfId="7" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="7" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="56" xfId="7" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="3" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="9" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="46" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="43" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="44" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="29" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="59" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="8" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="7" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="9" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="3" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="45" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="27" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="13" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="63" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="95" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="96" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="75" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="82" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="116" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="117" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="120" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="114" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="115" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="121" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="128" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="85" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="92" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="128" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="57" xfId="7" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4598,16 +4412,202 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="54" xfId="7" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="55" xfId="7" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="7" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="7" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="56" xfId="7" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="7" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="7" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="7" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="9" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="3" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="45" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="27" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="13" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="9" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="63" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="59" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="8" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="3" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="46" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="43" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="44" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="29" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="75" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="82" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="95" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="96" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="116" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="117" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="120" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="114" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="115" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="121" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="128" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="85" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="57" xfId="7" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="92" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="128" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -5620,9 +5620,9 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9.296875" defaultRowHeight="13" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="9.296875" style="8"/>
+    <col min="1" max="16384" width="9.33203125" style="8"/>
   </cols>
   <sheetData/>
   <sheetProtection algorithmName="SHA-512" hashValue="QlCKGrx57nkYwPx0eDaq3pNN7GQBebSmJG1SF3iBnD9+FbwfRvS/bdH9Avc3obRTEblfOpx3GmPuVLWfQ9kQSg==" saltValue="DS8L3gwns9DhQRUyMR+NlQ==" spinCount="100000" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
@@ -5639,19 +5639,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:N89"/>
-  <sheetFormatPr defaultColWidth="6.796875" defaultRowHeight="13" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="6.83203125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="1.796875" style="26" customWidth="1"/>
-    <col min="2" max="2" width="33.296875" style="26" customWidth="1"/>
+    <col min="1" max="1" width="1.83203125" style="26" customWidth="1"/>
+    <col min="2" max="2" width="33.33203125" style="26" customWidth="1"/>
     <col min="3" max="3" width="10" style="26" customWidth="1"/>
-    <col min="4" max="4" width="14.296875" style="26" customWidth="1"/>
-    <col min="5" max="7" width="11.296875" style="26" customWidth="1"/>
-    <col min="8" max="8" width="12.69921875" style="26" customWidth="1"/>
-    <col min="9" max="14" width="11.296875" style="26" customWidth="1"/>
-    <col min="15" max="16384" width="6.796875" style="26"/>
+    <col min="4" max="4" width="14.33203125" style="26" customWidth="1"/>
+    <col min="5" max="7" width="11.33203125" style="26" customWidth="1"/>
+    <col min="8" max="8" width="12.6640625" style="26" customWidth="1"/>
+    <col min="9" max="14" width="11.33203125" style="26" customWidth="1"/>
+    <col min="15" max="16384" width="6.83203125" style="26"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="35.15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="35.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="114" t="s">
         <v>92</v>
       </c>
@@ -5669,7 +5669,7 @@
       <c r="M1" s="111"/>
       <c r="N1" s="111"/>
     </row>
-    <row r="2" spans="1:14" ht="9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="111"/>
       <c r="B2" s="111"/>
       <c r="C2" s="111"/>
@@ -5685,12 +5685,12 @@
       <c r="M2" s="111"/>
       <c r="N2" s="111"/>
     </row>
-    <row r="3" spans="1:14" s="67" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" s="67" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="26"/>
-      <c r="B3" s="392" t="s">
+      <c r="B3" s="399" t="s">
         <v>93</v>
       </c>
-      <c r="C3" s="392" t="s">
+      <c r="C3" s="399" t="s">
         <v>36</v>
       </c>
       <c r="D3" s="115" t="s">
@@ -5707,31 +5707,31 @@
       <c r="M3" s="116"/>
       <c r="N3" s="288"/>
     </row>
-    <row r="4" spans="1:14" s="67" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" s="67" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="26"/>
-      <c r="B4" s="393"/>
-      <c r="C4" s="393"/>
-      <c r="D4" s="392" t="s">
+      <c r="B4" s="400"/>
+      <c r="C4" s="400"/>
+      <c r="D4" s="399" t="s">
         <v>95</v>
       </c>
-      <c r="E4" s="395" t="s">
+      <c r="E4" s="402" t="s">
         <v>96</v>
       </c>
-      <c r="F4" s="396"/>
-      <c r="G4" s="396"/>
-      <c r="H4" s="396"/>
-      <c r="I4" s="396"/>
-      <c r="J4" s="396"/>
-      <c r="K4" s="396"/>
-      <c r="L4" s="396"/>
-      <c r="M4" s="396"/>
-      <c r="N4" s="397"/>
-    </row>
-    <row r="5" spans="1:14" s="67" customFormat="1" ht="70" x14ac:dyDescent="0.3">
+      <c r="F4" s="403"/>
+      <c r="G4" s="403"/>
+      <c r="H4" s="403"/>
+      <c r="I4" s="403"/>
+      <c r="J4" s="403"/>
+      <c r="K4" s="403"/>
+      <c r="L4" s="403"/>
+      <c r="M4" s="403"/>
+      <c r="N4" s="404"/>
+    </row>
+    <row r="5" spans="1:14" s="67" customFormat="1" ht="90" x14ac:dyDescent="0.2">
       <c r="A5" s="26"/>
-      <c r="B5" s="394"/>
-      <c r="C5" s="394"/>
-      <c r="D5" s="394"/>
+      <c r="B5" s="401"/>
+      <c r="C5" s="401"/>
+      <c r="D5" s="401"/>
       <c r="E5" s="171" t="s">
         <v>97</v>
       </c>
@@ -5763,24 +5763,24 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="117"/>
-      <c r="C6" s="391" t="s">
+      <c r="C6" s="405" t="s">
         <v>70</v>
       </c>
-      <c r="D6" s="391"/>
-      <c r="E6" s="391"/>
-      <c r="F6" s="391"/>
-      <c r="G6" s="391"/>
-      <c r="H6" s="391"/>
-      <c r="I6" s="391"/>
-      <c r="J6" s="391"/>
-      <c r="K6" s="391"/>
-      <c r="L6" s="391"/>
-      <c r="M6" s="391"/>
-      <c r="N6" s="391"/>
-    </row>
-    <row r="7" spans="1:14" s="112" customFormat="1" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D6" s="405"/>
+      <c r="E6" s="405"/>
+      <c r="F6" s="405"/>
+      <c r="G6" s="405"/>
+      <c r="H6" s="405"/>
+      <c r="I6" s="405"/>
+      <c r="J6" s="405"/>
+      <c r="K6" s="405"/>
+      <c r="L6" s="405"/>
+      <c r="M6" s="405"/>
+      <c r="N6" s="405"/>
+    </row>
+    <row r="7" spans="1:14" s="112" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="26"/>
       <c r="B7" s="118" t="s">
         <v>36</v>
@@ -5822,7 +5822,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="8" spans="1:14" s="67" customFormat="1" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" s="67" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="26"/>
       <c r="B8" s="118" t="s">
         <v>95</v>
@@ -5864,7 +5864,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:14" s="67" customFormat="1" ht="28" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" s="67" customFormat="1" ht="29.25" x14ac:dyDescent="0.25">
       <c r="A9" s="26"/>
       <c r="B9" s="297" t="s">
         <v>96</v>
@@ -5882,7 +5882,7 @@
       <c r="M9" s="293"/>
       <c r="N9" s="293"/>
     </row>
-    <row r="10" spans="1:14" s="67" customFormat="1" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" s="67" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="26"/>
       <c r="B10" s="120" t="s">
         <v>97</v>
@@ -5924,7 +5924,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="11" spans="1:14" s="67" customFormat="1" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" s="67" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="26"/>
       <c r="B11" s="120" t="s">
         <v>98</v>
@@ -5966,7 +5966,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="12" spans="1:14" s="67" customFormat="1" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" s="67" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="120" t="s">
         <v>106</v>
       </c>
@@ -6007,7 +6007,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:14" s="113" customFormat="1" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" s="113" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="286" t="s">
         <v>107</v>
       </c>
@@ -6048,7 +6048,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:14" s="67" customFormat="1" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" s="67" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="120" t="s">
         <v>108</v>
       </c>
@@ -6089,7 +6089,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:14" s="67" customFormat="1" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" s="67" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="120" t="s">
         <v>102</v>
       </c>
@@ -6130,7 +6130,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="16" spans="1:14" s="67" customFormat="1" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" s="67" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="120" t="s">
         <v>103</v>
       </c>
@@ -6171,7 +6171,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:14" s="41" customFormat="1" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:14" s="41" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="120" t="s">
         <v>104</v>
       </c>
@@ -6212,7 +6212,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="18" spans="1:14" s="41" customFormat="1" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14" s="41" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="120" t="s">
         <v>105</v>
       </c>
@@ -6253,7 +6253,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:14" s="41" customFormat="1" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" s="41" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="120" t="s">
         <v>35</v>
       </c>
@@ -6294,24 +6294,24 @@
         <v>44</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B20" s="117"/>
-      <c r="C20" s="391" t="s">
+      <c r="C20" s="405" t="s">
         <v>75</v>
       </c>
-      <c r="D20" s="391"/>
-      <c r="E20" s="391"/>
-      <c r="F20" s="391"/>
-      <c r="G20" s="391"/>
-      <c r="H20" s="391"/>
-      <c r="I20" s="391"/>
-      <c r="J20" s="391"/>
-      <c r="K20" s="391"/>
-      <c r="L20" s="391"/>
-      <c r="M20" s="391"/>
-      <c r="N20" s="391"/>
-    </row>
-    <row r="21" spans="1:14" s="112" customFormat="1" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D20" s="405"/>
+      <c r="E20" s="405"/>
+      <c r="F20" s="405"/>
+      <c r="G20" s="405"/>
+      <c r="H20" s="405"/>
+      <c r="I20" s="405"/>
+      <c r="J20" s="405"/>
+      <c r="K20" s="405"/>
+      <c r="L20" s="405"/>
+      <c r="M20" s="405"/>
+      <c r="N20" s="405"/>
+    </row>
+    <row r="21" spans="1:14" s="112" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="26"/>
       <c r="B21" s="118" t="s">
         <v>36</v>
@@ -6353,7 +6353,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="22" spans="1:14" s="67" customFormat="1" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14" s="67" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="26"/>
       <c r="B22" s="118" t="s">
         <v>95</v>
@@ -6395,7 +6395,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:14" s="67" customFormat="1" ht="28" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:14" s="67" customFormat="1" ht="29.25" x14ac:dyDescent="0.25">
       <c r="A23" s="26"/>
       <c r="B23" s="119" t="s">
         <v>96</v>
@@ -6413,7 +6413,7 @@
       <c r="M23" s="293"/>
       <c r="N23" s="293"/>
     </row>
-    <row r="24" spans="1:14" s="67" customFormat="1" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:14" s="67" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="26"/>
       <c r="B24" s="120" t="s">
         <v>97</v>
@@ -6455,7 +6455,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:14" s="67" customFormat="1" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:14" s="67" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="26"/>
       <c r="B25" s="120" t="s">
         <v>98</v>
@@ -6497,7 +6497,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="26" spans="1:14" s="67" customFormat="1" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:14" s="67" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="120" t="s">
         <v>106</v>
       </c>
@@ -6538,7 +6538,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="27" spans="1:14" s="113" customFormat="1" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:14" s="113" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="286" t="s">
         <v>107</v>
       </c>
@@ -6579,7 +6579,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:14" s="67" customFormat="1" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:14" s="67" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="120" t="s">
         <v>108</v>
       </c>
@@ -6620,7 +6620,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:14" s="67" customFormat="1" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:14" s="67" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="120" t="s">
         <v>102</v>
       </c>
@@ -6661,7 +6661,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="30" spans="1:14" s="67" customFormat="1" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:14" s="67" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="120" t="s">
         <v>103</v>
       </c>
@@ -6702,7 +6702,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:14" s="41" customFormat="1" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:14" s="41" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="120" t="s">
         <v>104</v>
       </c>
@@ -6743,7 +6743,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:14" s="41" customFormat="1" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:14" s="41" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="120" t="s">
         <v>105</v>
       </c>
@@ -6784,7 +6784,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="1:14" s="41" customFormat="1" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:14" s="41" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="120" t="s">
         <v>35</v>
       </c>
@@ -6825,24 +6825,24 @@
         <v>53</v>
       </c>
     </row>
-    <row r="34" spans="1:14" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B34" s="117"/>
-      <c r="C34" s="391" t="s">
+      <c r="C34" s="405" t="s">
         <v>76</v>
       </c>
-      <c r="D34" s="391"/>
-      <c r="E34" s="391"/>
-      <c r="F34" s="391"/>
-      <c r="G34" s="391"/>
-      <c r="H34" s="391"/>
-      <c r="I34" s="391"/>
-      <c r="J34" s="391"/>
-      <c r="K34" s="391"/>
-      <c r="L34" s="391"/>
-      <c r="M34" s="391"/>
-      <c r="N34" s="391"/>
-    </row>
-    <row r="35" spans="1:14" s="112" customFormat="1" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D34" s="405"/>
+      <c r="E34" s="405"/>
+      <c r="F34" s="405"/>
+      <c r="G34" s="405"/>
+      <c r="H34" s="405"/>
+      <c r="I34" s="405"/>
+      <c r="J34" s="405"/>
+      <c r="K34" s="405"/>
+      <c r="L34" s="405"/>
+      <c r="M34" s="405"/>
+      <c r="N34" s="405"/>
+    </row>
+    <row r="35" spans="1:14" s="112" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="26"/>
       <c r="B35" s="118" t="s">
         <v>36</v>
@@ -6884,7 +6884,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="36" spans="1:14" s="67" customFormat="1" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:14" s="67" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="26"/>
       <c r="B36" s="118" t="s">
         <v>95</v>
@@ -6926,7 +6926,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="37" spans="1:14" s="67" customFormat="1" ht="28" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:14" s="67" customFormat="1" ht="29.25" x14ac:dyDescent="0.25">
       <c r="A37" s="26"/>
       <c r="B37" s="119" t="s">
         <v>96</v>
@@ -6944,7 +6944,7 @@
       <c r="M37" s="293"/>
       <c r="N37" s="293"/>
     </row>
-    <row r="38" spans="1:14" s="67" customFormat="1" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:14" s="67" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="26"/>
       <c r="B38" s="120" t="s">
         <v>97</v>
@@ -6986,7 +6986,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="39" spans="1:14" s="67" customFormat="1" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:14" s="67" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="26"/>
       <c r="B39" s="120" t="s">
         <v>98</v>
@@ -7028,7 +7028,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="40" spans="1:14" s="67" customFormat="1" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:14" s="67" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="120" t="s">
         <v>106</v>
       </c>
@@ -7069,7 +7069,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="41" spans="1:14" s="113" customFormat="1" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:14" s="113" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="286" t="s">
         <v>107</v>
       </c>
@@ -7110,7 +7110,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="1:14" s="67" customFormat="1" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:14" s="67" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="120" t="s">
         <v>108</v>
       </c>
@@ -7151,7 +7151,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="1:14" s="67" customFormat="1" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:14" s="67" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="120" t="s">
         <v>102</v>
       </c>
@@ -7192,7 +7192,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:14" s="67" customFormat="1" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:14" s="67" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="120" t="s">
         <v>103</v>
       </c>
@@ -7233,7 +7233,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:14" s="41" customFormat="1" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:14" s="41" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="120" t="s">
         <v>104</v>
       </c>
@@ -7274,7 +7274,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="46" spans="1:14" s="41" customFormat="1" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:14" s="41" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B46" s="120" t="s">
         <v>105</v>
       </c>
@@ -7315,7 +7315,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:14" s="41" customFormat="1" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:14" s="41" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B47" s="120" t="s">
         <v>35</v>
       </c>
@@ -7356,24 +7356,24 @@
         <v>56</v>
       </c>
     </row>
-    <row r="48" spans="1:14" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B48" s="117"/>
-      <c r="C48" s="391" t="s">
+      <c r="C48" s="405" t="s">
         <v>77</v>
       </c>
-      <c r="D48" s="391"/>
-      <c r="E48" s="391"/>
-      <c r="F48" s="391"/>
-      <c r="G48" s="391"/>
-      <c r="H48" s="391"/>
-      <c r="I48" s="391"/>
-      <c r="J48" s="391"/>
-      <c r="K48" s="391"/>
-      <c r="L48" s="391"/>
-      <c r="M48" s="391"/>
-      <c r="N48" s="391"/>
-    </row>
-    <row r="49" spans="1:14" s="112" customFormat="1" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D48" s="405"/>
+      <c r="E48" s="405"/>
+      <c r="F48" s="405"/>
+      <c r="G48" s="405"/>
+      <c r="H48" s="405"/>
+      <c r="I48" s="405"/>
+      <c r="J48" s="405"/>
+      <c r="K48" s="405"/>
+      <c r="L48" s="405"/>
+      <c r="M48" s="405"/>
+      <c r="N48" s="405"/>
+    </row>
+    <row r="49" spans="1:14" s="112" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="26"/>
       <c r="B49" s="118" t="s">
         <v>36</v>
@@ -7415,7 +7415,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="50" spans="1:14" s="67" customFormat="1" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:14" s="67" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="26"/>
       <c r="B50" s="118" t="s">
         <v>95</v>
@@ -7457,7 +7457,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="51" spans="1:14" s="67" customFormat="1" ht="28" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:14" s="67" customFormat="1" ht="29.25" x14ac:dyDescent="0.25">
       <c r="A51" s="26"/>
       <c r="B51" s="119" t="s">
         <v>96</v>
@@ -7475,7 +7475,7 @@
       <c r="M51" s="293"/>
       <c r="N51" s="293"/>
     </row>
-    <row r="52" spans="1:14" s="67" customFormat="1" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:14" s="67" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="26"/>
       <c r="B52" s="120" t="s">
         <v>97</v>
@@ -7517,7 +7517,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="53" spans="1:14" s="67" customFormat="1" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:14" s="67" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="26"/>
       <c r="B53" s="120" t="s">
         <v>98</v>
@@ -7559,7 +7559,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="54" spans="1:14" s="67" customFormat="1" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:14" s="67" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B54" s="120" t="s">
         <v>106</v>
       </c>
@@ -7600,7 +7600,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:14" s="113" customFormat="1" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:14" s="113" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B55" s="286" t="s">
         <v>107</v>
       </c>
@@ -7641,7 +7641,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="56" spans="1:14" s="67" customFormat="1" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:14" s="67" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B56" s="120" t="s">
         <v>108</v>
       </c>
@@ -7682,7 +7682,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="1:14" s="67" customFormat="1" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:14" s="67" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B57" s="120" t="s">
         <v>102</v>
       </c>
@@ -7723,7 +7723,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:14" s="67" customFormat="1" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:14" s="67" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B58" s="120" t="s">
         <v>103</v>
       </c>
@@ -7764,7 +7764,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:14" s="41" customFormat="1" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:14" s="41" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B59" s="120" t="s">
         <v>104</v>
       </c>
@@ -7805,7 +7805,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="60" spans="1:14" s="41" customFormat="1" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:14" s="41" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B60" s="120" t="s">
         <v>105</v>
       </c>
@@ -7846,7 +7846,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:14" s="41" customFormat="1" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:14" s="41" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B61" s="120" t="s">
         <v>35</v>
       </c>
@@ -7887,24 +7887,24 @@
         <v>41</v>
       </c>
     </row>
-    <row r="62" spans="1:14" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B62" s="117"/>
-      <c r="C62" s="391" t="s">
+      <c r="C62" s="405" t="s">
         <v>57</v>
       </c>
-      <c r="D62" s="391"/>
-      <c r="E62" s="391"/>
-      <c r="F62" s="391"/>
-      <c r="G62" s="391"/>
-      <c r="H62" s="391"/>
-      <c r="I62" s="391"/>
-      <c r="J62" s="391"/>
-      <c r="K62" s="391"/>
-      <c r="L62" s="391"/>
-      <c r="M62" s="391"/>
-      <c r="N62" s="391"/>
-    </row>
-    <row r="63" spans="1:14" s="112" customFormat="1" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D62" s="405"/>
+      <c r="E62" s="405"/>
+      <c r="F62" s="405"/>
+      <c r="G62" s="405"/>
+      <c r="H62" s="405"/>
+      <c r="I62" s="405"/>
+      <c r="J62" s="405"/>
+      <c r="K62" s="405"/>
+      <c r="L62" s="405"/>
+      <c r="M62" s="405"/>
+      <c r="N62" s="405"/>
+    </row>
+    <row r="63" spans="1:14" s="112" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="26"/>
       <c r="B63" s="118" t="s">
         <v>36</v>
@@ -7946,7 +7946,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="64" spans="1:14" s="67" customFormat="1" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:14" s="67" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="26"/>
       <c r="B64" s="118" t="s">
         <v>95</v>
@@ -7988,7 +7988,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="65" spans="1:14" s="67" customFormat="1" ht="28" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:14" s="67" customFormat="1" ht="29.25" x14ac:dyDescent="0.25">
       <c r="A65" s="26"/>
       <c r="B65" s="119" t="s">
         <v>96</v>
@@ -8006,7 +8006,7 @@
       <c r="M65" s="293"/>
       <c r="N65" s="293"/>
     </row>
-    <row r="66" spans="1:14" s="67" customFormat="1" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:14" s="67" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="26"/>
       <c r="B66" s="120" t="s">
         <v>97</v>
@@ -8048,7 +8048,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="67" spans="1:14" s="67" customFormat="1" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:14" s="67" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="26"/>
       <c r="B67" s="120" t="s">
         <v>98</v>
@@ -8090,7 +8090,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:14" s="67" customFormat="1" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:14" s="67" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="120" t="s">
         <v>106</v>
       </c>
@@ -8131,7 +8131,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="69" spans="1:14" s="113" customFormat="1" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:14" s="113" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B69" s="286" t="s">
         <v>107</v>
       </c>
@@ -8172,7 +8172,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="70" spans="1:14" s="67" customFormat="1" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:14" s="67" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B70" s="120" t="s">
         <v>108</v>
       </c>
@@ -8213,7 +8213,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="71" spans="1:14" s="67" customFormat="1" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:14" s="67" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B71" s="120" t="s">
         <v>102</v>
       </c>
@@ -8254,7 +8254,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="72" spans="1:14" s="67" customFormat="1" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:14" s="67" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B72" s="120" t="s">
         <v>103</v>
       </c>
@@ -8295,7 +8295,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="73" spans="1:14" s="41" customFormat="1" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:14" s="41" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B73" s="120" t="s">
         <v>104</v>
       </c>
@@ -8336,7 +8336,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="74" spans="1:14" s="41" customFormat="1" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:14" s="41" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B74" s="120" t="s">
         <v>105</v>
       </c>
@@ -8377,7 +8377,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="75" spans="1:14" s="41" customFormat="1" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:14" s="41" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B75" s="120" t="s">
         <v>35</v>
       </c>
@@ -8418,24 +8418,24 @@
         <v>52</v>
       </c>
     </row>
-    <row r="76" spans="1:14" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B76" s="117"/>
-      <c r="C76" s="391" t="s">
+      <c r="C76" s="405" t="s">
         <v>78</v>
       </c>
-      <c r="D76" s="391"/>
-      <c r="E76" s="391"/>
-      <c r="F76" s="391"/>
-      <c r="G76" s="391"/>
-      <c r="H76" s="391"/>
-      <c r="I76" s="391"/>
-      <c r="J76" s="391"/>
-      <c r="K76" s="391"/>
-      <c r="L76" s="391"/>
-      <c r="M76" s="391"/>
-      <c r="N76" s="391"/>
-    </row>
-    <row r="77" spans="1:14" s="112" customFormat="1" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D76" s="405"/>
+      <c r="E76" s="405"/>
+      <c r="F76" s="405"/>
+      <c r="G76" s="405"/>
+      <c r="H76" s="405"/>
+      <c r="I76" s="405"/>
+      <c r="J76" s="405"/>
+      <c r="K76" s="405"/>
+      <c r="L76" s="405"/>
+      <c r="M76" s="405"/>
+      <c r="N76" s="405"/>
+    </row>
+    <row r="77" spans="1:14" s="112" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="26"/>
       <c r="B77" s="118" t="s">
         <v>36</v>
@@ -8477,7 +8477,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="78" spans="1:14" s="67" customFormat="1" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:14" s="67" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="26"/>
       <c r="B78" s="118" t="s">
         <v>95</v>
@@ -8519,7 +8519,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="79" spans="1:14" s="67" customFormat="1" ht="28" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:14" s="67" customFormat="1" ht="29.25" x14ac:dyDescent="0.25">
       <c r="A79" s="26"/>
       <c r="B79" s="119" t="s">
         <v>96</v>
@@ -8537,7 +8537,7 @@
       <c r="M79" s="293"/>
       <c r="N79" s="293"/>
     </row>
-    <row r="80" spans="1:14" s="67" customFormat="1" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:14" s="67" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="26"/>
       <c r="B80" s="120" t="s">
         <v>97</v>
@@ -8579,7 +8579,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:14" s="67" customFormat="1" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:14" s="67" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="26"/>
       <c r="B81" s="120" t="s">
         <v>98</v>
@@ -8621,7 +8621,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="82" spans="1:14" s="67" customFormat="1" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:14" s="67" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B82" s="120" t="s">
         <v>106</v>
       </c>
@@ -8662,7 +8662,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:14" s="113" customFormat="1" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:14" s="113" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B83" s="286" t="s">
         <v>107</v>
       </c>
@@ -8703,7 +8703,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="84" spans="1:14" s="67" customFormat="1" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:14" s="67" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B84" s="120" t="s">
         <v>108</v>
       </c>
@@ -8744,7 +8744,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="85" spans="1:14" s="67" customFormat="1" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:14" s="67" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B85" s="120" t="s">
         <v>102</v>
       </c>
@@ -8785,7 +8785,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="86" spans="1:14" s="67" customFormat="1" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:14" s="67" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B86" s="120" t="s">
         <v>103</v>
       </c>
@@ -8826,7 +8826,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="87" spans="1:14" s="41" customFormat="1" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:14" s="41" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B87" s="120" t="s">
         <v>104</v>
       </c>
@@ -8867,7 +8867,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="88" spans="1:14" s="41" customFormat="1" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:14" s="41" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B88" s="120" t="s">
         <v>105</v>
       </c>
@@ -8908,7 +8908,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="89" spans="1:14" s="41" customFormat="1" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:14" s="41" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B89" s="287" t="s">
         <v>35</v>
       </c>
@@ -8952,16 +8952,16 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="Z6Prg6FVKXGQTe4kGg0rgGwYzTxvwxcBvQsUvSOJc8N0Li0+tfs5+Mpdl2deOz68PchKfAwNiBJKzGFrwgYTpg==" saltValue="8eoUe15CONBApn+A/hcHxw==" spinCount="100000" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <mergeCells count="10">
+    <mergeCell ref="C48:N48"/>
+    <mergeCell ref="C62:N62"/>
+    <mergeCell ref="C76:N76"/>
+    <mergeCell ref="C20:N20"/>
+    <mergeCell ref="C34:N34"/>
     <mergeCell ref="B3:B5"/>
     <mergeCell ref="E4:N4"/>
     <mergeCell ref="D4:D5"/>
     <mergeCell ref="C6:N6"/>
     <mergeCell ref="C3:C5"/>
-    <mergeCell ref="C48:N48"/>
-    <mergeCell ref="C62:N62"/>
-    <mergeCell ref="C76:N76"/>
-    <mergeCell ref="C20:N20"/>
-    <mergeCell ref="C34:N34"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -8974,17 +8974,17 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0992BC87-50C3-41A9-A775-7AA79DFEEC95}">
   <dimension ref="A1:N59"/>
-  <sheetFormatPr defaultColWidth="6.796875" defaultRowHeight="13" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="6.83203125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.296875" style="66" customWidth="1"/>
-    <col min="2" max="2" width="1.796875" style="66" customWidth="1"/>
-    <col min="3" max="3" width="32.796875" style="66" customWidth="1"/>
-    <col min="4" max="14" width="9.796875" style="66" customWidth="1"/>
-    <col min="15" max="15" width="4.796875" style="66" customWidth="1"/>
-    <col min="16" max="16384" width="6.796875" style="66"/>
+    <col min="1" max="1" width="2.33203125" style="66" customWidth="1"/>
+    <col min="2" max="2" width="1.83203125" style="66" customWidth="1"/>
+    <col min="3" max="3" width="32.83203125" style="66" customWidth="1"/>
+    <col min="4" max="14" width="9.83203125" style="66" customWidth="1"/>
+    <col min="15" max="15" width="4.83203125" style="66" customWidth="1"/>
+    <col min="16" max="16384" width="6.83203125" style="66"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" ht="33" x14ac:dyDescent="0.25">
       <c r="B1" s="74" t="s">
         <v>109</v>
       </c>
@@ -9001,7 +9001,7 @@
       <c r="M1" s="64"/>
       <c r="N1" s="64"/>
     </row>
-    <row r="2" spans="1:14" ht="13.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="121"/>
       <c r="B2" s="64"/>
       <c r="C2" s="64"/>
@@ -9019,11 +9019,11 @@
       </c>
       <c r="N2" s="64"/>
     </row>
-    <row r="3" spans="1:14" ht="13.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="401" t="s">
+    <row r="3" spans="1:14" ht="13.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="B3" s="409" t="s">
         <v>69</v>
       </c>
-      <c r="C3" s="380"/>
+      <c r="C3" s="392"/>
       <c r="D3" s="123" t="s">
         <v>50</v>
       </c>
@@ -9046,9 +9046,9 @@
       </c>
       <c r="N3" s="124"/>
     </row>
-    <row r="4" spans="1:14" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="402"/>
-      <c r="C4" s="402"/>
+    <row r="4" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="410"/>
+      <c r="C4" s="410"/>
       <c r="D4" s="54" t="s">
         <v>36</v>
       </c>
@@ -9083,24 +9083,24 @@
         <v>52</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="16.399999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" ht="16.350000000000001" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B5" s="79"/>
       <c r="C5" s="126"/>
-      <c r="D5" s="387" t="s">
+      <c r="D5" s="397" t="s">
         <v>70</v>
       </c>
-      <c r="E5" s="388"/>
-      <c r="F5" s="388"/>
-      <c r="G5" s="388"/>
-      <c r="H5" s="388"/>
-      <c r="I5" s="388"/>
-      <c r="J5" s="388"/>
-      <c r="K5" s="388"/>
-      <c r="L5" s="388"/>
-      <c r="M5" s="388"/>
-      <c r="N5" s="388"/>
-    </row>
-    <row r="6" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E5" s="398"/>
+      <c r="F5" s="398"/>
+      <c r="G5" s="398"/>
+      <c r="H5" s="398"/>
+      <c r="I5" s="398"/>
+      <c r="J5" s="398"/>
+      <c r="K5" s="398"/>
+      <c r="L5" s="398"/>
+      <c r="M5" s="398"/>
+      <c r="N5" s="398"/>
+    </row>
+    <row r="6" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="79" t="s">
         <v>71</v>
       </c>
@@ -9139,7 +9139,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="99" t="s">
         <v>72</v>
       </c>
@@ -9178,7 +9178,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="99" t="s">
         <v>110</v>
       </c>
@@ -9217,7 +9217,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="99" t="s">
         <v>452</v>
       </c>
@@ -9256,7 +9256,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="99" t="s">
         <v>453</v>
       </c>
@@ -9294,7 +9294,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="99" t="s">
         <v>73</v>
       </c>
@@ -9333,7 +9333,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="99" t="s">
         <v>74</v>
       </c>
@@ -9372,7 +9372,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="16.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:14" ht="16.350000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B13" s="127" t="s">
         <v>36</v>
       </c>
@@ -9411,24 +9411,24 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="16.399999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" ht="16.350000000000001" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B14" s="79"/>
       <c r="C14" s="126"/>
-      <c r="D14" s="398" t="s">
+      <c r="D14" s="406" t="s">
         <v>75</v>
       </c>
-      <c r="E14" s="399"/>
-      <c r="F14" s="399"/>
-      <c r="G14" s="399"/>
-      <c r="H14" s="399"/>
-      <c r="I14" s="399"/>
-      <c r="J14" s="399"/>
-      <c r="K14" s="399"/>
-      <c r="L14" s="399"/>
-      <c r="M14" s="399"/>
-      <c r="N14" s="400"/>
-    </row>
-    <row r="15" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E14" s="407"/>
+      <c r="F14" s="407"/>
+      <c r="G14" s="407"/>
+      <c r="H14" s="407"/>
+      <c r="I14" s="407"/>
+      <c r="J14" s="407"/>
+      <c r="K14" s="407"/>
+      <c r="L14" s="407"/>
+      <c r="M14" s="407"/>
+      <c r="N14" s="408"/>
+    </row>
+    <row r="15" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="79" t="s">
         <v>71</v>
       </c>
@@ -9467,7 +9467,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="99" t="s">
         <v>72</v>
       </c>
@@ -9506,7 +9506,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="99" t="s">
         <v>110</v>
       </c>
@@ -9545,7 +9545,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="18" spans="2:14" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="99" t="s">
         <v>452</v>
       </c>
@@ -9584,7 +9584,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="2:14" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="99" t="s">
         <v>453</v>
       </c>
@@ -9623,7 +9623,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="99" t="s">
         <v>73</v>
       </c>
@@ -9662,7 +9662,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="99" t="s">
         <v>74</v>
       </c>
@@ -9701,7 +9701,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="22" spans="2:14" ht="16.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:14" ht="16.350000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B22" s="127" t="s">
         <v>36</v>
       </c>
@@ -9740,24 +9740,24 @@
         <v>22</v>
       </c>
     </row>
-    <row r="23" spans="2:14" ht="16.399999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:14" ht="16.350000000000001" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B23" s="79"/>
       <c r="C23" s="126"/>
-      <c r="D23" s="398" t="s">
+      <c r="D23" s="406" t="s">
         <v>76</v>
       </c>
-      <c r="E23" s="399"/>
-      <c r="F23" s="399"/>
-      <c r="G23" s="399"/>
-      <c r="H23" s="399"/>
-      <c r="I23" s="399"/>
-      <c r="J23" s="399"/>
-      <c r="K23" s="399"/>
-      <c r="L23" s="399"/>
-      <c r="M23" s="399"/>
-      <c r="N23" s="400"/>
-    </row>
-    <row r="24" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E23" s="407"/>
+      <c r="F23" s="407"/>
+      <c r="G23" s="407"/>
+      <c r="H23" s="407"/>
+      <c r="I23" s="407"/>
+      <c r="J23" s="407"/>
+      <c r="K23" s="407"/>
+      <c r="L23" s="407"/>
+      <c r="M23" s="407"/>
+      <c r="N23" s="408"/>
+    </row>
+    <row r="24" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="79" t="s">
         <v>71</v>
       </c>
@@ -9796,7 +9796,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="25" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="99" t="s">
         <v>72</v>
       </c>
@@ -9835,7 +9835,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="99" t="s">
         <v>110</v>
       </c>
@@ -9874,7 +9874,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="27" spans="2:14" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="99" t="s">
         <v>452</v>
       </c>
@@ -9913,7 +9913,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="2:14" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="99" t="s">
         <v>453</v>
       </c>
@@ -9952,7 +9952,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="99" t="s">
         <v>73</v>
       </c>
@@ -9991,7 +9991,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="30" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="99" t="s">
         <v>74</v>
       </c>
@@ -10030,7 +10030,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="31" spans="2:14" ht="16.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:14" ht="16.350000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B31" s="127" t="s">
         <v>36</v>
       </c>
@@ -10069,24 +10069,24 @@
         <v>19</v>
       </c>
     </row>
-    <row r="32" spans="2:14" ht="16.399999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:14" ht="16.350000000000001" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B32" s="79"/>
       <c r="C32" s="126"/>
-      <c r="D32" s="403" t="s">
+      <c r="D32" s="411" t="s">
         <v>77</v>
       </c>
-      <c r="E32" s="404"/>
-      <c r="F32" s="404"/>
-      <c r="G32" s="404"/>
-      <c r="H32" s="404"/>
-      <c r="I32" s="404"/>
-      <c r="J32" s="404"/>
-      <c r="K32" s="404"/>
-      <c r="L32" s="404"/>
-      <c r="M32" s="404"/>
-      <c r="N32" s="405"/>
-    </row>
-    <row r="33" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E32" s="412"/>
+      <c r="F32" s="412"/>
+      <c r="G32" s="412"/>
+      <c r="H32" s="412"/>
+      <c r="I32" s="412"/>
+      <c r="J32" s="412"/>
+      <c r="K32" s="412"/>
+      <c r="L32" s="412"/>
+      <c r="M32" s="412"/>
+      <c r="N32" s="413"/>
+    </row>
+    <row r="33" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="79" t="s">
         <v>71</v>
       </c>
@@ -10125,7 +10125,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="34" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="99" t="s">
         <v>72</v>
       </c>
@@ -10164,7 +10164,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="99" t="s">
         <v>110</v>
       </c>
@@ -10203,7 +10203,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="2:14" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="99" t="s">
         <v>452</v>
       </c>
@@ -10242,7 +10242,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="37" spans="2:14" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="99" t="s">
         <v>453</v>
       </c>
@@ -10281,7 +10281,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="99" t="s">
         <v>73</v>
       </c>
@@ -10320,7 +10320,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="99" t="s">
         <v>74</v>
       </c>
@@ -10359,7 +10359,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="2:14" ht="16.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:14" ht="16.350000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B40" s="127" t="s">
         <v>36</v>
       </c>
@@ -10398,24 +10398,24 @@
         <v>23</v>
       </c>
     </row>
-    <row r="41" spans="2:14" ht="16.399999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:14" ht="16.350000000000001" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B41" s="79"/>
       <c r="C41" s="126"/>
-      <c r="D41" s="398" t="s">
+      <c r="D41" s="406" t="s">
         <v>57</v>
       </c>
-      <c r="E41" s="399"/>
-      <c r="F41" s="399"/>
-      <c r="G41" s="399"/>
-      <c r="H41" s="399"/>
-      <c r="I41" s="399"/>
-      <c r="J41" s="399"/>
-      <c r="K41" s="399"/>
-      <c r="L41" s="399"/>
-      <c r="M41" s="399"/>
-      <c r="N41" s="400"/>
-    </row>
-    <row r="42" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E41" s="407"/>
+      <c r="F41" s="407"/>
+      <c r="G41" s="407"/>
+      <c r="H41" s="407"/>
+      <c r="I41" s="407"/>
+      <c r="J41" s="407"/>
+      <c r="K41" s="407"/>
+      <c r="L41" s="407"/>
+      <c r="M41" s="407"/>
+      <c r="N41" s="408"/>
+    </row>
+    <row r="42" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="79" t="s">
         <v>71</v>
       </c>
@@ -10454,7 +10454,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="43" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="99" t="s">
         <v>72</v>
       </c>
@@ -10493,7 +10493,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="99" t="s">
         <v>110</v>
       </c>
@@ -10532,7 +10532,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="45" spans="2:14" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="99" t="s">
         <v>452</v>
       </c>
@@ -10571,7 +10571,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="2:14" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B46" s="99" t="s">
         <v>453</v>
       </c>
@@ -10610,7 +10610,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="47" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B47" s="99" t="s">
         <v>73</v>
       </c>
@@ -10649,7 +10649,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="48" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B48" s="99" t="s">
         <v>74</v>
       </c>
@@ -10688,7 +10688,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="49" spans="2:14" ht="16.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:14" ht="16.350000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B49" s="127" t="s">
         <v>36</v>
       </c>
@@ -10727,24 +10727,24 @@
         <v>24</v>
       </c>
     </row>
-    <row r="50" spans="2:14" ht="16.399999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:14" ht="16.350000000000001" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B50" s="79"/>
       <c r="C50" s="126"/>
-      <c r="D50" s="398" t="s">
+      <c r="D50" s="406" t="s">
         <v>111</v>
       </c>
-      <c r="E50" s="399"/>
-      <c r="F50" s="399"/>
-      <c r="G50" s="399"/>
-      <c r="H50" s="399"/>
-      <c r="I50" s="399"/>
-      <c r="J50" s="399"/>
-      <c r="K50" s="399"/>
-      <c r="L50" s="399"/>
-      <c r="M50" s="399"/>
-      <c r="N50" s="400"/>
-    </row>
-    <row r="51" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E50" s="407"/>
+      <c r="F50" s="407"/>
+      <c r="G50" s="407"/>
+      <c r="H50" s="407"/>
+      <c r="I50" s="407"/>
+      <c r="J50" s="407"/>
+      <c r="K50" s="407"/>
+      <c r="L50" s="407"/>
+      <c r="M50" s="407"/>
+      <c r="N50" s="408"/>
+    </row>
+    <row r="51" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="79" t="s">
         <v>71</v>
       </c>
@@ -10783,7 +10783,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="52" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B52" s="99" t="s">
         <v>72</v>
       </c>
@@ -10822,7 +10822,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B53" s="99" t="s">
         <v>110</v>
       </c>
@@ -10861,7 +10861,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="2:14" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B54" s="99" t="s">
         <v>452</v>
       </c>
@@ -10900,7 +10900,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="55" spans="2:14" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B55" s="99" t="s">
         <v>453</v>
       </c>
@@ -10939,7 +10939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B56" s="99" t="s">
         <v>73</v>
       </c>
@@ -10978,7 +10978,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="57" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B57" s="99" t="s">
         <v>74</v>
       </c>
@@ -11017,7 +11017,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="2:14" ht="16.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:14" ht="16.350000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B58" s="127" t="s">
         <v>36</v>
       </c>
@@ -11056,7 +11056,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="59" spans="2:14" ht="13.5" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:14" ht="13.5" thickTop="1" x14ac:dyDescent="0.2">
       <c r="C59" s="166" t="s">
         <v>112</v>
       </c>
@@ -11083,54 +11083,54 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <sheetPr codeName="Sheet10"/>
   <dimension ref="A1:T61"/>
-  <sheetFormatPr defaultColWidth="7.796875" defaultRowHeight="13" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="7.83203125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="3.296875" style="66" customWidth="1"/>
-    <col min="2" max="2" width="14.69921875" style="130" customWidth="1"/>
-    <col min="3" max="3" width="10.796875" style="130" customWidth="1"/>
-    <col min="4" max="5" width="9.796875" style="130" customWidth="1"/>
+    <col min="1" max="1" width="3.33203125" style="66" customWidth="1"/>
+    <col min="2" max="2" width="14.6640625" style="130" customWidth="1"/>
+    <col min="3" max="3" width="10.83203125" style="130" customWidth="1"/>
+    <col min="4" max="5" width="9.83203125" style="130" customWidth="1"/>
     <col min="6" max="6" width="11" style="130" customWidth="1"/>
-    <col min="7" max="8" width="9.796875" style="130" customWidth="1"/>
-    <col min="9" max="9" width="10.796875" style="66" customWidth="1"/>
-    <col min="10" max="10" width="9.796875" style="66" customWidth="1"/>
-    <col min="11" max="11" width="8.796875" style="66" customWidth="1"/>
-    <col min="12" max="12" width="10.69921875" style="66" customWidth="1"/>
-    <col min="13" max="13" width="9.796875" style="66" customWidth="1"/>
-    <col min="14" max="14" width="8.796875" style="66" customWidth="1"/>
-    <col min="15" max="15" width="10.796875" style="66" customWidth="1"/>
-    <col min="16" max="16" width="9.796875" style="66" customWidth="1"/>
-    <col min="17" max="17" width="8.796875" style="66" customWidth="1"/>
-    <col min="18" max="18" width="10.796875" style="66" customWidth="1"/>
-    <col min="19" max="19" width="9.796875" style="66" customWidth="1"/>
+    <col min="7" max="8" width="9.83203125" style="130" customWidth="1"/>
+    <col min="9" max="9" width="10.83203125" style="66" customWidth="1"/>
+    <col min="10" max="10" width="9.83203125" style="66" customWidth="1"/>
+    <col min="11" max="11" width="8.83203125" style="66" customWidth="1"/>
+    <col min="12" max="12" width="10.6640625" style="66" customWidth="1"/>
+    <col min="13" max="13" width="9.83203125" style="66" customWidth="1"/>
+    <col min="14" max="14" width="8.83203125" style="66" customWidth="1"/>
+    <col min="15" max="15" width="10.83203125" style="66" customWidth="1"/>
+    <col min="16" max="16" width="9.83203125" style="66" customWidth="1"/>
+    <col min="17" max="17" width="8.83203125" style="66" customWidth="1"/>
+    <col min="18" max="18" width="10.83203125" style="66" customWidth="1"/>
+    <col min="19" max="19" width="9.83203125" style="66" customWidth="1"/>
     <col min="20" max="20" width="12" style="66" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="7.796875" style="66"/>
+    <col min="21" max="16384" width="7.83203125" style="66"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="408" t="s">
+    <row r="1" spans="1:20" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="416" t="s">
         <v>113</v>
       </c>
-      <c r="B1" s="408"/>
-      <c r="C1" s="408"/>
-      <c r="D1" s="408"/>
-      <c r="E1" s="408"/>
-      <c r="F1" s="408"/>
-      <c r="G1" s="408"/>
-      <c r="H1" s="408"/>
-      <c r="I1" s="408"/>
-      <c r="J1" s="408"/>
-      <c r="K1" s="408"/>
-      <c r="L1" s="408"/>
-      <c r="M1" s="408"/>
-      <c r="N1" s="408"/>
-      <c r="O1" s="408"/>
-      <c r="P1" s="408"/>
-      <c r="Q1" s="408"/>
-      <c r="R1" s="408"/>
-      <c r="S1" s="408"/>
-      <c r="T1" s="408"/>
-    </row>
-    <row r="2" spans="1:20" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B1" s="416"/>
+      <c r="C1" s="416"/>
+      <c r="D1" s="416"/>
+      <c r="E1" s="416"/>
+      <c r="F1" s="416"/>
+      <c r="G1" s="416"/>
+      <c r="H1" s="416"/>
+      <c r="I1" s="416"/>
+      <c r="J1" s="416"/>
+      <c r="K1" s="416"/>
+      <c r="L1" s="416"/>
+      <c r="M1" s="416"/>
+      <c r="N1" s="416"/>
+      <c r="O1" s="416"/>
+      <c r="P1" s="416"/>
+      <c r="Q1" s="416"/>
+      <c r="R1" s="416"/>
+      <c r="S1" s="416"/>
+      <c r="T1" s="416"/>
+    </row>
+    <row r="2" spans="1:20" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="64"/>
       <c r="B2" s="129"/>
       <c r="C2" s="129"/>
@@ -11143,43 +11143,43 @@
       <c r="J2" s="64"/>
       <c r="K2" s="64"/>
     </row>
-    <row r="3" spans="1:20" ht="16" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:20" ht="15.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="102" t="s">
         <v>114</v>
       </c>
       <c r="B3" s="133"/>
-      <c r="C3" s="409" t="s">
+      <c r="C3" s="417" t="s">
         <v>115</v>
       </c>
-      <c r="D3" s="410"/>
-      <c r="E3" s="410"/>
-      <c r="F3" s="406" t="s">
+      <c r="D3" s="418"/>
+      <c r="E3" s="418"/>
+      <c r="F3" s="414" t="s">
         <v>116</v>
       </c>
-      <c r="G3" s="410"/>
-      <c r="H3" s="410"/>
-      <c r="I3" s="406" t="s">
+      <c r="G3" s="418"/>
+      <c r="H3" s="418"/>
+      <c r="I3" s="414" t="s">
         <v>117</v>
       </c>
-      <c r="J3" s="406"/>
-      <c r="K3" s="406"/>
-      <c r="L3" s="406" t="s">
+      <c r="J3" s="414"/>
+      <c r="K3" s="414"/>
+      <c r="L3" s="414" t="s">
         <v>118</v>
       </c>
-      <c r="M3" s="406"/>
-      <c r="N3" s="406"/>
-      <c r="O3" s="406" t="s">
+      <c r="M3" s="414"/>
+      <c r="N3" s="414"/>
+      <c r="O3" s="414" t="s">
         <v>119</v>
       </c>
-      <c r="P3" s="406"/>
-      <c r="Q3" s="406"/>
-      <c r="R3" s="406" t="s">
+      <c r="P3" s="414"/>
+      <c r="Q3" s="414"/>
+      <c r="R3" s="414" t="s">
         <v>120</v>
       </c>
-      <c r="S3" s="406"/>
-      <c r="T3" s="407"/>
-    </row>
-    <row r="4" spans="1:20" ht="16" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="S3" s="414"/>
+      <c r="T3" s="415"/>
+    </row>
+    <row r="4" spans="1:20" ht="15.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="134" t="s">
         <v>80</v>
       </c>
@@ -11239,7 +11239,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="5" spans="1:20" ht="16" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:20" ht="15.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A5" s="79"/>
       <c r="B5" s="136" t="s">
         <v>121</v>
@@ -11299,7 +11299,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:20" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="79"/>
       <c r="B6" s="136" t="s">
         <v>122</v>
@@ -11359,7 +11359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:20" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="79"/>
       <c r="B7" s="136" t="s">
         <v>123</v>
@@ -11419,7 +11419,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:20" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="79"/>
       <c r="B8" s="136" t="s">
         <v>82</v>
@@ -11479,7 +11479,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:20" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="79"/>
       <c r="B9" s="136" t="s">
         <v>83</v>
@@ -11539,7 +11539,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:20" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="79"/>
       <c r="B10" s="136" t="s">
         <v>84</v>
@@ -11599,7 +11599,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:20" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="79"/>
       <c r="B11" s="136" t="s">
         <v>85</v>
@@ -11659,7 +11659,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:20" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="79"/>
       <c r="B12" s="136" t="s">
         <v>86</v>
@@ -11719,7 +11719,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:20" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="79"/>
       <c r="B13" s="136" t="s">
         <v>87</v>
@@ -11779,7 +11779,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:20" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="79"/>
       <c r="B14" s="136" t="s">
         <v>88</v>
@@ -11839,7 +11839,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:20" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="79"/>
       <c r="B15" s="136" t="s">
         <v>89</v>
@@ -11899,7 +11899,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:20" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="79"/>
       <c r="B16" s="136" t="s">
         <v>124</v>
@@ -11959,7 +11959,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:20" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="79"/>
       <c r="B17" s="136" t="s">
         <v>125</v>
@@ -12019,7 +12019,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:20" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="79"/>
       <c r="B18" s="136" t="s">
         <v>126</v>
@@ -12079,7 +12079,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="19" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:20" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="79"/>
       <c r="B19" s="136" t="s">
         <v>127</v>
@@ -12139,7 +12139,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="20" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:20" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="79"/>
       <c r="B20" s="136" t="s">
         <v>128</v>
@@ -12199,7 +12199,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="21" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:20" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="79"/>
       <c r="B21" s="136" t="s">
         <v>129</v>
@@ -12259,7 +12259,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="22" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:20" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="79"/>
       <c r="B22" s="136" t="s">
         <v>130</v>
@@ -12319,7 +12319,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="23" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:20" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="79"/>
       <c r="B23" s="80" t="s">
         <v>131</v>
@@ -12379,7 +12379,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="24" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:20" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="79"/>
       <c r="B24" s="136" t="s">
         <v>91</v>
@@ -12439,7 +12439,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="25" spans="1:20" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:20" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="137"/>
       <c r="B25" s="138" t="s">
         <v>36</v>
@@ -12499,7 +12499,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="26" spans="1:20" ht="14.5" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:20" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A26" s="79"/>
       <c r="C26" s="132"/>
       <c r="D26" s="132"/>
@@ -12513,7 +12513,7 @@
       <c r="L26" s="79"/>
       <c r="M26" s="67"/>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C27" s="131"/>
       <c r="D27" s="131"/>
       <c r="E27" s="131"/>
@@ -12523,7 +12523,7 @@
       <c r="L27" s="67"/>
       <c r="M27" s="67"/>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C28" s="131"/>
       <c r="D28" s="131"/>
       <c r="E28" s="131"/>
@@ -12533,7 +12533,7 @@
       <c r="L28" s="67"/>
       <c r="M28" s="67"/>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C29" s="131"/>
       <c r="D29" s="131"/>
       <c r="E29" s="131"/>
@@ -12543,7 +12543,7 @@
       <c r="L29" s="67"/>
       <c r="M29" s="67"/>
     </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C30" s="131"/>
       <c r="D30" s="131"/>
       <c r="E30" s="131"/>
@@ -12553,7 +12553,7 @@
       <c r="L30" s="67"/>
       <c r="M30" s="67"/>
     </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C31" s="131"/>
       <c r="D31" s="131"/>
       <c r="E31" s="131"/>
@@ -12563,7 +12563,7 @@
       <c r="L31" s="67"/>
       <c r="M31" s="67"/>
     </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C32" s="131"/>
       <c r="D32" s="131"/>
       <c r="E32" s="131"/>
@@ -12573,7 +12573,7 @@
       <c r="L32" s="67"/>
       <c r="M32" s="67"/>
     </row>
-    <row r="33" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="33" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C33" s="131"/>
       <c r="D33" s="131"/>
       <c r="E33" s="131"/>
@@ -12583,7 +12583,7 @@
       <c r="L33" s="67"/>
       <c r="M33" s="67"/>
     </row>
-    <row r="34" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="34" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C34" s="131"/>
       <c r="D34" s="131"/>
       <c r="E34" s="131"/>
@@ -12593,7 +12593,7 @@
       <c r="L34" s="67"/>
       <c r="M34" s="67"/>
     </row>
-    <row r="35" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="35" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C35" s="131"/>
       <c r="D35" s="131"/>
       <c r="E35" s="131"/>
@@ -12603,7 +12603,7 @@
       <c r="L35" s="67"/>
       <c r="M35" s="67"/>
     </row>
-    <row r="36" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="36" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C36" s="131"/>
       <c r="D36" s="131"/>
       <c r="E36" s="131"/>
@@ -12613,7 +12613,7 @@
       <c r="L36" s="67"/>
       <c r="M36" s="67"/>
     </row>
-    <row r="37" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="37" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C37" s="131"/>
       <c r="D37" s="131"/>
       <c r="E37" s="131"/>
@@ -12623,7 +12623,7 @@
       <c r="L37" s="67"/>
       <c r="M37" s="67"/>
     </row>
-    <row r="38" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="38" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C38" s="131"/>
       <c r="D38" s="131"/>
       <c r="E38" s="131"/>
@@ -12633,7 +12633,7 @@
       <c r="L38" s="67"/>
       <c r="M38" s="67"/>
     </row>
-    <row r="39" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="39" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C39" s="131"/>
       <c r="D39" s="131"/>
       <c r="E39" s="131"/>
@@ -12643,7 +12643,7 @@
       <c r="L39" s="67"/>
       <c r="M39" s="67"/>
     </row>
-    <row r="40" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="40" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C40" s="131"/>
       <c r="D40" s="131"/>
       <c r="E40" s="131"/>
@@ -12653,7 +12653,7 @@
       <c r="L40" s="67"/>
       <c r="M40" s="67"/>
     </row>
-    <row r="41" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="41" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C41" s="131"/>
       <c r="D41" s="131"/>
       <c r="E41" s="131"/>
@@ -12663,7 +12663,7 @@
       <c r="L41" s="67"/>
       <c r="M41" s="67"/>
     </row>
-    <row r="42" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="42" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C42" s="131"/>
       <c r="D42" s="131"/>
       <c r="E42" s="131"/>
@@ -12673,7 +12673,7 @@
       <c r="L42" s="67"/>
       <c r="M42" s="67"/>
     </row>
-    <row r="43" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="43" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C43" s="131"/>
       <c r="D43" s="131"/>
       <c r="E43" s="131"/>
@@ -12683,7 +12683,7 @@
       <c r="L43" s="67"/>
       <c r="M43" s="67"/>
     </row>
-    <row r="44" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="44" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C44" s="131"/>
       <c r="D44" s="131"/>
       <c r="E44" s="131"/>
@@ -12693,7 +12693,7 @@
       <c r="L44" s="67"/>
       <c r="M44" s="67"/>
     </row>
-    <row r="45" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="45" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C45" s="131"/>
       <c r="D45" s="131"/>
       <c r="E45" s="131"/>
@@ -12703,7 +12703,7 @@
       <c r="L45" s="67"/>
       <c r="M45" s="67"/>
     </row>
-    <row r="46" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="46" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C46" s="131"/>
       <c r="D46" s="131"/>
       <c r="E46" s="131"/>
@@ -12713,7 +12713,7 @@
       <c r="L46" s="67"/>
       <c r="M46" s="67"/>
     </row>
-    <row r="47" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="47" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C47" s="131"/>
       <c r="D47" s="131"/>
       <c r="E47" s="131"/>
@@ -12723,7 +12723,7 @@
       <c r="L47" s="67"/>
       <c r="M47" s="67"/>
     </row>
-    <row r="48" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="48" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C48" s="131"/>
       <c r="D48" s="131"/>
       <c r="E48" s="131"/>
@@ -12733,7 +12733,7 @@
       <c r="L48" s="67"/>
       <c r="M48" s="67"/>
     </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="131"/>
       <c r="D49" s="131"/>
       <c r="E49" s="131"/>
@@ -12743,7 +12743,7 @@
       <c r="L49" s="67"/>
       <c r="M49" s="67"/>
     </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="131"/>
       <c r="D50" s="131"/>
       <c r="E50" s="131"/>
@@ -12753,7 +12753,7 @@
       <c r="L50" s="67"/>
       <c r="M50" s="67"/>
     </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="131"/>
       <c r="D51" s="131"/>
       <c r="E51" s="131"/>
@@ -12763,7 +12763,7 @@
       <c r="L51" s="67"/>
       <c r="M51" s="67"/>
     </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="131"/>
       <c r="D52" s="131"/>
       <c r="E52" s="131"/>
@@ -12773,7 +12773,7 @@
       <c r="L52" s="67"/>
       <c r="M52" s="67"/>
     </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="131"/>
       <c r="D53" s="131"/>
       <c r="E53" s="131"/>
@@ -12783,7 +12783,7 @@
       <c r="L53" s="67"/>
       <c r="M53" s="67"/>
     </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="131"/>
       <c r="D54" s="131"/>
       <c r="E54" s="131"/>
@@ -12793,7 +12793,7 @@
       <c r="L54" s="67"/>
       <c r="M54" s="67"/>
     </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="131"/>
       <c r="D55" s="131"/>
       <c r="E55" s="131"/>
@@ -12803,7 +12803,7 @@
       <c r="L55" s="67"/>
       <c r="M55" s="67"/>
     </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="131"/>
       <c r="D56" s="131"/>
       <c r="E56" s="131"/>
@@ -12813,7 +12813,7 @@
       <c r="L56" s="67"/>
       <c r="M56" s="67"/>
     </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="131"/>
       <c r="D57" s="131"/>
       <c r="E57" s="131"/>
@@ -12823,7 +12823,7 @@
       <c r="L57" s="67"/>
       <c r="M57" s="67"/>
     </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="131"/>
       <c r="D58" s="131"/>
       <c r="E58" s="131"/>
@@ -12833,7 +12833,7 @@
       <c r="L58" s="67"/>
       <c r="M58" s="67"/>
     </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="131"/>
       <c r="D59" s="131"/>
       <c r="E59" s="131"/>
@@ -12843,7 +12843,7 @@
       <c r="L59" s="67"/>
       <c r="M59" s="67"/>
     </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="131"/>
       <c r="D60" s="131"/>
       <c r="E60" s="131"/>
@@ -12853,7 +12853,7 @@
       <c r="L60" s="67"/>
       <c r="M60" s="67"/>
     </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="131"/>
       <c r="D61" s="131"/>
       <c r="E61" s="131"/>
@@ -12886,59 +12886,59 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <sheetPr codeName="Sheet11"/>
   <dimension ref="A1:AE132"/>
-  <sheetFormatPr defaultColWidth="9.296875" defaultRowHeight="13" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.19921875" style="34" customWidth="1"/>
-    <col min="2" max="2" width="8.296875" style="139" customWidth="1"/>
-    <col min="3" max="3" width="67.796875" style="34" customWidth="1"/>
-    <col min="4" max="4" width="36.19921875" style="34" customWidth="1"/>
-    <col min="5" max="5" width="8.796875" style="34" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.69921875" style="34" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.1640625" style="34" customWidth="1"/>
+    <col min="2" max="2" width="8.33203125" style="139" customWidth="1"/>
+    <col min="3" max="3" width="67.83203125" style="34" customWidth="1"/>
+    <col min="4" max="4" width="36.1640625" style="34" customWidth="1"/>
+    <col min="5" max="5" width="8.83203125" style="34" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.6640625" style="34" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12" style="34" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.796875" style="34" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.69921875" style="34" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.83203125" style="34" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.6640625" style="34" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12" style="34" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.796875" style="34" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.69921875" style="34" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.83203125" style="34" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.6640625" style="34" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="12" style="34" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.796875" style="34" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.69921875" style="34" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.83203125" style="34" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.6640625" style="34" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="12" style="34" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="8.796875" style="34" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9.69921875" style="34" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="8.83203125" style="34" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.6640625" style="34" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="12" style="34" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="8.796875" style="34" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="9.69921875" style="34" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="12.296875" style="34" customWidth="1"/>
-    <col min="23" max="16384" width="9.296875" style="26"/>
+    <col min="20" max="20" width="8.83203125" style="34" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="9.6640625" style="34" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.33203125" style="34" customWidth="1"/>
+    <col min="23" max="16384" width="9.33203125" style="26"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B1" s="417" t="s">
+    <row r="1" spans="1:22" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="345" t="s">
         <v>132</v>
       </c>
-      <c r="C1" s="417"/>
-      <c r="D1" s="417"/>
-      <c r="E1" s="417"/>
-      <c r="F1" s="417"/>
-      <c r="G1" s="417"/>
-      <c r="H1" s="417"/>
-      <c r="I1" s="417"/>
-      <c r="J1" s="417"/>
-      <c r="K1" s="417"/>
-      <c r="L1" s="417"/>
-      <c r="M1" s="417"/>
-      <c r="N1" s="417"/>
-      <c r="O1" s="417"/>
-      <c r="P1" s="417"/>
-      <c r="Q1" s="417"/>
-      <c r="R1" s="417"/>
-      <c r="S1" s="417"/>
-      <c r="T1" s="417"/>
-      <c r="U1" s="417"/>
-      <c r="V1" s="417"/>
-    </row>
-    <row r="2" spans="1:22" ht="11.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C1" s="345"/>
+      <c r="D1" s="345"/>
+      <c r="E1" s="345"/>
+      <c r="F1" s="345"/>
+      <c r="G1" s="345"/>
+      <c r="H1" s="345"/>
+      <c r="I1" s="345"/>
+      <c r="J1" s="345"/>
+      <c r="K1" s="345"/>
+      <c r="L1" s="345"/>
+      <c r="M1" s="345"/>
+      <c r="N1" s="345"/>
+      <c r="O1" s="345"/>
+      <c r="P1" s="345"/>
+      <c r="Q1" s="345"/>
+      <c r="R1" s="345"/>
+      <c r="S1" s="345"/>
+      <c r="T1" s="345"/>
+      <c r="U1" s="345"/>
+      <c r="V1" s="345"/>
+    </row>
+    <row r="2" spans="1:22" ht="11.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C2" s="140"/>
       <c r="D2" s="140"/>
       <c r="G2" s="140"/>
@@ -12952,51 +12952,51 @@
       <c r="S2" s="140"/>
       <c r="T2" s="140"/>
     </row>
-    <row r="3" spans="1:22" ht="16.399999999999999" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="411" t="s">
+    <row r="3" spans="1:22" ht="16.350000000000001" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="349" t="s">
         <v>133</v>
       </c>
-      <c r="C3" s="413" t="s">
+      <c r="C3" s="351" t="s">
         <v>134</v>
       </c>
-      <c r="D3" s="413" t="s">
+      <c r="D3" s="351" t="s">
         <v>135</v>
       </c>
-      <c r="E3" s="415" t="s">
+      <c r="E3" s="346" t="s">
         <v>115</v>
       </c>
-      <c r="F3" s="416"/>
-      <c r="G3" s="416"/>
-      <c r="H3" s="415" t="s">
+      <c r="F3" s="347"/>
+      <c r="G3" s="347"/>
+      <c r="H3" s="346" t="s">
         <v>116</v>
       </c>
-      <c r="I3" s="416"/>
-      <c r="J3" s="416"/>
-      <c r="K3" s="415" t="s">
+      <c r="I3" s="347"/>
+      <c r="J3" s="347"/>
+      <c r="K3" s="346" t="s">
         <v>117</v>
       </c>
-      <c r="L3" s="416"/>
-      <c r="M3" s="416"/>
-      <c r="N3" s="415" t="s">
+      <c r="L3" s="347"/>
+      <c r="M3" s="347"/>
+      <c r="N3" s="346" t="s">
         <v>118</v>
       </c>
-      <c r="O3" s="416"/>
-      <c r="P3" s="416"/>
-      <c r="Q3" s="415" t="s">
+      <c r="O3" s="347"/>
+      <c r="P3" s="347"/>
+      <c r="Q3" s="346" t="s">
         <v>119</v>
       </c>
-      <c r="R3" s="416"/>
-      <c r="S3" s="416"/>
-      <c r="T3" s="415" t="s">
+      <c r="R3" s="347"/>
+      <c r="S3" s="347"/>
+      <c r="T3" s="346" t="s">
         <v>136</v>
       </c>
-      <c r="U3" s="416"/>
-      <c r="V3" s="418"/>
-    </row>
-    <row r="4" spans="1:22" ht="16.399999999999999" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="412"/>
-      <c r="C4" s="414"/>
-      <c r="D4" s="414"/>
+      <c r="U3" s="347"/>
+      <c r="V3" s="348"/>
+    </row>
+    <row r="4" spans="1:22" ht="16.350000000000001" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="350"/>
+      <c r="C4" s="352"/>
+      <c r="D4" s="352"/>
       <c r="E4" s="309" t="s">
         <v>36</v>
       </c>
@@ -13052,7 +13052,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="5" spans="1:22" s="141" customFormat="1" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:22" s="141" customFormat="1" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A5" s="142"/>
       <c r="B5" s="147"/>
       <c r="C5" s="148" t="s">
@@ -13114,7 +13114,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="6" spans="1:22" s="141" customFormat="1" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:22" s="141" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="142"/>
       <c r="B6" s="312" t="s">
         <v>138</v>
@@ -13180,7 +13180,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:22" s="141" customFormat="1" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:22" s="141" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="142"/>
       <c r="B7" s="150" t="s">
         <v>141</v>
@@ -13246,7 +13246,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="8" spans="1:22" s="141" customFormat="1" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:22" s="141" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="142"/>
       <c r="B8" s="150" t="s">
         <v>144</v>
@@ -13312,7 +13312,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="9" spans="1:22" s="141" customFormat="1" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:22" s="141" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="142"/>
       <c r="B9" s="150" t="s">
         <v>147</v>
@@ -13378,7 +13378,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="10" spans="1:22" s="141" customFormat="1" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:22" s="141" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="142"/>
       <c r="B10" s="150" t="s">
         <v>150</v>
@@ -13444,7 +13444,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="11" spans="1:22" s="141" customFormat="1" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:22" s="141" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="142"/>
       <c r="B11" s="150" t="s">
         <v>153</v>
@@ -13510,7 +13510,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="12" spans="1:22" s="141" customFormat="1" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:22" s="141" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="142"/>
       <c r="B12" s="150" t="s">
         <v>156</v>
@@ -13576,7 +13576,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="13" spans="1:22" s="141" customFormat="1" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:22" s="141" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="142"/>
       <c r="B13" s="150" t="s">
         <v>159</v>
@@ -13642,7 +13642,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="14" spans="1:22" s="141" customFormat="1" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:22" s="141" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="142"/>
       <c r="B14" s="150" t="s">
         <v>162</v>
@@ -13708,7 +13708,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="15" spans="1:22" s="141" customFormat="1" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:22" s="141" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="142"/>
       <c r="B15" s="150" t="s">
         <v>165</v>
@@ -13774,7 +13774,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="16" spans="1:22" s="141" customFormat="1" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:22" s="141" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="142"/>
       <c r="B16" s="150" t="s">
         <v>168</v>
@@ -13840,7 +13840,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="17" spans="1:22" s="141" customFormat="1" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:22" s="141" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="142"/>
       <c r="B17" s="150" t="s">
         <v>171</v>
@@ -13906,7 +13906,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="1:22" s="141" customFormat="1" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:22" s="141" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="142"/>
       <c r="B18" s="150" t="s">
         <v>174</v>
@@ -13972,7 +13972,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="19" spans="1:22" s="141" customFormat="1" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:22" s="141" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="142"/>
       <c r="B19" s="150" t="s">
         <v>177</v>
@@ -14038,7 +14038,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="20" spans="1:22" s="141" customFormat="1" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:22" s="141" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="142"/>
       <c r="B20" s="150" t="s">
         <v>180</v>
@@ -14104,7 +14104,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="21" spans="1:22" s="141" customFormat="1" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:22" s="141" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="142"/>
       <c r="B21" s="150" t="s">
         <v>183</v>
@@ -14170,7 +14170,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="22" spans="1:22" s="141" customFormat="1" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:22" s="141" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="142"/>
       <c r="B22" s="150" t="s">
         <v>186</v>
@@ -14236,7 +14236,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="23" spans="1:22" s="141" customFormat="1" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:22" s="141" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="142"/>
       <c r="B23" s="150" t="s">
         <v>189</v>
@@ -14302,7 +14302,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="24" spans="1:22" s="141" customFormat="1" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:22" s="141" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="142"/>
       <c r="B24" s="150" t="s">
         <v>192</v>
@@ -14368,7 +14368,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="25" spans="1:22" s="141" customFormat="1" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:22" s="141" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="142"/>
       <c r="B25" s="150" t="s">
         <v>195</v>
@@ -14434,7 +14434,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="26" spans="1:22" s="141" customFormat="1" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:22" s="141" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="142"/>
       <c r="B26" s="150" t="s">
         <v>198</v>
@@ -14500,7 +14500,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="27" spans="1:22" s="141" customFormat="1" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:22" s="141" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="142"/>
       <c r="B27" s="150" t="s">
         <v>201</v>
@@ -14566,7 +14566,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="28" spans="1:22" s="141" customFormat="1" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:22" s="141" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="142"/>
       <c r="B28" s="150" t="s">
         <v>204</v>
@@ -14632,7 +14632,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="29" spans="1:22" s="141" customFormat="1" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:22" s="141" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="142"/>
       <c r="B29" s="150" t="s">
         <v>207</v>
@@ -14698,7 +14698,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="30" spans="1:22" s="141" customFormat="1" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:22" s="141" customFormat="1" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A30" s="142"/>
       <c r="B30" s="154" t="s">
         <v>210</v>
@@ -14764,7 +14764,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="1:22" ht="13.5" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:22" ht="13.5" thickTop="1" x14ac:dyDescent="0.2">
       <c r="B31" s="159" t="s">
         <v>37</v>
       </c>
@@ -14791,7 +14791,7 @@
       <c r="U31" s="26"/>
       <c r="V31" s="26"/>
     </row>
-    <row r="32" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B32" s="144"/>
       <c r="C32" s="84"/>
       <c r="D32" s="143"/>
@@ -14814,39 +14814,39 @@
       <c r="U32" s="26"/>
       <c r="V32" s="26"/>
     </row>
-    <row r="33" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B33" s="145"/>
       <c r="C33" s="84"/>
       <c r="D33" s="143"/>
       <c r="E33" s="82"/>
       <c r="N33" s="82"/>
     </row>
-    <row r="34" spans="1:31" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B34" s="417" t="s">
+    <row r="34" spans="1:31" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="345" t="s">
         <v>132</v>
       </c>
-      <c r="C34" s="417"/>
-      <c r="D34" s="417"/>
-      <c r="E34" s="417"/>
-      <c r="F34" s="417"/>
-      <c r="G34" s="417"/>
-      <c r="H34" s="417"/>
-      <c r="I34" s="417"/>
-      <c r="J34" s="417"/>
-      <c r="K34" s="417"/>
-      <c r="L34" s="417"/>
-      <c r="M34" s="417"/>
-      <c r="N34" s="417"/>
-      <c r="O34" s="417"/>
-      <c r="P34" s="417"/>
-      <c r="Q34" s="417"/>
-      <c r="R34" s="417"/>
-      <c r="S34" s="417"/>
-      <c r="T34" s="417"/>
-      <c r="U34" s="417"/>
-      <c r="V34" s="417"/>
-    </row>
-    <row r="35" spans="1:31" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C34" s="345"/>
+      <c r="D34" s="345"/>
+      <c r="E34" s="345"/>
+      <c r="F34" s="345"/>
+      <c r="G34" s="345"/>
+      <c r="H34" s="345"/>
+      <c r="I34" s="345"/>
+      <c r="J34" s="345"/>
+      <c r="K34" s="345"/>
+      <c r="L34" s="345"/>
+      <c r="M34" s="345"/>
+      <c r="N34" s="345"/>
+      <c r="O34" s="345"/>
+      <c r="P34" s="345"/>
+      <c r="Q34" s="345"/>
+      <c r="R34" s="345"/>
+      <c r="S34" s="345"/>
+      <c r="T34" s="345"/>
+      <c r="U34" s="345"/>
+      <c r="V34" s="345"/>
+    </row>
+    <row r="35" spans="1:31" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C35" s="140"/>
       <c r="D35" s="140"/>
       <c r="H35" s="140"/>
@@ -14867,46 +14867,46 @@
       <c r="AD35" s="146"/>
       <c r="AE35" s="146"/>
     </row>
-    <row r="36" spans="1:31" ht="16.399999999999999" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B36" s="411" t="s">
+    <row r="36" spans="1:31" ht="16.350000000000001" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="349" t="s">
         <v>133</v>
       </c>
-      <c r="C36" s="413" t="s">
+      <c r="C36" s="351" t="s">
         <v>134</v>
       </c>
-      <c r="D36" s="413" t="s">
+      <c r="D36" s="351" t="s">
         <v>135</v>
       </c>
-      <c r="E36" s="415" t="s">
+      <c r="E36" s="346" t="s">
         <v>115</v>
       </c>
-      <c r="F36" s="416"/>
-      <c r="G36" s="416"/>
-      <c r="H36" s="415" t="s">
+      <c r="F36" s="347"/>
+      <c r="G36" s="347"/>
+      <c r="H36" s="346" t="s">
         <v>116</v>
       </c>
-      <c r="I36" s="416"/>
-      <c r="J36" s="416"/>
-      <c r="K36" s="415" t="s">
+      <c r="I36" s="347"/>
+      <c r="J36" s="347"/>
+      <c r="K36" s="346" t="s">
         <v>117</v>
       </c>
-      <c r="L36" s="416"/>
-      <c r="M36" s="416"/>
-      <c r="N36" s="415" t="s">
+      <c r="L36" s="347"/>
+      <c r="M36" s="347"/>
+      <c r="N36" s="346" t="s">
         <v>118</v>
       </c>
-      <c r="O36" s="416"/>
-      <c r="P36" s="416"/>
-      <c r="Q36" s="415" t="s">
+      <c r="O36" s="347"/>
+      <c r="P36" s="347"/>
+      <c r="Q36" s="346" t="s">
         <v>119</v>
       </c>
-      <c r="R36" s="416"/>
-      <c r="S36" s="416"/>
-      <c r="T36" s="415" t="s">
+      <c r="R36" s="347"/>
+      <c r="S36" s="347"/>
+      <c r="T36" s="346" t="s">
         <v>120</v>
       </c>
-      <c r="U36" s="416"/>
-      <c r="V36" s="418"/>
+      <c r="U36" s="347"/>
+      <c r="V36" s="348"/>
       <c r="W36" s="146"/>
       <c r="X36" s="146"/>
       <c r="Y36" s="146"/>
@@ -14917,10 +14917,10 @@
       <c r="AD36" s="146"/>
       <c r="AE36" s="146"/>
     </row>
-    <row r="37" spans="1:31" ht="16.399999999999999" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B37" s="412"/>
-      <c r="C37" s="414"/>
-      <c r="D37" s="414"/>
+    <row r="37" spans="1:31" ht="16.350000000000001" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="350"/>
+      <c r="C37" s="352"/>
+      <c r="D37" s="352"/>
       <c r="E37" s="309" t="s">
         <v>36</v>
       </c>
@@ -14985,7 +14985,7 @@
       <c r="AD37" s="146"/>
       <c r="AE37" s="146"/>
     </row>
-    <row r="38" spans="1:31" s="141" customFormat="1" ht="16.399999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:31" s="141" customFormat="1" ht="16.350000000000001" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A38" s="142"/>
       <c r="B38" s="333" t="s">
         <v>214</v>
@@ -15060,7 +15060,7 @@
       <c r="AD38" s="146"/>
       <c r="AE38" s="146"/>
     </row>
-    <row r="39" spans="1:31" s="141" customFormat="1" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:31" s="141" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="142"/>
       <c r="B39" s="150" t="s">
         <v>217</v>
@@ -15135,7 +15135,7 @@
       <c r="AD39" s="146"/>
       <c r="AE39" s="146"/>
     </row>
-    <row r="40" spans="1:31" s="141" customFormat="1" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:31" s="141" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="142"/>
       <c r="B40" s="150" t="s">
         <v>220</v>
@@ -15210,7 +15210,7 @@
       <c r="AD40" s="146"/>
       <c r="AE40" s="146"/>
     </row>
-    <row r="41" spans="1:31" s="141" customFormat="1" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:31" s="141" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="142"/>
       <c r="B41" s="150" t="s">
         <v>223</v>
@@ -15285,7 +15285,7 @@
       <c r="AD41" s="146"/>
       <c r="AE41" s="146"/>
     </row>
-    <row r="42" spans="1:31" s="141" customFormat="1" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:31" s="141" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="142"/>
       <c r="B42" s="150" t="s">
         <v>226</v>
@@ -15360,7 +15360,7 @@
       <c r="AD42" s="146"/>
       <c r="AE42" s="146"/>
     </row>
-    <row r="43" spans="1:31" s="141" customFormat="1" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:31" s="141" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="142"/>
       <c r="B43" s="150" t="s">
         <v>229</v>
@@ -15435,7 +15435,7 @@
       <c r="AD43" s="146"/>
       <c r="AE43" s="146"/>
     </row>
-    <row r="44" spans="1:31" s="141" customFormat="1" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:31" s="141" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="142"/>
       <c r="B44" s="150" t="s">
         <v>232</v>
@@ -15510,7 +15510,7 @@
       <c r="AD44" s="146"/>
       <c r="AE44" s="146"/>
     </row>
-    <row r="45" spans="1:31" s="141" customFormat="1" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:31" s="141" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="142"/>
       <c r="B45" s="150" t="s">
         <v>235</v>
@@ -15585,7 +15585,7 @@
       <c r="AD45" s="146"/>
       <c r="AE45" s="146"/>
     </row>
-    <row r="46" spans="1:31" s="141" customFormat="1" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:31" s="141" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="142"/>
       <c r="B46" s="150" t="s">
         <v>238</v>
@@ -15660,7 +15660,7 @@
       <c r="AD46" s="146"/>
       <c r="AE46" s="146"/>
     </row>
-    <row r="47" spans="1:31" s="170" customFormat="1" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:31" s="170" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="168"/>
       <c r="B47" s="150" t="s">
         <v>241</v>
@@ -15735,7 +15735,7 @@
       <c r="AD47" s="169"/>
       <c r="AE47" s="169"/>
     </row>
-    <row r="48" spans="1:31" s="141" customFormat="1" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:31" s="141" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="142"/>
       <c r="B48" s="150" t="s">
         <v>244</v>
@@ -15810,7 +15810,7 @@
       <c r="AD48" s="146"/>
       <c r="AE48" s="146"/>
     </row>
-    <row r="49" spans="1:31" s="141" customFormat="1" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:31" s="141" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="142"/>
       <c r="B49" s="150" t="s">
         <v>247</v>
@@ -15885,7 +15885,7 @@
       <c r="AD49" s="146"/>
       <c r="AE49" s="146"/>
     </row>
-    <row r="50" spans="1:31" s="141" customFormat="1" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:31" s="141" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="142"/>
       <c r="B50" s="150" t="s">
         <v>250</v>
@@ -15960,7 +15960,7 @@
       <c r="AD50" s="146"/>
       <c r="AE50" s="146"/>
     </row>
-    <row r="51" spans="1:31" s="141" customFormat="1" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:31" s="141" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="142"/>
       <c r="B51" s="150" t="s">
         <v>253</v>
@@ -16035,7 +16035,7 @@
       <c r="AD51" s="146"/>
       <c r="AE51" s="146"/>
     </row>
-    <row r="52" spans="1:31" s="141" customFormat="1" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:31" s="141" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="142"/>
       <c r="B52" s="150" t="s">
         <v>256</v>
@@ -16110,7 +16110,7 @@
       <c r="AD52" s="146"/>
       <c r="AE52" s="146"/>
     </row>
-    <row r="53" spans="1:31" s="141" customFormat="1" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:31" s="141" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="142"/>
       <c r="B53" s="150" t="s">
         <v>259</v>
@@ -16185,7 +16185,7 @@
       <c r="AD53" s="146"/>
       <c r="AE53" s="146"/>
     </row>
-    <row r="54" spans="1:31" s="141" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:31" s="141" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="142"/>
       <c r="B54" s="150" t="s">
         <v>262</v>
@@ -16260,7 +16260,7 @@
       <c r="AD54" s="146"/>
       <c r="AE54" s="146"/>
     </row>
-    <row r="55" spans="1:31" s="141" customFormat="1" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:31" s="141" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="142"/>
       <c r="B55" s="150" t="s">
         <v>265</v>
@@ -16335,7 +16335,7 @@
       <c r="AD55" s="146"/>
       <c r="AE55" s="146"/>
     </row>
-    <row r="56" spans="1:31" s="141" customFormat="1" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:31" s="141" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="142"/>
       <c r="B56" s="150" t="s">
         <v>268</v>
@@ -16410,7 +16410,7 @@
       <c r="AD56" s="146"/>
       <c r="AE56" s="146"/>
     </row>
-    <row r="57" spans="1:31" s="141" customFormat="1" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:31" s="141" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="142"/>
       <c r="B57" s="150" t="s">
         <v>271</v>
@@ -16485,7 +16485,7 @@
       <c r="AD57" s="146"/>
       <c r="AE57" s="146"/>
     </row>
-    <row r="58" spans="1:31" s="141" customFormat="1" ht="42" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:31" s="141" customFormat="1" ht="60" x14ac:dyDescent="0.2">
       <c r="A58" s="142"/>
       <c r="B58" s="150" t="s">
         <v>274</v>
@@ -16560,7 +16560,7 @@
       <c r="AD58" s="146"/>
       <c r="AE58" s="146"/>
     </row>
-    <row r="59" spans="1:31" s="141" customFormat="1" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:31" s="141" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="142"/>
       <c r="B59" s="150" t="s">
         <v>277</v>
@@ -16635,7 +16635,7 @@
       <c r="AD59" s="146"/>
       <c r="AE59" s="146"/>
     </row>
-    <row r="60" spans="1:31" s="141" customFormat="1" ht="27.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:31" s="141" customFormat="1" ht="27.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="142"/>
       <c r="B60" s="338" t="s">
         <v>280</v>
@@ -16710,7 +16710,7 @@
       <c r="AD60" s="146"/>
       <c r="AE60" s="146"/>
     </row>
-    <row r="61" spans="1:31" s="141" customFormat="1" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:31" s="141" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="142"/>
       <c r="B61" s="150" t="s">
         <v>283</v>
@@ -16785,7 +16785,7 @@
       <c r="AD61" s="146"/>
       <c r="AE61" s="146"/>
     </row>
-    <row r="62" spans="1:31" s="141" customFormat="1" ht="28.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:31" s="141" customFormat="1" ht="28.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A62" s="142"/>
       <c r="B62" s="154" t="s">
         <v>286</v>
@@ -16860,7 +16860,7 @@
       <c r="AD62" s="146"/>
       <c r="AE62" s="146"/>
     </row>
-    <row r="63" spans="1:31" ht="13.5" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:31" ht="13.5" thickTop="1" x14ac:dyDescent="0.2">
       <c r="B63" s="157" t="s">
         <v>37</v>
       </c>
@@ -16887,7 +16887,7 @@
       <c r="U63" s="26"/>
       <c r="V63" s="26"/>
     </row>
-    <row r="64" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B64" s="145"/>
       <c r="C64" s="84"/>
       <c r="D64" s="143"/>
@@ -16910,7 +16910,7 @@
       <c r="U64" s="26"/>
       <c r="V64" s="26"/>
     </row>
-    <row r="65" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B65" s="145"/>
       <c r="C65" s="84"/>
       <c r="D65" s="143"/>
@@ -16933,32 +16933,32 @@
       <c r="U65" s="26"/>
       <c r="V65" s="26"/>
     </row>
-    <row r="66" spans="1:22" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B66" s="417" t="s">
+    <row r="66" spans="1:22" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B66" s="345" t="s">
         <v>132</v>
       </c>
-      <c r="C66" s="417"/>
-      <c r="D66" s="417"/>
-      <c r="E66" s="417"/>
-      <c r="F66" s="417"/>
-      <c r="G66" s="417"/>
-      <c r="H66" s="417"/>
-      <c r="I66" s="417"/>
-      <c r="J66" s="417"/>
-      <c r="K66" s="417"/>
-      <c r="L66" s="417"/>
-      <c r="M66" s="417"/>
-      <c r="N66" s="417"/>
-      <c r="O66" s="417"/>
-      <c r="P66" s="417"/>
-      <c r="Q66" s="417"/>
-      <c r="R66" s="417"/>
-      <c r="S66" s="417"/>
-      <c r="T66" s="417"/>
-      <c r="U66" s="417"/>
-      <c r="V66" s="417"/>
-    </row>
-    <row r="67" spans="1:22" ht="11.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C66" s="345"/>
+      <c r="D66" s="345"/>
+      <c r="E66" s="345"/>
+      <c r="F66" s="345"/>
+      <c r="G66" s="345"/>
+      <c r="H66" s="345"/>
+      <c r="I66" s="345"/>
+      <c r="J66" s="345"/>
+      <c r="K66" s="345"/>
+      <c r="L66" s="345"/>
+      <c r="M66" s="345"/>
+      <c r="N66" s="345"/>
+      <c r="O66" s="345"/>
+      <c r="P66" s="345"/>
+      <c r="Q66" s="345"/>
+      <c r="R66" s="345"/>
+      <c r="S66" s="345"/>
+      <c r="T66" s="345"/>
+      <c r="U66" s="345"/>
+      <c r="V66" s="345"/>
+    </row>
+    <row r="67" spans="1:22" ht="11.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C67" s="140"/>
       <c r="D67" s="140"/>
       <c r="H67" s="140"/>
@@ -16968,51 +16968,51 @@
       <c r="R67" s="140"/>
       <c r="S67" s="140"/>
     </row>
-    <row r="68" spans="1:22" ht="16.399999999999999" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B68" s="411" t="s">
+    <row r="68" spans="1:22" ht="16.350000000000001" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B68" s="349" t="s">
         <v>133</v>
       </c>
-      <c r="C68" s="413" t="s">
+      <c r="C68" s="351" t="s">
         <v>134</v>
       </c>
-      <c r="D68" s="413" t="s">
+      <c r="D68" s="351" t="s">
         <v>135</v>
       </c>
-      <c r="E68" s="415" t="s">
+      <c r="E68" s="346" t="s">
         <v>115</v>
       </c>
-      <c r="F68" s="416"/>
-      <c r="G68" s="416"/>
-      <c r="H68" s="415" t="s">
+      <c r="F68" s="347"/>
+      <c r="G68" s="347"/>
+      <c r="H68" s="346" t="s">
         <v>116</v>
       </c>
-      <c r="I68" s="416"/>
-      <c r="J68" s="416"/>
-      <c r="K68" s="415" t="s">
+      <c r="I68" s="347"/>
+      <c r="J68" s="347"/>
+      <c r="K68" s="346" t="s">
         <v>117</v>
       </c>
-      <c r="L68" s="416"/>
-      <c r="M68" s="416"/>
-      <c r="N68" s="415" t="s">
+      <c r="L68" s="347"/>
+      <c r="M68" s="347"/>
+      <c r="N68" s="346" t="s">
         <v>118</v>
       </c>
-      <c r="O68" s="416"/>
-      <c r="P68" s="416"/>
-      <c r="Q68" s="415" t="s">
+      <c r="O68" s="347"/>
+      <c r="P68" s="347"/>
+      <c r="Q68" s="346" t="s">
         <v>119</v>
       </c>
-      <c r="R68" s="416"/>
-      <c r="S68" s="416"/>
-      <c r="T68" s="415" t="s">
+      <c r="R68" s="347"/>
+      <c r="S68" s="347"/>
+      <c r="T68" s="346" t="s">
         <v>120</v>
       </c>
-      <c r="U68" s="416"/>
-      <c r="V68" s="418"/>
-    </row>
-    <row r="69" spans="1:22" ht="16.399999999999999" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B69" s="412"/>
-      <c r="C69" s="414"/>
-      <c r="D69" s="414"/>
+      <c r="U68" s="347"/>
+      <c r="V68" s="348"/>
+    </row>
+    <row r="69" spans="1:22" ht="16.350000000000001" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B69" s="350"/>
+      <c r="C69" s="352"/>
+      <c r="D69" s="352"/>
       <c r="E69" s="309" t="s">
         <v>36</v>
       </c>
@@ -17068,7 +17068,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="70" spans="1:22" s="141" customFormat="1" ht="16.399999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:22" s="141" customFormat="1" ht="16.350000000000001" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A70" s="142"/>
       <c r="B70" s="338" t="s">
         <v>289</v>
@@ -17134,7 +17134,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="71" spans="1:22" s="141" customFormat="1" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:22" s="141" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="142"/>
       <c r="B71" s="150" t="s">
         <v>292</v>
@@ -17200,7 +17200,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="72" spans="1:22" s="141" customFormat="1" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:22" s="141" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="142"/>
       <c r="B72" s="150" t="s">
         <v>295</v>
@@ -17266,7 +17266,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="73" spans="1:22" s="141" customFormat="1" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:22" s="141" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="142"/>
       <c r="B73" s="150" t="s">
         <v>298</v>
@@ -17332,7 +17332,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:22" s="141" customFormat="1" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:22" s="141" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="142"/>
       <c r="B74" s="312" t="s">
         <v>301</v>
@@ -17398,7 +17398,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:22" s="141" customFormat="1" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:22" s="141" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="142"/>
       <c r="B75" s="150" t="s">
         <v>304</v>
@@ -17464,7 +17464,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="76" spans="1:22" s="141" customFormat="1" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:22" s="141" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="142"/>
       <c r="B76" s="150" t="s">
         <v>307</v>
@@ -17530,7 +17530,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:22" s="141" customFormat="1" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:22" s="141" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="142"/>
       <c r="B77" s="338" t="s">
         <v>310</v>
@@ -17596,7 +17596,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="78" spans="1:22" s="141" customFormat="1" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:22" s="141" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="142"/>
       <c r="B78" s="150" t="s">
         <v>313</v>
@@ -17662,7 +17662,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="79" spans="1:22" s="141" customFormat="1" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:22" s="141" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="142"/>
       <c r="B79" s="150" t="s">
         <v>316</v>
@@ -17728,7 +17728,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="80" spans="1:22" s="141" customFormat="1" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:22" s="141" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="142"/>
       <c r="B80" s="150" t="s">
         <v>319</v>
@@ -17794,7 +17794,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="81" spans="1:22" s="141" customFormat="1" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:22" s="141" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="142"/>
       <c r="B81" s="338" t="s">
         <v>322</v>
@@ -17860,7 +17860,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="82" spans="1:22" s="141" customFormat="1" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:22" s="141" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="142"/>
       <c r="B82" s="338" t="s">
         <v>325</v>
@@ -17926,7 +17926,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="83" spans="1:22" s="141" customFormat="1" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:22" s="141" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="142"/>
       <c r="B83" s="312" t="s">
         <v>328</v>
@@ -17992,7 +17992,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="84" spans="1:22" s="141" customFormat="1" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:22" s="141" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="142"/>
       <c r="B84" s="150" t="s">
         <v>331</v>
@@ -18058,7 +18058,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="85" spans="1:22" s="141" customFormat="1" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:22" s="141" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="142"/>
       <c r="B85" s="150" t="s">
         <v>334</v>
@@ -18124,7 +18124,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="86" spans="1:22" s="141" customFormat="1" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:22" s="141" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="142"/>
       <c r="B86" s="150" t="s">
         <v>337</v>
@@ -18190,7 +18190,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="87" spans="1:22" s="141" customFormat="1" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:22" s="141" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="142"/>
       <c r="B87" s="150" t="s">
         <v>340</v>
@@ -18256,7 +18256,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="88" spans="1:22" s="141" customFormat="1" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:22" s="141" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="142"/>
       <c r="B88" s="150" t="s">
         <v>343</v>
@@ -18322,7 +18322,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="89" spans="1:22" s="141" customFormat="1" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:22" s="141" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="142"/>
       <c r="B89" s="150" t="s">
         <v>346</v>
@@ -18388,7 +18388,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="90" spans="1:22" s="141" customFormat="1" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:22" s="141" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="142"/>
       <c r="B90" s="150" t="s">
         <v>349</v>
@@ -18454,7 +18454,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="91" spans="1:22" s="141" customFormat="1" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:22" s="141" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="142"/>
       <c r="B91" s="312" t="s">
         <v>352</v>
@@ -18520,7 +18520,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="92" spans="1:22" s="141" customFormat="1" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:22" s="141" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="142"/>
       <c r="B92" s="150" t="s">
         <v>355</v>
@@ -18586,7 +18586,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="93" spans="1:22" s="141" customFormat="1" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:22" s="141" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="142"/>
       <c r="B93" s="150" t="s">
         <v>358</v>
@@ -18652,7 +18652,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="94" spans="1:22" s="141" customFormat="1" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:22" s="141" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="142"/>
       <c r="B94" s="150" t="s">
         <v>361</v>
@@ -18718,7 +18718,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="95" spans="1:22" s="141" customFormat="1" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:22" s="141" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="142"/>
       <c r="B95" s="150" t="s">
         <v>364</v>
@@ -18784,7 +18784,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="96" spans="1:22" s="141" customFormat="1" ht="16.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:22" s="141" customFormat="1" ht="16.350000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A96" s="142"/>
       <c r="B96" s="154" t="s">
         <v>367</v>
@@ -18850,7 +18850,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="97" spans="1:22" ht="13.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:22" ht="13.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="B97" s="159" t="s">
         <v>37</v>
       </c>
@@ -18877,7 +18877,7 @@
       <c r="U97" s="26"/>
       <c r="V97" s="26"/>
     </row>
-    <row r="98" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B98" s="161"/>
       <c r="C98" s="84"/>
       <c r="D98" s="143"/>
@@ -18900,32 +18900,32 @@
       <c r="U98" s="26"/>
       <c r="V98" s="26"/>
     </row>
-    <row r="99" spans="1:22" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B99" s="417" t="s">
+    <row r="99" spans="1:22" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B99" s="345" t="s">
         <v>132</v>
       </c>
-      <c r="C99" s="417"/>
-      <c r="D99" s="417"/>
-      <c r="E99" s="417"/>
-      <c r="F99" s="417"/>
-      <c r="G99" s="417"/>
-      <c r="H99" s="417"/>
-      <c r="I99" s="417"/>
-      <c r="J99" s="417"/>
-      <c r="K99" s="417"/>
-      <c r="L99" s="417"/>
-      <c r="M99" s="417"/>
-      <c r="N99" s="417"/>
-      <c r="O99" s="417"/>
-      <c r="P99" s="417"/>
-      <c r="Q99" s="417"/>
-      <c r="R99" s="417"/>
-      <c r="S99" s="417"/>
-      <c r="T99" s="417"/>
-      <c r="U99" s="417"/>
-      <c r="V99" s="417"/>
-    </row>
-    <row r="100" spans="1:22" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C99" s="345"/>
+      <c r="D99" s="345"/>
+      <c r="E99" s="345"/>
+      <c r="F99" s="345"/>
+      <c r="G99" s="345"/>
+      <c r="H99" s="345"/>
+      <c r="I99" s="345"/>
+      <c r="J99" s="345"/>
+      <c r="K99" s="345"/>
+      <c r="L99" s="345"/>
+      <c r="M99" s="345"/>
+      <c r="N99" s="345"/>
+      <c r="O99" s="345"/>
+      <c r="P99" s="345"/>
+      <c r="Q99" s="345"/>
+      <c r="R99" s="345"/>
+      <c r="S99" s="345"/>
+      <c r="T99" s="345"/>
+      <c r="U99" s="345"/>
+      <c r="V99" s="345"/>
+    </row>
+    <row r="100" spans="1:22" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C100" s="140"/>
       <c r="D100" s="140"/>
       <c r="F100" s="140"/>
@@ -18941,51 +18941,51 @@
       <c r="S100" s="140"/>
       <c r="T100" s="140"/>
     </row>
-    <row r="101" spans="1:22" ht="16.399999999999999" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B101" s="411" t="s">
+    <row r="101" spans="1:22" ht="16.350000000000001" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B101" s="349" t="s">
         <v>133</v>
       </c>
-      <c r="C101" s="413" t="s">
+      <c r="C101" s="351" t="s">
         <v>134</v>
       </c>
-      <c r="D101" s="413" t="s">
+      <c r="D101" s="351" t="s">
         <v>135</v>
       </c>
-      <c r="E101" s="415" t="s">
+      <c r="E101" s="346" t="s">
         <v>115</v>
       </c>
-      <c r="F101" s="416"/>
-      <c r="G101" s="416"/>
-      <c r="H101" s="415" t="s">
+      <c r="F101" s="347"/>
+      <c r="G101" s="347"/>
+      <c r="H101" s="346" t="s">
         <v>116</v>
       </c>
-      <c r="I101" s="416"/>
-      <c r="J101" s="416"/>
-      <c r="K101" s="415" t="s">
+      <c r="I101" s="347"/>
+      <c r="J101" s="347"/>
+      <c r="K101" s="346" t="s">
         <v>117</v>
       </c>
-      <c r="L101" s="416"/>
-      <c r="M101" s="416"/>
-      <c r="N101" s="415" t="s">
+      <c r="L101" s="347"/>
+      <c r="M101" s="347"/>
+      <c r="N101" s="346" t="s">
         <v>118</v>
       </c>
-      <c r="O101" s="416"/>
-      <c r="P101" s="416"/>
-      <c r="Q101" s="415" t="s">
+      <c r="O101" s="347"/>
+      <c r="P101" s="347"/>
+      <c r="Q101" s="346" t="s">
         <v>119</v>
       </c>
-      <c r="R101" s="416"/>
-      <c r="S101" s="416"/>
-      <c r="T101" s="415" t="s">
+      <c r="R101" s="347"/>
+      <c r="S101" s="347"/>
+      <c r="T101" s="346" t="s">
         <v>120</v>
       </c>
-      <c r="U101" s="416"/>
-      <c r="V101" s="418"/>
-    </row>
-    <row r="102" spans="1:22" ht="16.399999999999999" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B102" s="412"/>
-      <c r="C102" s="414"/>
-      <c r="D102" s="414"/>
+      <c r="U101" s="347"/>
+      <c r="V101" s="348"/>
+    </row>
+    <row r="102" spans="1:22" ht="16.350000000000001" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B102" s="350"/>
+      <c r="C102" s="352"/>
+      <c r="D102" s="352"/>
       <c r="E102" s="309" t="s">
         <v>36</v>
       </c>
@@ -19041,7 +19041,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="103" spans="1:22" s="141" customFormat="1" ht="16.399999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:22" s="141" customFormat="1" ht="16.350000000000001" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A103" s="142"/>
       <c r="B103" s="338" t="s">
         <v>370</v>
@@ -19107,7 +19107,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="104" spans="1:22" s="141" customFormat="1" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:22" s="141" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="142"/>
       <c r="B104" s="150" t="s">
         <v>373</v>
@@ -19173,7 +19173,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="105" spans="1:22" s="141" customFormat="1" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:22" s="141" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="142"/>
       <c r="B105" s="150" t="s">
         <v>376</v>
@@ -19239,7 +19239,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="106" spans="1:22" s="141" customFormat="1" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:22" s="141" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="142"/>
       <c r="B106" s="150" t="s">
         <v>379</v>
@@ -19305,7 +19305,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="107" spans="1:22" s="141" customFormat="1" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:22" s="141" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="142"/>
       <c r="B107" s="338" t="s">
         <v>382</v>
@@ -19371,7 +19371,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="108" spans="1:22" s="141" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:22" s="141" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="142"/>
       <c r="B108" s="338" t="s">
         <v>385</v>
@@ -19437,7 +19437,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="109" spans="1:22" s="141" customFormat="1" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:22" s="141" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="142"/>
       <c r="B109" s="338" t="s">
         <v>388</v>
@@ -19503,7 +19503,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="110" spans="1:22" s="141" customFormat="1" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:22" s="141" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="142"/>
       <c r="B110" s="150" t="s">
         <v>391</v>
@@ -19569,7 +19569,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="111" spans="1:22" s="141" customFormat="1" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:22" s="141" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="142"/>
       <c r="B111" s="150" t="s">
         <v>394</v>
@@ -19635,7 +19635,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="112" spans="1:22" s="141" customFormat="1" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:22" s="141" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="142"/>
       <c r="B112" s="312" t="s">
         <v>397</v>
@@ -19701,7 +19701,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="113" spans="1:22" s="141" customFormat="1" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:22" s="141" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="142"/>
       <c r="B113" s="150" t="s">
         <v>400</v>
@@ -19767,7 +19767,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="114" spans="1:22" s="141" customFormat="1" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:22" s="141" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="142"/>
       <c r="B114" s="150" t="s">
         <v>403</v>
@@ -19833,7 +19833,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="115" spans="1:22" s="141" customFormat="1" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:22" s="141" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="142"/>
       <c r="B115" s="150" t="s">
         <v>406</v>
@@ -19899,7 +19899,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="116" spans="1:22" s="141" customFormat="1" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:22" s="141" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="142"/>
       <c r="B116" s="150" t="s">
         <v>409</v>
@@ -19965,7 +19965,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="117" spans="1:22" s="141" customFormat="1" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:22" s="141" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="142"/>
       <c r="B117" s="338" t="s">
         <v>412</v>
@@ -20031,7 +20031,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:22" s="141" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:22" s="141" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="142"/>
       <c r="B118" s="338" t="s">
         <v>415</v>
@@ -20097,7 +20097,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:22" s="141" customFormat="1" ht="26.15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:22" s="141" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="142"/>
       <c r="B119" s="338" t="s">
         <v>418</v>
@@ -20163,7 +20163,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="120" spans="1:22" s="141" customFormat="1" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:22" s="141" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="142"/>
       <c r="B120" s="338" t="s">
         <v>421</v>
@@ -20229,7 +20229,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="121" spans="1:22" s="141" customFormat="1" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:22" s="141" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="142"/>
       <c r="B121" s="150" t="s">
         <v>424</v>
@@ -20295,7 +20295,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="122" spans="1:22" s="141" customFormat="1" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:22" s="141" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="142"/>
       <c r="B122" s="150" t="s">
         <v>427</v>
@@ -20361,7 +20361,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="123" spans="1:22" s="141" customFormat="1" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:22" s="141" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="142"/>
       <c r="B123" s="150" t="s">
         <v>430</v>
@@ -20427,7 +20427,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="124" spans="1:22" s="141" customFormat="1" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:22" s="141" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="142"/>
       <c r="B124" s="150" t="s">
         <v>433</v>
@@ -20493,7 +20493,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="125" spans="1:22" s="141" customFormat="1" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:22" s="141" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="142"/>
       <c r="B125" s="150" t="s">
         <v>436</v>
@@ -20559,7 +20559,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="126" spans="1:22" s="141" customFormat="1" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:22" s="141" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="142"/>
       <c r="B126" s="150" t="s">
         <v>439</v>
@@ -20625,7 +20625,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="127" spans="1:22" s="141" customFormat="1" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:22" s="141" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="142"/>
       <c r="B127" s="150" t="s">
         <v>442</v>
@@ -20691,7 +20691,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="128" spans="1:22" s="141" customFormat="1" ht="28.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:22" s="141" customFormat="1" ht="28.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A128" s="142"/>
       <c r="B128" s="154" t="s">
         <v>445</v>
@@ -20757,7 +20757,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="129" spans="2:22" ht="13.5" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="2:22" ht="13.5" thickTop="1" x14ac:dyDescent="0.2">
       <c r="B129" s="159" t="s">
         <v>37</v>
       </c>
@@ -20784,7 +20784,7 @@
       <c r="U129" s="26"/>
       <c r="V129" s="26"/>
     </row>
-    <row r="130" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="130" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B130" s="144"/>
       <c r="C130" s="35" t="s">
         <v>448</v>
@@ -20809,12 +20809,36 @@
       <c r="U130" s="26"/>
       <c r="V130" s="26"/>
     </row>
-    <row r="132" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="132" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C132" s="60"/>
     </row>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="gZU9Zr/RUYPWhH7sHE7va9HqJx3QsiMPfm80bvOEQmGuntXGj2h4sf2vQiv/74IFzb2wotUMOhm8RB8wzxH+nA==" saltValue="wOZ7jpKpqbM3NM+gYMrs2g==" spinCount="100000" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <mergeCells count="40">
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="C68:C69"/>
+    <mergeCell ref="D68:D69"/>
+    <mergeCell ref="E68:G68"/>
+    <mergeCell ref="B101:B102"/>
+    <mergeCell ref="C101:C102"/>
+    <mergeCell ref="D101:D102"/>
+    <mergeCell ref="E101:G101"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:G3"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="E36:G36"/>
+    <mergeCell ref="H3:J3"/>
+    <mergeCell ref="K3:M3"/>
+    <mergeCell ref="K101:M101"/>
+    <mergeCell ref="K68:M68"/>
+    <mergeCell ref="H36:J36"/>
+    <mergeCell ref="K36:M36"/>
+    <mergeCell ref="H101:J101"/>
+    <mergeCell ref="H68:J68"/>
     <mergeCell ref="B1:V1"/>
     <mergeCell ref="B34:V34"/>
     <mergeCell ref="B66:V66"/>
@@ -20831,30 +20855,6 @@
     <mergeCell ref="N36:P36"/>
     <mergeCell ref="Q36:S36"/>
     <mergeCell ref="T36:V36"/>
-    <mergeCell ref="H3:J3"/>
-    <mergeCell ref="K3:M3"/>
-    <mergeCell ref="K101:M101"/>
-    <mergeCell ref="K68:M68"/>
-    <mergeCell ref="H36:J36"/>
-    <mergeCell ref="K36:M36"/>
-    <mergeCell ref="H101:J101"/>
-    <mergeCell ref="H68:J68"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="E3:G3"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="C36:C37"/>
-    <mergeCell ref="D36:D37"/>
-    <mergeCell ref="E36:G36"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="C68:C69"/>
-    <mergeCell ref="D68:D69"/>
-    <mergeCell ref="E68:G68"/>
-    <mergeCell ref="B101:B102"/>
-    <mergeCell ref="C101:C102"/>
-    <mergeCell ref="D101:D102"/>
-    <mergeCell ref="E101:G101"/>
   </mergeCells>
   <phoneticPr fontId="38" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -20872,58 +20872,58 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C870864-4422-4181-BFCD-572DB7D75AE4}">
   <dimension ref="A1:Q21"/>
-  <sheetFormatPr defaultColWidth="9.296875" defaultRowHeight="18" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="18.75" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.296875" style="6" customWidth="1"/>
+    <col min="1" max="1" width="6.33203125" style="6" customWidth="1"/>
     <col min="2" max="2" width="11" style="5" customWidth="1"/>
-    <col min="3" max="16384" width="9.296875" style="5"/>
+    <col min="3" max="16384" width="9.33203125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A1" s="346" t="s">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A1" s="354" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="346"/>
-      <c r="C1" s="346"/>
-      <c r="D1" s="346"/>
-      <c r="E1" s="346"/>
-      <c r="F1" s="346"/>
-      <c r="G1" s="346"/>
-      <c r="H1" s="346"/>
-      <c r="I1" s="346"/>
-      <c r="J1" s="346"/>
-      <c r="K1" s="346"/>
-      <c r="L1" s="346"/>
-      <c r="M1" s="346"/>
-      <c r="N1" s="346"/>
-      <c r="O1" s="346"/>
-      <c r="P1" s="346"/>
-      <c r="Q1" s="346"/>
-    </row>
-    <row r="3" spans="1:17" ht="41.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B1" s="354"/>
+      <c r="C1" s="354"/>
+      <c r="D1" s="354"/>
+      <c r="E1" s="354"/>
+      <c r="F1" s="354"/>
+      <c r="G1" s="354"/>
+      <c r="H1" s="354"/>
+      <c r="I1" s="354"/>
+      <c r="J1" s="354"/>
+      <c r="K1" s="354"/>
+      <c r="L1" s="354"/>
+      <c r="M1" s="354"/>
+      <c r="N1" s="354"/>
+      <c r="O1" s="354"/>
+      <c r="P1" s="354"/>
+      <c r="Q1" s="354"/>
+    </row>
+    <row r="3" spans="1:17" ht="41.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6">
         <v>1</v>
       </c>
-      <c r="B3" s="345" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="345"/>
-      <c r="D3" s="345"/>
-      <c r="E3" s="345"/>
-      <c r="F3" s="345"/>
-      <c r="G3" s="345"/>
-      <c r="H3" s="345"/>
-      <c r="I3" s="345"/>
-      <c r="J3" s="345"/>
-      <c r="K3" s="345"/>
-      <c r="L3" s="345"/>
-      <c r="M3" s="345"/>
-      <c r="N3" s="345"/>
-      <c r="O3" s="345"/>
-      <c r="P3" s="345"/>
-      <c r="Q3" s="345"/>
-    </row>
-    <row r="4" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B3" s="353" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="353"/>
+      <c r="D3" s="353"/>
+      <c r="E3" s="353"/>
+      <c r="F3" s="353"/>
+      <c r="G3" s="353"/>
+      <c r="H3" s="353"/>
+      <c r="I3" s="353"/>
+      <c r="J3" s="353"/>
+      <c r="K3" s="353"/>
+      <c r="L3" s="353"/>
+      <c r="M3" s="353"/>
+      <c r="N3" s="353"/>
+      <c r="O3" s="353"/>
+      <c r="P3" s="353"/>
+      <c r="Q3" s="353"/>
+    </row>
+    <row r="4" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
       <c r="D4" s="7"/>
@@ -20941,53 +20941,53 @@
       <c r="P4" s="7"/>
       <c r="Q4" s="7"/>
     </row>
-    <row r="5" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="6">
         <v>2</v>
       </c>
-      <c r="B5" s="345" t="s">
+      <c r="B5" s="353" t="s">
         <v>459</v>
       </c>
-      <c r="C5" s="345"/>
-      <c r="D5" s="345"/>
-      <c r="E5" s="345"/>
-      <c r="F5" s="345"/>
-      <c r="G5" s="345"/>
-      <c r="H5" s="345"/>
-      <c r="I5" s="345"/>
-      <c r="J5" s="345"/>
-      <c r="K5" s="345"/>
-      <c r="L5" s="345"/>
-      <c r="M5" s="345"/>
-      <c r="N5" s="345"/>
-      <c r="O5" s="345"/>
-      <c r="P5" s="345"/>
-      <c r="Q5" s="345"/>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="C5" s="353"/>
+      <c r="D5" s="353"/>
+      <c r="E5" s="353"/>
+      <c r="F5" s="353"/>
+      <c r="G5" s="353"/>
+      <c r="H5" s="353"/>
+      <c r="I5" s="353"/>
+      <c r="J5" s="353"/>
+      <c r="K5" s="353"/>
+      <c r="L5" s="353"/>
+      <c r="M5" s="353"/>
+      <c r="N5" s="353"/>
+      <c r="O5" s="353"/>
+      <c r="P5" s="353"/>
+      <c r="Q5" s="353"/>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" s="6">
         <v>3</v>
       </c>
-      <c r="B7" s="345" t="s">
+      <c r="B7" s="353" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="345"/>
-      <c r="D7" s="345"/>
-      <c r="E7" s="345"/>
-      <c r="F7" s="345"/>
-      <c r="G7" s="345"/>
-      <c r="H7" s="345"/>
-      <c r="I7" s="345"/>
-      <c r="J7" s="345"/>
-      <c r="K7" s="345"/>
-      <c r="L7" s="345"/>
-      <c r="M7" s="345"/>
-      <c r="N7" s="345"/>
-      <c r="O7" s="345"/>
-      <c r="P7" s="345"/>
-      <c r="Q7" s="345"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="C7" s="353"/>
+      <c r="D7" s="353"/>
+      <c r="E7" s="353"/>
+      <c r="F7" s="353"/>
+      <c r="G7" s="353"/>
+      <c r="H7" s="353"/>
+      <c r="I7" s="353"/>
+      <c r="J7" s="353"/>
+      <c r="K7" s="353"/>
+      <c r="L7" s="353"/>
+      <c r="M7" s="353"/>
+      <c r="N7" s="353"/>
+      <c r="O7" s="353"/>
+      <c r="P7" s="353"/>
+      <c r="Q7" s="353"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
@@ -21005,30 +21005,30 @@
       <c r="P8" s="7"/>
       <c r="Q8" s="7"/>
     </row>
-    <row r="9" spans="1:17" ht="60" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:17" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="6">
         <v>4</v>
       </c>
-      <c r="B9" s="345" t="s">
+      <c r="B9" s="353" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="345"/>
-      <c r="D9" s="345"/>
-      <c r="E9" s="345"/>
-      <c r="F9" s="345"/>
-      <c r="G9" s="345"/>
-      <c r="H9" s="345"/>
-      <c r="I9" s="345"/>
-      <c r="J9" s="345"/>
-      <c r="K9" s="345"/>
-      <c r="L9" s="345"/>
-      <c r="M9" s="345"/>
-      <c r="N9" s="345"/>
-      <c r="O9" s="345"/>
-      <c r="P9" s="345"/>
-      <c r="Q9" s="345"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="C9" s="353"/>
+      <c r="D9" s="353"/>
+      <c r="E9" s="353"/>
+      <c r="F9" s="353"/>
+      <c r="G9" s="353"/>
+      <c r="H9" s="353"/>
+      <c r="I9" s="353"/>
+      <c r="J9" s="353"/>
+      <c r="K9" s="353"/>
+      <c r="L9" s="353"/>
+      <c r="M9" s="353"/>
+      <c r="N9" s="353"/>
+      <c r="O9" s="353"/>
+      <c r="P9" s="353"/>
+      <c r="Q9" s="353"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
       <c r="E10" s="7"/>
@@ -21045,80 +21045,80 @@
       <c r="P10" s="7"/>
       <c r="Q10" s="7"/>
     </row>
-    <row r="11" spans="1:17" ht="60" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:17" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="6">
         <v>5</v>
       </c>
-      <c r="B11" s="345" t="s">
+      <c r="B11" s="353" t="s">
         <v>460</v>
       </c>
-      <c r="C11" s="345" t="s">
+      <c r="C11" s="353" t="s">
         <v>5</v>
       </c>
-      <c r="D11" s="345"/>
-      <c r="E11" s="345"/>
-      <c r="F11" s="345"/>
-      <c r="G11" s="345"/>
-      <c r="H11" s="345"/>
-      <c r="I11" s="345"/>
-      <c r="J11" s="345"/>
-      <c r="K11" s="345"/>
-      <c r="L11" s="345"/>
-      <c r="M11" s="345"/>
-      <c r="N11" s="345"/>
-      <c r="O11" s="345"/>
-      <c r="P11" s="345"/>
-      <c r="Q11" s="345"/>
-    </row>
-    <row r="13" spans="1:17" ht="41.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="D11" s="353"/>
+      <c r="E11" s="353"/>
+      <c r="F11" s="353"/>
+      <c r="G11" s="353"/>
+      <c r="H11" s="353"/>
+      <c r="I11" s="353"/>
+      <c r="J11" s="353"/>
+      <c r="K11" s="353"/>
+      <c r="L11" s="353"/>
+      <c r="M11" s="353"/>
+      <c r="N11" s="353"/>
+      <c r="O11" s="353"/>
+      <c r="P11" s="353"/>
+      <c r="Q11" s="353"/>
+    </row>
+    <row r="13" spans="1:17" ht="41.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="6">
         <v>6</v>
       </c>
-      <c r="B13" s="345" t="s">
+      <c r="B13" s="353" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="345"/>
-      <c r="D13" s="345"/>
-      <c r="E13" s="345"/>
-      <c r="F13" s="345"/>
-      <c r="G13" s="345"/>
-      <c r="H13" s="345"/>
-      <c r="I13" s="345"/>
-      <c r="J13" s="345"/>
-      <c r="K13" s="345"/>
-      <c r="L13" s="345"/>
-      <c r="M13" s="345"/>
-      <c r="N13" s="345"/>
-      <c r="O13" s="345"/>
-      <c r="P13" s="345"/>
-      <c r="Q13" s="345"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="C13" s="353"/>
+      <c r="D13" s="353"/>
+      <c r="E13" s="353"/>
+      <c r="F13" s="353"/>
+      <c r="G13" s="353"/>
+      <c r="H13" s="353"/>
+      <c r="I13" s="353"/>
+      <c r="J13" s="353"/>
+      <c r="K13" s="353"/>
+      <c r="L13" s="353"/>
+      <c r="M13" s="353"/>
+      <c r="N13" s="353"/>
+      <c r="O13" s="353"/>
+      <c r="P13" s="353"/>
+      <c r="Q13" s="353"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15" s="5"/>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" s="5"/>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="5"/>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="5"/>
       <c r="B18" s="5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B19" s="5" t="s">
         <v>458</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B20" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B21" s="5" t="s">
         <v>8</v>
       </c>
@@ -21143,24 +21143,24 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AA71A74-9F27-4552-A39D-CA0C263A5AA9}">
   <dimension ref="A1:L37"/>
-  <sheetFormatPr defaultColWidth="9.796875" defaultRowHeight="13" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.83203125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="3.296875" style="8" customWidth="1"/>
-    <col min="2" max="2" width="9.796875" style="1"/>
-    <col min="3" max="3" width="3.796875" style="8" customWidth="1"/>
-    <col min="4" max="4" width="108.69921875" style="8" customWidth="1"/>
-    <col min="5" max="10" width="13.296875" style="8" customWidth="1"/>
-    <col min="11" max="11" width="5.796875" style="8" customWidth="1"/>
-    <col min="12" max="16384" width="9.796875" style="8"/>
+    <col min="1" max="1" width="3.33203125" style="8" customWidth="1"/>
+    <col min="2" max="2" width="9.83203125" style="1"/>
+    <col min="3" max="3" width="3.83203125" style="8" customWidth="1"/>
+    <col min="4" max="4" width="108.6640625" style="8" customWidth="1"/>
+    <col min="5" max="10" width="13.33203125" style="8" customWidth="1"/>
+    <col min="11" max="11" width="5.83203125" style="8" customWidth="1"/>
+    <col min="12" max="16384" width="9.83203125" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="9"/>
-      <c r="B1" s="346" t="s">
+      <c r="B1" s="354" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="346"/>
-      <c r="D1" s="346"/>
+      <c r="C1" s="354"/>
+      <c r="D1" s="354"/>
       <c r="E1" s="9"/>
       <c r="F1" s="10"/>
       <c r="G1" s="10"/>
@@ -21170,7 +21170,7 @@
       <c r="K1" s="11"/>
       <c r="L1" s="11"/>
     </row>
-    <row r="2" spans="1:12" ht="14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A2" s="12"/>
       <c r="B2" s="162"/>
       <c r="C2" s="12"/>
@@ -21182,13 +21182,13 @@
       <c r="I2" s="12"/>
       <c r="J2" s="12"/>
     </row>
-    <row r="3" spans="1:12" ht="14" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A3" s="12"/>
-      <c r="B3" s="347" t="s">
+      <c r="B3" s="355" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="347"/>
-      <c r="D3" s="347"/>
+      <c r="C3" s="355"/>
+      <c r="D3" s="355"/>
       <c r="E3" s="13"/>
       <c r="F3" s="13"/>
       <c r="G3" s="13"/>
@@ -21196,7 +21196,7 @@
       <c r="I3" s="12"/>
       <c r="J3" s="12"/>
     </row>
-    <row r="4" spans="1:12" ht="14" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A4" s="14"/>
       <c r="B4" s="163"/>
       <c r="C4" s="14"/>
@@ -21208,7 +21208,7 @@
       <c r="I4" s="14"/>
       <c r="J4" s="14"/>
     </row>
-    <row r="5" spans="1:12" ht="14" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A5" s="14"/>
       <c r="B5" s="162" t="s">
         <v>11</v>
@@ -21226,7 +21226,7 @@
       <c r="I5" s="12"/>
       <c r="J5" s="12"/>
     </row>
-    <row r="7" spans="1:12" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="164">
         <v>1</v>
       </c>
@@ -21234,10 +21234,10 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="4.4000000000000004" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" ht="4.3499999999999996" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B8" s="164"/>
     </row>
-    <row r="9" spans="1:12" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B9" s="164">
         <v>2</v>
       </c>
@@ -21245,10 +21245,10 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="4.4000000000000004" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" ht="4.3499999999999996" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" s="164"/>
     </row>
-    <row r="11" spans="1:12" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B11" s="164">
         <v>3</v>
       </c>
@@ -21256,10 +21256,10 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="4.4000000000000004" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" ht="4.3499999999999996" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B12" s="164"/>
     </row>
-    <row r="13" spans="1:12" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B13" s="164">
         <v>4</v>
       </c>
@@ -21267,10 +21267,10 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="4.4000000000000004" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" ht="4.3499999999999996" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B14" s="164"/>
     </row>
-    <row r="15" spans="1:12" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B15" s="164">
         <v>5</v>
       </c>
@@ -21278,10 +21278,10 @@
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="4.4000000000000004" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" ht="4.3499999999999996" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="164"/>
     </row>
-    <row r="17" spans="2:5" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:5" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B17" s="164">
         <v>6</v>
       </c>
@@ -21289,10 +21289,10 @@
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="2:5" ht="4.4000000000000004" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:5" ht="4.3499999999999996" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B18" s="164"/>
     </row>
-    <row r="19" spans="2:5" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:5" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B19" s="164">
         <v>7</v>
       </c>
@@ -21300,10 +21300,10 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="2:5" ht="4.4000000000000004" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:5" ht="4.3499999999999996" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B20" s="164"/>
     </row>
-    <row r="21" spans="2:5" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:5" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B21" s="164">
         <v>8</v>
       </c>
@@ -21311,21 +21311,21 @@
         <v>21</v>
       </c>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B22" s="164"/>
     </row>
-    <row r="23" spans="2:5" ht="14" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:5" ht="14.25" x14ac:dyDescent="0.2">
       <c r="B23" s="164"/>
       <c r="D23" s="15" t="s">
         <v>22</v>
       </c>
       <c r="E23" s="18"/>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B24" s="164"/>
       <c r="D24" s="19"/>
     </row>
-    <row r="25" spans="2:5" ht="26" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:5" ht="25.5" x14ac:dyDescent="0.2">
       <c r="B25" s="164">
         <v>9</v>
       </c>
@@ -21333,11 +21333,11 @@
         <v>454</v>
       </c>
     </row>
-    <row r="26" spans="2:5" ht="4.4000000000000004" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:5" ht="4.3499999999999996" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B26" s="164"/>
       <c r="D26" s="19"/>
     </row>
-    <row r="27" spans="2:5" ht="26" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:5" ht="25.5" x14ac:dyDescent="0.2">
       <c r="B27" s="164">
         <v>10</v>
       </c>
@@ -21345,11 +21345,11 @@
         <v>455</v>
       </c>
     </row>
-    <row r="28" spans="2:5" ht="4.4000000000000004" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:5" ht="4.3499999999999996" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B28" s="164"/>
       <c r="D28" s="19"/>
     </row>
-    <row r="29" spans="2:5" ht="26" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:5" ht="25.5" x14ac:dyDescent="0.2">
       <c r="B29" s="164">
         <v>11</v>
       </c>
@@ -21357,20 +21357,20 @@
         <v>456</v>
       </c>
     </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B30" s="164"/>
     </row>
-    <row r="31" spans="2:5" ht="14" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:5" ht="14.25" x14ac:dyDescent="0.2">
       <c r="B31" s="164"/>
       <c r="D31" s="15" t="s">
         <v>23</v>
       </c>
       <c r="E31" s="18"/>
     </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B32" s="164"/>
     </row>
-    <row r="33" spans="2:4" ht="26" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:4" ht="25.5" x14ac:dyDescent="0.2">
       <c r="B33" s="164">
         <v>12</v>
       </c>
@@ -21378,11 +21378,11 @@
         <v>457</v>
       </c>
     </row>
-    <row r="34" spans="2:4" ht="4.4000000000000004" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:4" ht="4.3499999999999996" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B34" s="164"/>
       <c r="D34" s="17"/>
     </row>
-    <row r="35" spans="2:4" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:4" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B35" s="164">
         <v>13</v>
       </c>
@@ -21390,11 +21390,11 @@
         <v>24</v>
       </c>
     </row>
-    <row r="36" spans="2:4" ht="4.4000000000000004" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:4" ht="4.3499999999999996" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B36" s="164"/>
       <c r="D36" s="17"/>
     </row>
-    <row r="37" spans="2:4" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:4" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B37" s="164">
         <v>14</v>
       </c>
@@ -21435,23 +21435,23 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF5906AB-2BEC-477D-9FDA-AC9698923BD9}">
   <dimension ref="A1:HT29"/>
-  <sheetFormatPr defaultColWidth="5.796875" defaultRowHeight="13" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="5.83203125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="4.296875" style="21" customWidth="1"/>
-    <col min="2" max="2" width="6.296875" style="21" customWidth="1"/>
-    <col min="3" max="3" width="8.796875" style="21" customWidth="1"/>
-    <col min="4" max="4" width="6.296875" style="21" customWidth="1"/>
-    <col min="5" max="10" width="13.796875" style="21" customWidth="1"/>
-    <col min="11" max="11" width="9.796875" style="21" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.19921875" style="21" customWidth="1"/>
-    <col min="13" max="13" width="7.296875" style="21" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.796875" style="21" customWidth="1"/>
-    <col min="15" max="24" width="5.796875" style="21"/>
-    <col min="25" max="25" width="8.796875" style="21" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="5.796875" style="21"/>
+    <col min="1" max="1" width="4.33203125" style="21" customWidth="1"/>
+    <col min="2" max="2" width="6.33203125" style="21" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" style="21" customWidth="1"/>
+    <col min="4" max="4" width="6.33203125" style="21" customWidth="1"/>
+    <col min="5" max="10" width="13.83203125" style="21" customWidth="1"/>
+    <col min="11" max="11" width="9.83203125" style="21" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.1640625" style="21" customWidth="1"/>
+    <col min="13" max="13" width="7.33203125" style="21" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.83203125" style="21" customWidth="1"/>
+    <col min="15" max="24" width="5.83203125" style="21"/>
+    <col min="25" max="25" width="8.83203125" style="21" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="5.83203125" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:228" ht="32.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:228" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1" s="20" t="s">
         <v>26</v>
       </c>
@@ -21464,7 +21464,7 @@
       <c r="I1" s="24"/>
       <c r="J1" s="173"/>
     </row>
-    <row r="2" spans="1:228" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:228" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="20"/>
       <c r="C2" s="22"/>
       <c r="D2" s="22"/>
@@ -21475,43 +21475,43 @@
       <c r="I2" s="24"/>
       <c r="J2" s="173"/>
     </row>
-    <row r="3" spans="1:228" ht="13.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="367" t="s">
+    <row r="3" spans="1:228" ht="13.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="B3" s="362" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="367"/>
-      <c r="D3" s="368"/>
-      <c r="E3" s="359" t="s">
+      <c r="C3" s="362"/>
+      <c r="D3" s="363"/>
+      <c r="E3" s="372" t="s">
         <v>22</v>
       </c>
-      <c r="F3" s="359" t="s">
+      <c r="F3" s="372" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="359" t="s">
+      <c r="G3" s="372" t="s">
         <v>28</v>
       </c>
-      <c r="H3" s="359" t="s">
+      <c r="H3" s="372" t="s">
         <v>29</v>
       </c>
-      <c r="I3" s="359" t="s">
+      <c r="I3" s="372" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="348" t="s">
+      <c r="J3" s="374" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:228" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="369"/>
-      <c r="C4" s="369"/>
-      <c r="D4" s="370"/>
-      <c r="E4" s="360"/>
-      <c r="F4" s="360"/>
-      <c r="G4" s="360"/>
-      <c r="H4" s="360"/>
-      <c r="I4" s="360"/>
-      <c r="J4" s="349"/>
-    </row>
-    <row r="5" spans="1:228" s="174" customFormat="1" ht="23.15" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:228" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="364"/>
+      <c r="C4" s="364"/>
+      <c r="D4" s="365"/>
+      <c r="E4" s="373"/>
+      <c r="F4" s="373"/>
+      <c r="G4" s="373"/>
+      <c r="H4" s="373"/>
+      <c r="I4" s="373"/>
+      <c r="J4" s="375"/>
+    </row>
+    <row r="5" spans="1:228" s="174" customFormat="1" ht="23.1" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A5" s="196"/>
       <c r="B5" s="197"/>
       <c r="C5" s="176" t="s">
@@ -21538,7 +21538,7 @@
       </c>
       <c r="S5" s="182"/>
     </row>
-    <row r="6" spans="1:228" s="174" customFormat="1" ht="23.15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:228" s="174" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="196"/>
       <c r="B6" s="197"/>
       <c r="C6" s="176" t="s">
@@ -21565,7 +21565,7 @@
       </c>
       <c r="S6" s="182"/>
     </row>
-    <row r="7" spans="1:228" s="174" customFormat="1" ht="23.15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:228" s="174" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="196"/>
       <c r="B7" s="197"/>
       <c r="C7" s="176" t="s">
@@ -21592,7 +21592,7 @@
       </c>
       <c r="S7" s="182"/>
     </row>
-    <row r="8" spans="1:228" s="174" customFormat="1" ht="23.15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:228" s="174" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="202"/>
       <c r="B8" s="197"/>
       <c r="C8" s="176" t="s">
@@ -21618,7 +21618,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:228" s="174" customFormat="1" ht="23.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:228" s="174" customFormat="1" ht="23.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B9" s="203"/>
       <c r="C9" s="204" t="s">
         <v>36</v>
@@ -21644,7 +21644,7 @@
       </c>
       <c r="V9" s="182"/>
     </row>
-    <row r="10" spans="1:228" ht="13.5" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:228" ht="13.5" thickTop="1" x14ac:dyDescent="0.2">
       <c r="B10" s="35" t="s">
         <v>37</v>
       </c>
@@ -21661,7 +21661,7 @@
       <c r="K10" s="165"/>
       <c r="V10" s="165"/>
     </row>
-    <row r="11" spans="1:228" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:228" x14ac:dyDescent="0.2">
       <c r="A11" s="30"/>
       <c r="B11" s="35"/>
       <c r="C11" s="36" t="s">
@@ -21885,7 +21885,7 @@
       <c r="HS11" s="30"/>
       <c r="HT11" s="25"/>
     </row>
-    <row r="12" spans="1:228" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:228" x14ac:dyDescent="0.2">
       <c r="A12" s="30"/>
       <c r="C12" s="36" t="s">
         <v>40</v>
@@ -22107,18 +22107,18 @@
       <c r="HS12" s="30"/>
       <c r="HT12" s="25"/>
     </row>
-    <row r="13" spans="1:228" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:228" x14ac:dyDescent="0.2">
       <c r="I13" s="26"/>
       <c r="J13" s="26"/>
       <c r="V13" s="165"/>
     </row>
-    <row r="14" spans="1:228" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:228" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C14" s="28"/>
       <c r="D14" s="28"/>
       <c r="I14" s="26"/>
       <c r="J14" s="26"/>
     </row>
-    <row r="15" spans="1:228" ht="33" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:228" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B15" s="20" t="s">
         <v>41</v>
       </c>
@@ -22134,7 +22134,7 @@
       <c r="V15" s="165"/>
       <c r="Y15" s="165"/>
     </row>
-    <row r="16" spans="1:228" ht="13.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:228" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B16" s="32"/>
       <c r="C16" s="33"/>
       <c r="D16" s="33"/>
@@ -22148,22 +22148,22 @@
       <c r="V16" s="165"/>
       <c r="Y16" s="165"/>
     </row>
-    <row r="17" spans="1:25" ht="13.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="350" t="s">
+    <row r="17" spans="1:25" ht="13.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="B17" s="366" t="s">
         <v>27</v>
       </c>
-      <c r="C17" s="350"/>
-      <c r="D17" s="371"/>
-      <c r="E17" s="350" t="s">
+      <c r="C17" s="366"/>
+      <c r="D17" s="367"/>
+      <c r="E17" s="366" t="s">
         <v>42</v>
       </c>
-      <c r="F17" s="353" t="s">
+      <c r="F17" s="377" t="s">
         <v>43</v>
       </c>
-      <c r="G17" s="356" t="s">
+      <c r="G17" s="380" t="s">
         <v>44</v>
       </c>
-      <c r="H17" s="353" t="s">
+      <c r="H17" s="377" t="s">
         <v>45</v>
       </c>
       <c r="I17" s="26"/>
@@ -22172,69 +22172,69 @@
       <c r="V17" s="165"/>
       <c r="Y17" s="165"/>
     </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="B18" s="351"/>
-      <c r="C18" s="351"/>
-      <c r="D18" s="372"/>
-      <c r="E18" s="351"/>
-      <c r="F18" s="354"/>
-      <c r="G18" s="357"/>
-      <c r="H18" s="354"/>
+    <row r="18" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="B18" s="368"/>
+      <c r="C18" s="368"/>
+      <c r="D18" s="369"/>
+      <c r="E18" s="368"/>
+      <c r="F18" s="378"/>
+      <c r="G18" s="381"/>
+      <c r="H18" s="378"/>
       <c r="I18" s="26"/>
       <c r="J18" s="26"/>
       <c r="K18" s="165"/>
       <c r="V18" s="165"/>
       <c r="Y18" s="165"/>
     </row>
-    <row r="19" spans="1:25" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="351"/>
-      <c r="C19" s="351"/>
-      <c r="D19" s="372"/>
-      <c r="E19" s="352"/>
-      <c r="F19" s="355"/>
-      <c r="G19" s="358"/>
-      <c r="H19" s="355"/>
+    <row r="19" spans="1:25" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B19" s="368"/>
+      <c r="C19" s="368"/>
+      <c r="D19" s="369"/>
+      <c r="E19" s="376"/>
+      <c r="F19" s="379"/>
+      <c r="G19" s="382"/>
+      <c r="H19" s="379"/>
       <c r="I19" s="26"/>
       <c r="J19" s="26"/>
       <c r="K19" s="165"/>
       <c r="V19" s="165"/>
       <c r="Y19" s="165"/>
     </row>
-    <row r="20" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="351"/>
-      <c r="C20" s="351"/>
-      <c r="D20" s="372"/>
-      <c r="E20" s="361" t="s">
+    <row r="20" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B20" s="368"/>
+      <c r="C20" s="368"/>
+      <c r="D20" s="369"/>
+      <c r="E20" s="356" t="s">
         <v>46</v>
       </c>
-      <c r="F20" s="361"/>
-      <c r="G20" s="364" t="s">
+      <c r="F20" s="356"/>
+      <c r="G20" s="359" t="s">
         <v>47</v>
       </c>
-      <c r="H20" s="361"/>
+      <c r="H20" s="356"/>
       <c r="I20" s="26"/>
       <c r="J20" s="26"/>
       <c r="V20" s="165"/>
     </row>
-    <row r="21" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="351"/>
-      <c r="C21" s="351"/>
-      <c r="D21" s="372"/>
-      <c r="E21" s="362"/>
-      <c r="F21" s="362"/>
-      <c r="G21" s="365"/>
-      <c r="H21" s="362"/>
-    </row>
-    <row r="22" spans="1:25" ht="13.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="373"/>
-      <c r="C22" s="373"/>
-      <c r="D22" s="374"/>
-      <c r="E22" s="363"/>
-      <c r="F22" s="363"/>
-      <c r="G22" s="366"/>
-      <c r="H22" s="363"/>
-    </row>
-    <row r="23" spans="1:25" s="174" customFormat="1" ht="23.15" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B21" s="368"/>
+      <c r="C21" s="368"/>
+      <c r="D21" s="369"/>
+      <c r="E21" s="357"/>
+      <c r="F21" s="357"/>
+      <c r="G21" s="360"/>
+      <c r="H21" s="357"/>
+    </row>
+    <row r="22" spans="1:25" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="370"/>
+      <c r="C22" s="370"/>
+      <c r="D22" s="371"/>
+      <c r="E22" s="358"/>
+      <c r="F22" s="358"/>
+      <c r="G22" s="361"/>
+      <c r="H22" s="358"/>
+    </row>
+    <row r="23" spans="1:25" s="174" customFormat="1" ht="23.1" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="B23" s="175"/>
       <c r="C23" s="176" t="s">
         <v>32</v>
@@ -22254,7 +22254,7 @@
       </c>
       <c r="I23" s="180"/>
     </row>
-    <row r="24" spans="1:25" s="174" customFormat="1" ht="23.15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:25" s="174" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B24" s="175"/>
       <c r="C24" s="176" t="s">
         <v>33</v>
@@ -22276,7 +22276,7 @@
       <c r="Q24" s="182"/>
       <c r="S24" s="182"/>
     </row>
-    <row r="25" spans="1:25" s="174" customFormat="1" ht="23.15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:25" s="174" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B25" s="175"/>
       <c r="C25" s="176" t="s">
         <v>34</v>
@@ -22298,7 +22298,7 @@
       <c r="Q25" s="182"/>
       <c r="S25" s="182"/>
     </row>
-    <row r="26" spans="1:25" s="174" customFormat="1" ht="23.15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:25" s="174" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B26" s="175"/>
       <c r="C26" s="176" t="s">
         <v>35</v>
@@ -22319,7 +22319,7 @@
       <c r="I26" s="180"/>
       <c r="M26" s="183"/>
     </row>
-    <row r="27" spans="1:25" s="174" customFormat="1" ht="23.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:25" s="174" customFormat="1" ht="23.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A27" s="184"/>
       <c r="B27" s="185"/>
       <c r="C27" s="186" t="s">
@@ -22341,7 +22341,7 @@
       <c r="I27" s="180"/>
       <c r="M27" s="183"/>
     </row>
-    <row r="28" spans="1:25" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:25" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A28" s="21" t="s">
         <v>12</v>
       </c>
@@ -22358,12 +22358,18 @@
       <c r="H28" s="1"/>
       <c r="M28" s="167"/>
     </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:25" x14ac:dyDescent="0.2">
       <c r="M29" s="167"/>
     </row>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="mkzB4SIhgzq/flgtmmMLKnxkplONCgYq6tlbxeGTAD5BkOb/WxCis9Ci0BgXguMNcfyHWTxwq0OMU9ZGc+kzkQ==" saltValue="rqPc/vKFLElDwJU5f08Kag==" spinCount="100000" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <mergeCells count="14">
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="E17:E19"/>
+    <mergeCell ref="F17:F19"/>
+    <mergeCell ref="G17:G19"/>
+    <mergeCell ref="H17:H19"/>
+    <mergeCell ref="I3:I4"/>
     <mergeCell ref="E20:F22"/>
     <mergeCell ref="G20:H22"/>
     <mergeCell ref="B3:D4"/>
@@ -22372,12 +22378,6 @@
     <mergeCell ref="F3:F4"/>
     <mergeCell ref="G3:G4"/>
     <mergeCell ref="H3:H4"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="E17:E19"/>
-    <mergeCell ref="F17:F19"/>
-    <mergeCell ref="G17:G19"/>
-    <mergeCell ref="H17:H19"/>
-    <mergeCell ref="I3:I4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -22387,25 +22387,25 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84A2A51B-4C15-42CC-BDC7-BC16F4178210}">
   <dimension ref="B1:AL43"/>
-  <sheetFormatPr defaultColWidth="7.796875" defaultRowHeight="13" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="7.83203125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.296875" style="26" customWidth="1"/>
-    <col min="2" max="2" width="2.796875" style="26" customWidth="1"/>
-    <col min="3" max="3" width="6.796875" style="26" customWidth="1"/>
-    <col min="4" max="4" width="11.69921875" style="26" customWidth="1"/>
-    <col min="5" max="7" width="10.19921875" style="26" customWidth="1"/>
-    <col min="8" max="8" width="9.296875" style="26" customWidth="1"/>
-    <col min="9" max="9" width="10.296875" style="26" customWidth="1"/>
-    <col min="10" max="15" width="8.796875" style="26" customWidth="1"/>
-    <col min="16" max="16" width="4.19921875" style="26" customWidth="1"/>
+    <col min="1" max="1" width="2.33203125" style="26" customWidth="1"/>
+    <col min="2" max="2" width="2.83203125" style="26" customWidth="1"/>
+    <col min="3" max="3" width="6.83203125" style="26" customWidth="1"/>
+    <col min="4" max="4" width="11.6640625" style="26" customWidth="1"/>
+    <col min="5" max="7" width="10.1640625" style="26" customWidth="1"/>
+    <col min="8" max="8" width="9.33203125" style="26" customWidth="1"/>
+    <col min="9" max="9" width="10.33203125" style="26" customWidth="1"/>
+    <col min="10" max="15" width="8.83203125" style="26" customWidth="1"/>
+    <col min="16" max="16" width="4.1640625" style="26" customWidth="1"/>
     <col min="17" max="17" width="4" style="26" customWidth="1"/>
-    <col min="18" max="20" width="6.296875" style="26" customWidth="1"/>
-    <col min="21" max="21" width="7.296875" style="26" customWidth="1"/>
-    <col min="22" max="22" width="9.796875" style="42" customWidth="1"/>
-    <col min="23" max="16384" width="7.796875" style="26"/>
+    <col min="18" max="20" width="6.33203125" style="26" customWidth="1"/>
+    <col min="21" max="21" width="7.33203125" style="26" customWidth="1"/>
+    <col min="22" max="22" width="9.83203125" style="42" customWidth="1"/>
+    <col min="23" max="16384" width="7.83203125" style="26"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:22" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1" s="50" t="s">
         <v>48</v>
       </c>
@@ -22428,7 +22428,7 @@
       <c r="T1" s="41"/>
       <c r="U1" s="41"/>
     </row>
-    <row r="2" spans="2:22" ht="13.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:22" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B2" s="43"/>
       <c r="C2" s="43"/>
       <c r="D2" s="43"/>
@@ -22451,12 +22451,12 @@
       <c r="T2" s="41"/>
       <c r="U2" s="41"/>
     </row>
-    <row r="3" spans="2:22" ht="13.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="375" t="s">
+    <row r="3" spans="2:22" ht="13.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="B3" s="383" t="s">
         <v>49</v>
       </c>
-      <c r="C3" s="376"/>
-      <c r="D3" s="377"/>
+      <c r="C3" s="384"/>
+      <c r="D3" s="385"/>
       <c r="E3" s="51" t="s">
         <v>50</v>
       </c>
@@ -22484,10 +22484,10 @@
       <c r="Q3" s="42"/>
       <c r="V3" s="26"/>
     </row>
-    <row r="4" spans="2:22" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="378"/>
-      <c r="C4" s="378"/>
-      <c r="D4" s="379"/>
+    <row r="4" spans="2:22" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="386"/>
+      <c r="C4" s="386"/>
+      <c r="D4" s="387"/>
       <c r="E4" s="53" t="s">
         <v>36</v>
       </c>
@@ -22524,7 +22524,7 @@
       <c r="Q4" s="42"/>
       <c r="V4" s="26"/>
     </row>
-    <row r="5" spans="2:22" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:22" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="B5" s="45"/>
       <c r="C5" s="45"/>
       <c r="D5" s="46"/>
@@ -22542,7 +22542,7 @@
       <c r="Q5" s="42"/>
       <c r="V5" s="26"/>
     </row>
-    <row r="6" spans="2:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="56"/>
       <c r="C6" s="37">
         <v>2025</v>
@@ -22586,7 +22586,7 @@
       <c r="Q6" s="42"/>
       <c r="V6" s="26"/>
     </row>
-    <row r="7" spans="2:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="56"/>
       <c r="C7" s="37"/>
       <c r="D7" s="38" t="s">
@@ -22628,7 +22628,7 @@
       <c r="Q7" s="42"/>
       <c r="V7" s="26"/>
     </row>
-    <row r="8" spans="2:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="56"/>
       <c r="C8" s="37"/>
       <c r="D8" s="37" t="s">
@@ -22670,7 +22670,7 @@
       <c r="Q8" s="42"/>
       <c r="V8" s="26"/>
     </row>
-    <row r="9" spans="2:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="56"/>
       <c r="C9" s="37"/>
       <c r="D9" s="37" t="s">
@@ -22712,7 +22712,7 @@
       <c r="Q9" s="42"/>
       <c r="V9" s="26"/>
     </row>
-    <row r="10" spans="2:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="56"/>
       <c r="C10" s="37"/>
       <c r="D10" s="38" t="s">
@@ -22754,7 +22754,7 @@
       <c r="Q10" s="42"/>
       <c r="V10" s="26"/>
     </row>
-    <row r="11" spans="2:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="56"/>
       <c r="C11" s="37"/>
       <c r="D11" s="37" t="s">
@@ -22796,7 +22796,7 @@
       <c r="Q11" s="42"/>
       <c r="V11" s="26"/>
     </row>
-    <row r="12" spans="2:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="56"/>
       <c r="C12" s="37"/>
       <c r="D12" s="37"/>
@@ -22814,7 +22814,7 @@
       <c r="Q12" s="42"/>
       <c r="V12" s="26"/>
     </row>
-    <row r="13" spans="2:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="56"/>
       <c r="C13" s="57">
         <v>2026</v>
@@ -22858,7 +22858,7 @@
       <c r="Q13" s="42"/>
       <c r="V13" s="26"/>
     </row>
-    <row r="14" spans="2:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="56"/>
       <c r="C14" s="57"/>
       <c r="D14" s="38" t="s">
@@ -22900,7 +22900,7 @@
       <c r="Q14" s="42"/>
       <c r="V14" s="26"/>
     </row>
-    <row r="15" spans="2:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="56"/>
       <c r="C15" s="57"/>
       <c r="D15" s="37" t="s">
@@ -22942,7 +22942,7 @@
       <c r="Q15" s="42"/>
       <c r="V15" s="26"/>
     </row>
-    <row r="16" spans="2:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="56"/>
       <c r="C16" s="57"/>
       <c r="D16" s="37" t="s">
@@ -22984,7 +22984,7 @@
       <c r="Q16" s="42"/>
       <c r="V16" s="26"/>
     </row>
-    <row r="17" spans="2:38" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:38" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="56"/>
       <c r="C17" s="57"/>
       <c r="D17" s="38" t="s">
@@ -23026,7 +23026,7 @@
       <c r="Q17" s="42"/>
       <c r="V17" s="26"/>
     </row>
-    <row r="18" spans="2:38" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:38" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="56"/>
       <c r="C18" s="37"/>
       <c r="D18" s="37" t="s">
@@ -23068,7 +23068,7 @@
       <c r="Q18" s="42"/>
       <c r="V18" s="26"/>
     </row>
-    <row r="19" spans="2:38" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:38" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B19" s="61"/>
       <c r="C19" s="58"/>
       <c r="D19" s="62"/>
@@ -23086,7 +23086,7 @@
       <c r="Q19" s="42"/>
       <c r="V19" s="26"/>
     </row>
-    <row r="20" spans="2:38" ht="6.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:38" ht="6.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="B20" s="43"/>
       <c r="C20" s="43"/>
       <c r="D20" s="43"/>
@@ -23104,14 +23104,14 @@
       <c r="Q20" s="42"/>
       <c r="V20" s="26"/>
     </row>
-    <row r="21" spans="2:38" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:38" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C21" s="60" t="s">
         <v>60</v>
       </c>
       <c r="Q21" s="42"/>
       <c r="V21" s="26"/>
     </row>
-    <row r="22" spans="2:38" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:38" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B22" s="43"/>
       <c r="C22" s="43"/>
       <c r="D22" s="43"/>
@@ -23129,7 +23129,7 @@
       <c r="Q22" s="42"/>
       <c r="V22" s="26"/>
     </row>
-    <row r="23" spans="2:38" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:38" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B23" s="43"/>
       <c r="C23" s="43"/>
       <c r="D23" s="43"/>
@@ -23147,7 +23147,7 @@
       <c r="Q23" s="42"/>
       <c r="V23" s="26"/>
     </row>
-    <row r="24" spans="2:38" ht="33" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:38" ht="33" x14ac:dyDescent="0.25">
       <c r="B24" s="50" t="s">
         <v>61</v>
       </c>
@@ -23167,7 +23167,7 @@
       <c r="Q24" s="42"/>
       <c r="V24" s="26"/>
     </row>
-    <row r="25" spans="2:38" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:38" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B25" s="43"/>
       <c r="C25" s="43"/>
       <c r="D25" s="43"/>
@@ -23190,12 +23190,12 @@
       <c r="Q25" s="42"/>
       <c r="V25" s="26"/>
     </row>
-    <row r="26" spans="2:38" ht="14.5" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="375" t="s">
+    <row r="26" spans="2:38" ht="15" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="B26" s="383" t="s">
         <v>49</v>
       </c>
-      <c r="C26" s="376"/>
-      <c r="D26" s="377"/>
+      <c r="C26" s="384"/>
+      <c r="D26" s="385"/>
       <c r="E26" s="51" t="s">
         <v>50</v>
       </c>
@@ -23220,10 +23220,10 @@
       <c r="Q26" s="42"/>
       <c r="V26" s="26"/>
     </row>
-    <row r="27" spans="2:38" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B27" s="378"/>
-      <c r="C27" s="378"/>
-      <c r="D27" s="379"/>
+    <row r="27" spans="2:38" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="386"/>
+      <c r="C27" s="386"/>
+      <c r="D27" s="387"/>
       <c r="E27" s="53" t="s">
         <v>36</v>
       </c>
@@ -23260,7 +23260,7 @@
       <c r="Q27" s="42"/>
       <c r="V27" s="26"/>
     </row>
-    <row r="28" spans="2:38" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:38" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="B28" s="45"/>
       <c r="C28" s="45"/>
       <c r="D28" s="46"/>
@@ -23297,7 +23297,7 @@
       <c r="AK28" s="27"/>
       <c r="AL28" s="27"/>
     </row>
-    <row r="29" spans="2:38" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:38" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="56"/>
       <c r="C29" s="37">
         <v>2025</v>
@@ -23361,7 +23361,7 @@
       <c r="AK29" s="27"/>
       <c r="AL29" s="27"/>
     </row>
-    <row r="30" spans="2:38" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:38" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="56"/>
       <c r="C30" s="37"/>
       <c r="D30" s="38" t="s">
@@ -23423,7 +23423,7 @@
       <c r="AK30" s="27"/>
       <c r="AL30" s="27"/>
     </row>
-    <row r="31" spans="2:38" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:38" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="56"/>
       <c r="C31" s="37"/>
       <c r="D31" s="37" t="s">
@@ -23465,7 +23465,7 @@
       <c r="Q31" s="49"/>
       <c r="V31" s="26"/>
     </row>
-    <row r="32" spans="2:38" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:38" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="56"/>
       <c r="C32" s="37"/>
       <c r="D32" s="37" t="s">
@@ -23526,7 +23526,7 @@
       <c r="AK32" s="27"/>
       <c r="AL32" s="27"/>
     </row>
-    <row r="33" spans="2:38" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:38" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="56"/>
       <c r="C33" s="37"/>
       <c r="D33" s="38" t="s">
@@ -23587,7 +23587,7 @@
       <c r="AK33" s="27"/>
       <c r="AL33" s="27"/>
     </row>
-    <row r="34" spans="2:38" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:38" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="56"/>
       <c r="C34" s="37"/>
       <c r="D34" s="37" t="s">
@@ -23648,7 +23648,7 @@
       <c r="AK34" s="27"/>
       <c r="AL34" s="27"/>
     </row>
-    <row r="35" spans="2:38" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:38" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="56"/>
       <c r="C35" s="37"/>
       <c r="D35" s="37"/>
@@ -23666,7 +23666,7 @@
       <c r="Q35" s="42"/>
       <c r="V35" s="26"/>
     </row>
-    <row r="36" spans="2:38" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:38" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="56"/>
       <c r="C36" s="57">
         <v>2026</v>
@@ -23710,7 +23710,7 @@
       <c r="Q36" s="42"/>
       <c r="V36" s="26"/>
     </row>
-    <row r="37" spans="2:38" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:38" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="56"/>
       <c r="C37" s="57"/>
       <c r="D37" s="38" t="s">
@@ -23751,7 +23751,7 @@
       </c>
       <c r="V37" s="26"/>
     </row>
-    <row r="38" spans="2:38" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:38" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="56"/>
       <c r="C38" s="57"/>
       <c r="D38" s="37" t="s">
@@ -23791,7 +23791,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="39" spans="2:38" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:38" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="56"/>
       <c r="C39" s="57"/>
       <c r="D39" s="37" t="s">
@@ -23831,7 +23831,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="40" spans="2:38" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:38" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="56"/>
       <c r="C40" s="57"/>
       <c r="D40" s="38" t="s">
@@ -23871,7 +23871,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="41" spans="2:38" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:38" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="56"/>
       <c r="C41" s="37"/>
       <c r="D41" s="37" t="s">
@@ -23911,7 +23911,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="42" spans="2:38" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:38" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B42" s="61"/>
       <c r="C42" s="58"/>
       <c r="D42" s="62"/>
@@ -23927,7 +23927,7 @@
       <c r="N42" s="220"/>
       <c r="O42" s="59"/>
     </row>
-    <row r="43" spans="2:38" ht="13.5" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:38" ht="13.5" thickTop="1" x14ac:dyDescent="0.2">
       <c r="C43" s="60" t="s">
         <v>60</v>
       </c>
@@ -23950,21 +23950,21 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr codeName="Sheet14"/>
   <dimension ref="B1:U41"/>
-  <sheetFormatPr defaultColWidth="5.796875" defaultRowHeight="13" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="5.83203125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.296875" style="26" customWidth="1"/>
-    <col min="2" max="2" width="2.796875" style="66" customWidth="1"/>
-    <col min="3" max="3" width="6.69921875" style="66" customWidth="1"/>
+    <col min="1" max="1" width="2.33203125" style="26" customWidth="1"/>
+    <col min="2" max="2" width="2.83203125" style="66" customWidth="1"/>
+    <col min="3" max="3" width="6.6640625" style="66" customWidth="1"/>
     <col min="4" max="4" width="13" style="66" customWidth="1"/>
-    <col min="5" max="15" width="8.796875" style="66" customWidth="1"/>
-    <col min="16" max="16" width="5.296875" style="66" customWidth="1"/>
-    <col min="17" max="17" width="5.296875" style="66" bestFit="1" customWidth="1"/>
+    <col min="5" max="15" width="8.83203125" style="66" customWidth="1"/>
+    <col min="16" max="16" width="5.33203125" style="66" customWidth="1"/>
+    <col min="17" max="17" width="5.33203125" style="66" bestFit="1" customWidth="1"/>
     <col min="18" max="21" width="6.5" style="66" bestFit="1" customWidth="1"/>
     <col min="22" max="38" width="6.5" style="26" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="5.796875" style="26"/>
+    <col min="39" max="16384" width="5.83203125" style="26"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:21" ht="33" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:21" ht="33" x14ac:dyDescent="0.25">
       <c r="B1" s="74" t="s">
         <v>63</v>
       </c>
@@ -23987,7 +23987,7 @@
       <c r="S1" s="67"/>
       <c r="T1" s="67"/>
     </row>
-    <row r="2" spans="2:21" ht="13.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:21" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B2" s="68"/>
       <c r="C2" s="68"/>
       <c r="D2" s="68"/>
@@ -24010,12 +24010,12 @@
       <c r="S2" s="67"/>
       <c r="T2" s="67"/>
     </row>
-    <row r="3" spans="2:21" ht="13.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="375" t="s">
+    <row r="3" spans="2:21" ht="13.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="B3" s="383" t="s">
         <v>49</v>
       </c>
-      <c r="C3" s="376"/>
-      <c r="D3" s="377"/>
+      <c r="C3" s="384"/>
+      <c r="D3" s="385"/>
       <c r="E3" s="51" t="s">
         <v>50</v>
       </c>
@@ -24044,10 +24044,10 @@
       <c r="T3" s="26"/>
       <c r="U3" s="26"/>
     </row>
-    <row r="4" spans="2:21" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="378"/>
-      <c r="C4" s="378"/>
-      <c r="D4" s="379"/>
+    <row r="4" spans="2:21" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="386"/>
+      <c r="C4" s="386"/>
+      <c r="D4" s="387"/>
       <c r="E4" s="53" t="s">
         <v>36</v>
       </c>
@@ -24088,7 +24088,7 @@
       <c r="T4" s="26"/>
       <c r="U4" s="26"/>
     </row>
-    <row r="5" spans="2:21" ht="12.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:21" ht="12.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B5" s="45"/>
       <c r="C5" s="45"/>
       <c r="D5" s="46"/>
@@ -24110,7 +24110,7 @@
       <c r="T5" s="26"/>
       <c r="U5" s="26"/>
     </row>
-    <row r="6" spans="2:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="56"/>
       <c r="C6" s="37">
         <v>2025</v>
@@ -24158,7 +24158,7 @@
       <c r="T6" s="26"/>
       <c r="U6" s="26"/>
     </row>
-    <row r="7" spans="2:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="56"/>
       <c r="C7" s="37"/>
       <c r="D7" s="38" t="s">
@@ -24204,7 +24204,7 @@
       <c r="T7" s="26"/>
       <c r="U7" s="26"/>
     </row>
-    <row r="8" spans="2:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="56"/>
       <c r="C8" s="37"/>
       <c r="D8" s="37" t="s">
@@ -24250,7 +24250,7 @@
       <c r="T8" s="26"/>
       <c r="U8" s="26"/>
     </row>
-    <row r="9" spans="2:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="56"/>
       <c r="C9" s="37"/>
       <c r="D9" s="37" t="s">
@@ -24296,7 +24296,7 @@
       <c r="T9" s="26"/>
       <c r="U9" s="26"/>
     </row>
-    <row r="10" spans="2:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="56"/>
       <c r="C10" s="37"/>
       <c r="D10" s="38" t="s">
@@ -24342,7 +24342,7 @@
       <c r="T10" s="26"/>
       <c r="U10" s="26"/>
     </row>
-    <row r="11" spans="2:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="56"/>
       <c r="C11" s="37"/>
       <c r="D11" s="37" t="s">
@@ -24388,7 +24388,7 @@
       <c r="T11" s="26"/>
       <c r="U11" s="26"/>
     </row>
-    <row r="12" spans="2:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="56"/>
       <c r="C12" s="37"/>
       <c r="D12" s="37"/>
@@ -24410,7 +24410,7 @@
       <c r="T12" s="26"/>
       <c r="U12" s="26"/>
     </row>
-    <row r="13" spans="2:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="56"/>
       <c r="C13" s="57">
         <v>2026</v>
@@ -24458,7 +24458,7 @@
       <c r="T13" s="26"/>
       <c r="U13" s="26"/>
     </row>
-    <row r="14" spans="2:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="56"/>
       <c r="C14" s="57"/>
       <c r="D14" s="38" t="s">
@@ -24504,7 +24504,7 @@
       <c r="T14" s="26"/>
       <c r="U14" s="26"/>
     </row>
-    <row r="15" spans="2:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="56"/>
       <c r="C15" s="57"/>
       <c r="D15" s="37" t="s">
@@ -24550,7 +24550,7 @@
       <c r="T15" s="26"/>
       <c r="U15" s="26"/>
     </row>
-    <row r="16" spans="2:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="56"/>
       <c r="C16" s="57"/>
       <c r="D16" s="37" t="s">
@@ -24596,7 +24596,7 @@
       <c r="T16" s="26"/>
       <c r="U16" s="26"/>
     </row>
-    <row r="17" spans="2:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="56"/>
       <c r="C17" s="57"/>
       <c r="D17" s="38" t="s">
@@ -24641,7 +24641,7 @@
       <c r="T17" s="26"/>
       <c r="U17" s="26"/>
     </row>
-    <row r="18" spans="2:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="56"/>
       <c r="C18" s="37"/>
       <c r="D18" s="37" t="s">
@@ -24687,7 +24687,7 @@
       <c r="T18" s="26"/>
       <c r="U18" s="26"/>
     </row>
-    <row r="19" spans="2:21" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:21" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B19" s="61"/>
       <c r="C19" s="58"/>
       <c r="D19" s="62"/>
@@ -24709,7 +24709,7 @@
       <c r="T19" s="26"/>
       <c r="U19" s="26"/>
     </row>
-    <row r="20" spans="2:21" ht="11.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:21" ht="11.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="B20" s="43"/>
       <c r="C20" s="60"/>
       <c r="D20" s="43"/>
@@ -24731,7 +24731,7 @@
       <c r="T20" s="26"/>
       <c r="U20" s="26"/>
     </row>
-    <row r="21" spans="2:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B21" s="43"/>
       <c r="C21" s="43"/>
       <c r="D21" s="43"/>
@@ -24753,7 +24753,7 @@
       <c r="T21" s="26"/>
       <c r="U21" s="26"/>
     </row>
-    <row r="22" spans="2:21" ht="33" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:21" ht="33" x14ac:dyDescent="0.25">
       <c r="B22" s="74" t="s">
         <v>65</v>
       </c>
@@ -24776,7 +24776,7 @@
       <c r="T22" s="26"/>
       <c r="U22" s="26"/>
     </row>
-    <row r="23" spans="2:21" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:21" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B23" s="47"/>
       <c r="C23" s="47"/>
       <c r="D23" s="48"/>
@@ -24797,12 +24797,12 @@
       <c r="T23" s="26"/>
       <c r="U23" s="26"/>
     </row>
-    <row r="24" spans="2:21" ht="13.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="375" t="s">
+    <row r="24" spans="2:21" ht="13.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="B24" s="383" t="s">
         <v>49</v>
       </c>
-      <c r="C24" s="376"/>
-      <c r="D24" s="377"/>
+      <c r="C24" s="384"/>
+      <c r="D24" s="385"/>
       <c r="E24" s="51" t="s">
         <v>50</v>
       </c>
@@ -24830,10 +24830,10 @@
       <c r="T24" s="26"/>
       <c r="U24" s="26"/>
     </row>
-    <row r="25" spans="2:21" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="378"/>
-      <c r="C25" s="378"/>
-      <c r="D25" s="379"/>
+    <row r="25" spans="2:21" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="386"/>
+      <c r="C25" s="386"/>
+      <c r="D25" s="387"/>
       <c r="E25" s="53" t="s">
         <v>36</v>
       </c>
@@ -24873,7 +24873,7 @@
       <c r="T25" s="26"/>
       <c r="U25" s="26"/>
     </row>
-    <row r="26" spans="2:21" ht="12.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:21" ht="12.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B26" s="45"/>
       <c r="C26" s="45"/>
       <c r="D26" s="46"/>
@@ -24894,7 +24894,7 @@
       <c r="T26" s="26"/>
       <c r="U26" s="26"/>
     </row>
-    <row r="27" spans="2:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="56"/>
       <c r="C27" s="37">
         <v>2025</v>
@@ -24941,7 +24941,7 @@
       <c r="T27" s="26"/>
       <c r="U27" s="26"/>
     </row>
-    <row r="28" spans="2:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="56"/>
       <c r="C28" s="37"/>
       <c r="D28" s="38" t="s">
@@ -24986,7 +24986,7 @@
       <c r="T28" s="26"/>
       <c r="U28" s="26"/>
     </row>
-    <row r="29" spans="2:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="56"/>
       <c r="C29" s="37"/>
       <c r="D29" s="37" t="s">
@@ -25031,7 +25031,7 @@
       <c r="T29" s="26"/>
       <c r="U29" s="26"/>
     </row>
-    <row r="30" spans="2:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="56"/>
       <c r="C30" s="37"/>
       <c r="D30" s="37" t="s">
@@ -25076,7 +25076,7 @@
       <c r="T30" s="26"/>
       <c r="U30" s="26"/>
     </row>
-    <row r="31" spans="2:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="56"/>
       <c r="C31" s="37"/>
       <c r="D31" s="38" t="s">
@@ -25121,7 +25121,7 @@
       <c r="T31" s="26"/>
       <c r="U31" s="26"/>
     </row>
-    <row r="32" spans="2:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="56"/>
       <c r="C32" s="37"/>
       <c r="D32" s="37" t="s">
@@ -25167,7 +25167,7 @@
       <c r="T32" s="26"/>
       <c r="U32" s="26"/>
     </row>
-    <row r="33" spans="2:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="56"/>
       <c r="C33" s="37"/>
       <c r="D33" s="37"/>
@@ -25189,7 +25189,7 @@
       <c r="T33" s="26"/>
       <c r="U33" s="26"/>
     </row>
-    <row r="34" spans="2:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="56"/>
       <c r="C34" s="57">
         <v>2026</v>
@@ -25237,7 +25237,7 @@
       <c r="T34" s="26"/>
       <c r="U34" s="26"/>
     </row>
-    <row r="35" spans="2:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="56"/>
       <c r="C35" s="57"/>
       <c r="D35" s="38" t="s">
@@ -25283,7 +25283,7 @@
       <c r="T35" s="26"/>
       <c r="U35" s="26"/>
     </row>
-    <row r="36" spans="2:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="56"/>
       <c r="C36" s="57"/>
       <c r="D36" s="37" t="s">
@@ -25329,7 +25329,7 @@
       <c r="T36" s="26"/>
       <c r="U36" s="26"/>
     </row>
-    <row r="37" spans="2:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="56"/>
       <c r="C37" s="57"/>
       <c r="D37" s="37" t="s">
@@ -25375,7 +25375,7 @@
       <c r="T37" s="26"/>
       <c r="U37" s="26"/>
     </row>
-    <row r="38" spans="2:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="56"/>
       <c r="C38" s="57"/>
       <c r="D38" s="38" t="s">
@@ -25421,7 +25421,7 @@
       <c r="T38" s="26"/>
       <c r="U38" s="26"/>
     </row>
-    <row r="39" spans="2:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="56"/>
       <c r="C39" s="37"/>
       <c r="D39" s="37" t="s">
@@ -25467,7 +25467,7 @@
       <c r="T39" s="26"/>
       <c r="U39" s="26"/>
     </row>
-    <row r="40" spans="2:21" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:21" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B40" s="61"/>
       <c r="C40" s="58"/>
       <c r="D40" s="62"/>
@@ -25483,7 +25483,7 @@
       <c r="N40" s="232"/>
       <c r="O40" s="236"/>
     </row>
-    <row r="41" spans="2:21" ht="13.5" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:21" ht="13.5" thickTop="1" x14ac:dyDescent="0.2">
       <c r="C41" s="60"/>
     </row>
   </sheetData>
@@ -25503,23 +25503,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr codeName="Sheet15"/>
   <dimension ref="B1:T43"/>
-  <sheetFormatPr defaultColWidth="5.796875" defaultRowHeight="13" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="5.83203125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.296875" style="83" customWidth="1"/>
-    <col min="2" max="2" width="2.796875" style="83" customWidth="1"/>
-    <col min="3" max="3" width="6.796875" style="83" customWidth="1"/>
+    <col min="1" max="1" width="2.33203125" style="83" customWidth="1"/>
+    <col min="2" max="2" width="2.83203125" style="83" customWidth="1"/>
+    <col min="3" max="3" width="6.83203125" style="83" customWidth="1"/>
     <col min="4" max="4" width="13" style="83" customWidth="1"/>
-    <col min="5" max="10" width="8.796875" style="83" customWidth="1"/>
+    <col min="5" max="10" width="8.83203125" style="83" customWidth="1"/>
     <col min="11" max="11" width="9.5" style="83" customWidth="1"/>
-    <col min="12" max="15" width="8.796875" style="83" customWidth="1"/>
-    <col min="16" max="16" width="6.69921875" style="83" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.19921875" style="83" customWidth="1"/>
-    <col min="18" max="20" width="6.69921875" style="83" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="8.796875" style="83" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="5.796875" style="83"/>
+    <col min="12" max="15" width="8.83203125" style="83" customWidth="1"/>
+    <col min="16" max="16" width="6.6640625" style="83" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.1640625" style="83" customWidth="1"/>
+    <col min="18" max="20" width="6.6640625" style="83" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="8.83203125" style="83" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="5.83203125" style="83"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:20" ht="33" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:20" ht="33" x14ac:dyDescent="0.25">
       <c r="B1" s="87" t="s">
         <v>66</v>
       </c>
@@ -25542,7 +25542,7 @@
       <c r="S1" s="82"/>
       <c r="T1" s="82"/>
     </row>
-    <row r="2" spans="2:20" ht="13.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:20" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B2" s="82"/>
       <c r="C2" s="82"/>
       <c r="D2" s="82"/>
@@ -25565,12 +25565,12 @@
       <c r="S2" s="82"/>
       <c r="T2" s="82"/>
     </row>
-    <row r="3" spans="2:20" ht="13.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="375" t="s">
+    <row r="3" spans="2:20" ht="13.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="B3" s="383" t="s">
         <v>49</v>
       </c>
-      <c r="C3" s="376"/>
-      <c r="D3" s="377"/>
+      <c r="C3" s="384"/>
+      <c r="D3" s="385"/>
       <c r="E3" s="51" t="s">
         <v>50</v>
       </c>
@@ -25593,10 +25593,10 @@
       </c>
       <c r="O3" s="51"/>
     </row>
-    <row r="4" spans="2:20" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="378"/>
-      <c r="C4" s="378"/>
-      <c r="D4" s="379"/>
+    <row r="4" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="386"/>
+      <c r="C4" s="386"/>
+      <c r="D4" s="387"/>
       <c r="E4" s="53" t="s">
         <v>36</v>
       </c>
@@ -25631,7 +25631,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="5" spans="2:20" ht="12.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:20" ht="12.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="B5" s="45"/>
       <c r="C5" s="45"/>
       <c r="D5" s="46"/>
@@ -25647,7 +25647,7 @@
       <c r="N5" s="221"/>
       <c r="O5" s="45"/>
     </row>
-    <row r="6" spans="2:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="56"/>
       <c r="C6" s="37">
         <v>2025</v>
@@ -25690,7 +25690,7 @@
       </c>
       <c r="P6" s="88"/>
     </row>
-    <row r="7" spans="2:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="56"/>
       <c r="C7" s="37"/>
       <c r="D7" s="38" t="s">
@@ -25731,7 +25731,7 @@
       </c>
       <c r="P7" s="88"/>
     </row>
-    <row r="8" spans="2:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="56"/>
       <c r="C8" s="37"/>
       <c r="D8" s="37" t="s">
@@ -25772,7 +25772,7 @@
       </c>
       <c r="P8" s="88"/>
     </row>
-    <row r="9" spans="2:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="56"/>
       <c r="C9" s="37"/>
       <c r="D9" s="37" t="s">
@@ -25813,7 +25813,7 @@
       </c>
       <c r="P9" s="88"/>
     </row>
-    <row r="10" spans="2:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="56"/>
       <c r="C10" s="37"/>
       <c r="D10" s="38" t="s">
@@ -25854,7 +25854,7 @@
       </c>
       <c r="P10" s="88"/>
     </row>
-    <row r="11" spans="2:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="56"/>
       <c r="C11" s="37"/>
       <c r="D11" s="37" t="s">
@@ -25895,7 +25895,7 @@
       </c>
       <c r="P11" s="88"/>
     </row>
-    <row r="12" spans="2:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="56"/>
       <c r="C12" s="37"/>
       <c r="D12" s="37"/>
@@ -25912,7 +25912,7 @@
       <c r="O12" s="211"/>
       <c r="P12" s="88"/>
     </row>
-    <row r="13" spans="2:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="56"/>
       <c r="C13" s="57">
         <v>2026</v>
@@ -25955,7 +25955,7 @@
       </c>
       <c r="P13" s="88"/>
     </row>
-    <row r="14" spans="2:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="56"/>
       <c r="C14" s="57"/>
       <c r="D14" s="38" t="s">
@@ -25996,7 +25996,7 @@
       </c>
       <c r="P14" s="88"/>
     </row>
-    <row r="15" spans="2:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="56"/>
       <c r="C15" s="57"/>
       <c r="D15" s="37" t="s">
@@ -26037,7 +26037,7 @@
       </c>
       <c r="P15" s="88"/>
     </row>
-    <row r="16" spans="2:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="56"/>
       <c r="C16" s="57"/>
       <c r="D16" s="37" t="s">
@@ -26078,7 +26078,7 @@
       </c>
       <c r="P16" s="88"/>
     </row>
-    <row r="17" spans="2:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="56"/>
       <c r="C17" s="57"/>
       <c r="D17" s="38" t="s">
@@ -26119,7 +26119,7 @@
       </c>
       <c r="P17" s="88"/>
     </row>
-    <row r="18" spans="2:16" s="26" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:16" s="26" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="56"/>
       <c r="C18" s="37"/>
       <c r="D18" s="37" t="s">
@@ -26159,7 +26159,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="2:16" s="26" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:16" s="26" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B19" s="61"/>
       <c r="C19" s="58"/>
       <c r="D19" s="62"/>
@@ -26175,7 +26175,7 @@
       <c r="N19" s="220"/>
       <c r="O19" s="59"/>
     </row>
-    <row r="20" spans="2:16" s="26" customFormat="1" ht="11.15" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:16" s="26" customFormat="1" ht="11.1" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="B20" s="43"/>
       <c r="C20" s="36" t="s">
         <v>40</v>
@@ -26193,7 +26193,7 @@
       <c r="N20" s="43"/>
       <c r="O20" s="43"/>
     </row>
-    <row r="21" spans="2:16" s="26" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:16" s="26" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B21" s="43"/>
       <c r="C21" s="60"/>
       <c r="D21" s="43"/>
@@ -26209,7 +26209,7 @@
       <c r="N21" s="43"/>
       <c r="O21" s="43"/>
     </row>
-    <row r="22" spans="2:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B22" s="82"/>
       <c r="C22" s="82"/>
       <c r="D22" s="82"/>
@@ -26225,7 +26225,7 @@
       <c r="N22" s="82"/>
       <c r="O22" s="82"/>
     </row>
-    <row r="23" spans="2:16" ht="33" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:16" ht="33" x14ac:dyDescent="0.25">
       <c r="B23" s="87" t="s">
         <v>67</v>
       </c>
@@ -26243,7 +26243,7 @@
       <c r="N23" s="81"/>
       <c r="O23" s="81"/>
     </row>
-    <row r="24" spans="2:16" ht="13.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:16" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B24" s="85"/>
       <c r="C24" s="85"/>
       <c r="D24" s="86"/>
@@ -26259,12 +26259,12 @@
       <c r="N24" s="86"/>
       <c r="O24" s="86"/>
     </row>
-    <row r="25" spans="2:16" ht="13.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="375" t="s">
+    <row r="25" spans="2:16" ht="13.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="B25" s="383" t="s">
         <v>49</v>
       </c>
-      <c r="C25" s="376"/>
-      <c r="D25" s="377"/>
+      <c r="C25" s="384"/>
+      <c r="D25" s="385"/>
       <c r="E25" s="51" t="s">
         <v>50</v>
       </c>
@@ -26287,10 +26287,10 @@
       </c>
       <c r="O25" s="51"/>
     </row>
-    <row r="26" spans="2:16" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="378"/>
-      <c r="C26" s="378"/>
-      <c r="D26" s="379"/>
+    <row r="26" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="386"/>
+      <c r="C26" s="386"/>
+      <c r="D26" s="387"/>
       <c r="E26" s="53" t="s">
         <v>36</v>
       </c>
@@ -26325,7 +26325,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="27" spans="2:16" ht="12.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:16" ht="12.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="B27" s="45"/>
       <c r="C27" s="45"/>
       <c r="D27" s="46"/>
@@ -26341,7 +26341,7 @@
       <c r="N27" s="221"/>
       <c r="O27" s="45"/>
     </row>
-    <row r="28" spans="2:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="56"/>
       <c r="C28" s="37">
         <v>2025</v>
@@ -26383,7 +26383,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="29" spans="2:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="56"/>
       <c r="C29" s="37"/>
       <c r="D29" s="38" t="s">
@@ -26423,7 +26423,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="30" spans="2:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="56"/>
       <c r="C30" s="37"/>
       <c r="D30" s="37" t="s">
@@ -26463,7 +26463,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="31" spans="2:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="56"/>
       <c r="C31" s="37"/>
       <c r="D31" s="37" t="s">
@@ -26503,7 +26503,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="32" spans="2:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="56"/>
       <c r="C32" s="37"/>
       <c r="D32" s="38" t="s">
@@ -26543,7 +26543,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="33" spans="2:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="56"/>
       <c r="C33" s="37"/>
       <c r="D33" s="37" t="s">
@@ -26583,7 +26583,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="34" spans="2:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="56"/>
       <c r="C34" s="37"/>
       <c r="D34" s="37"/>
@@ -26599,7 +26599,7 @@
       <c r="N34" s="218"/>
       <c r="O34" s="211"/>
     </row>
-    <row r="35" spans="2:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="56"/>
       <c r="C35" s="57">
         <v>2026</v>
@@ -26641,7 +26641,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="2:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="56"/>
       <c r="C36" s="57"/>
       <c r="D36" s="38" t="s">
@@ -26681,7 +26681,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="2:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="56"/>
       <c r="C37" s="57"/>
       <c r="D37" s="37" t="s">
@@ -26721,7 +26721,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="38" spans="2:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="56"/>
       <c r="C38" s="57"/>
       <c r="D38" s="37" t="s">
@@ -26761,7 +26761,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="2:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="56"/>
       <c r="C39" s="57"/>
       <c r="D39" s="38" t="s">
@@ -26801,7 +26801,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="40" spans="2:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="56"/>
       <c r="C40" s="37"/>
       <c r="D40" s="37" t="s">
@@ -26841,7 +26841,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="41" spans="2:15" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:15" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B41" s="61"/>
       <c r="C41" s="58"/>
       <c r="D41" s="62"/>
@@ -26857,12 +26857,12 @@
       <c r="N41" s="220"/>
       <c r="O41" s="59"/>
     </row>
-    <row r="42" spans="2:15" ht="13.5" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:15" ht="13.5" thickTop="1" x14ac:dyDescent="0.2">
       <c r="C42" s="35" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="60"/>
     </row>
   </sheetData>
@@ -26884,18 +26884,18 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q53"/>
-  <sheetFormatPr defaultColWidth="6.796875" defaultRowHeight="13" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="6.83203125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.19921875" style="66" customWidth="1"/>
-    <col min="2" max="2" width="22.796875" style="66" customWidth="1"/>
-    <col min="3" max="3" width="2.796875" style="66" customWidth="1"/>
-    <col min="4" max="14" width="9.796875" style="66" customWidth="1"/>
-    <col min="15" max="15" width="7.19921875" style="66" customWidth="1"/>
-    <col min="16" max="17" width="4.796875" style="66" customWidth="1"/>
-    <col min="18" max="16384" width="6.796875" style="66"/>
+    <col min="1" max="1" width="2.1640625" style="66" customWidth="1"/>
+    <col min="2" max="2" width="22.83203125" style="66" customWidth="1"/>
+    <col min="3" max="3" width="2.83203125" style="66" customWidth="1"/>
+    <col min="4" max="14" width="9.83203125" style="66" customWidth="1"/>
+    <col min="15" max="15" width="7.1640625" style="66" customWidth="1"/>
+    <col min="16" max="17" width="4.83203125" style="66" customWidth="1"/>
+    <col min="18" max="16384" width="6.83203125" style="66"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:17" ht="33" x14ac:dyDescent="0.25">
       <c r="A1" s="74" t="s">
         <v>451</v>
       </c>
@@ -26916,7 +26916,7 @@
       <c r="P1" s="68"/>
       <c r="Q1" s="68"/>
     </row>
-    <row r="2" spans="1:17" ht="15.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:17" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="89"/>
       <c r="B2" s="65"/>
       <c r="C2" s="65"/>
@@ -26932,12 +26932,12 @@
       <c r="M2" s="65"/>
       <c r="N2" s="65"/>
     </row>
-    <row r="3" spans="1:17" ht="13.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="384" t="s">
+    <row r="3" spans="1:17" ht="13.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="394" t="s">
         <v>69</v>
       </c>
-      <c r="B3" s="376"/>
-      <c r="C3" s="377"/>
+      <c r="B3" s="384"/>
+      <c r="C3" s="385"/>
       <c r="D3" s="75" t="s">
         <v>50</v>
       </c>
@@ -26960,10 +26960,10 @@
       </c>
       <c r="N3" s="76"/>
     </row>
-    <row r="4" spans="1:17" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="378"/>
-      <c r="B4" s="378"/>
-      <c r="C4" s="379"/>
+    <row r="4" spans="1:17" ht="14.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="386"/>
+      <c r="B4" s="386"/>
+      <c r="C4" s="387"/>
       <c r="D4" s="77" t="s">
         <v>36</v>
       </c>
@@ -26998,25 +26998,25 @@
         <v>52</v>
       </c>
     </row>
-    <row r="5" spans="1:17" s="91" customFormat="1" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="376"/>
-      <c r="B5" s="376"/>
-      <c r="C5" s="377"/>
-      <c r="D5" s="385" t="s">
+    <row r="5" spans="1:17" s="91" customFormat="1" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="384"/>
+      <c r="B5" s="384"/>
+      <c r="C5" s="385"/>
+      <c r="D5" s="388" t="s">
         <v>70</v>
       </c>
-      <c r="E5" s="386"/>
-      <c r="F5" s="386"/>
-      <c r="G5" s="386"/>
-      <c r="H5" s="386"/>
-      <c r="I5" s="386"/>
-      <c r="J5" s="386"/>
-      <c r="K5" s="386"/>
-      <c r="L5" s="386"/>
-      <c r="M5" s="386"/>
-      <c r="N5" s="386"/>
-    </row>
-    <row r="6" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E5" s="389"/>
+      <c r="F5" s="389"/>
+      <c r="G5" s="389"/>
+      <c r="H5" s="389"/>
+      <c r="I5" s="389"/>
+      <c r="J5" s="389"/>
+      <c r="K5" s="389"/>
+      <c r="L5" s="389"/>
+      <c r="M5" s="389"/>
+      <c r="N5" s="389"/>
+    </row>
+    <row r="6" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="79"/>
       <c r="B6" s="79"/>
       <c r="C6" s="79"/>
@@ -27032,7 +27032,7 @@
       <c r="M6" s="254"/>
       <c r="N6" s="271"/>
     </row>
-    <row r="7" spans="1:17" s="92" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" s="92" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="94"/>
       <c r="B7" s="95" t="s">
         <v>71</v>
@@ -27073,7 +27073,7 @@
       </c>
       <c r="O7" s="93"/>
     </row>
-    <row r="8" spans="1:17" s="92" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" s="92" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="94"/>
       <c r="B8" s="95" t="s">
         <v>72</v>
@@ -27114,7 +27114,7 @@
       </c>
       <c r="O8" s="93"/>
     </row>
-    <row r="9" spans="1:17" s="92" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" s="92" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="94"/>
       <c r="B9" s="95" t="s">
         <v>73</v>
@@ -27154,7 +27154,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="10" spans="1:17" s="92" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" s="92" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="94"/>
       <c r="B10" s="95" t="s">
         <v>74</v>
@@ -27194,7 +27194,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="96"/>
       <c r="B11" s="96"/>
       <c r="C11" s="96"/>
@@ -27210,7 +27210,7 @@
       <c r="M11" s="255"/>
       <c r="N11" s="272"/>
     </row>
-    <row r="12" spans="1:17" s="92" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:17" s="92" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="261" t="s">
         <v>12</v>
       </c>
@@ -27252,25 +27252,25 @@
         <v>124</v>
       </c>
     </row>
-    <row r="13" spans="1:17" s="91" customFormat="1" ht="19.399999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="376"/>
-      <c r="B13" s="376"/>
-      <c r="C13" s="377"/>
-      <c r="D13" s="382" t="s">
+    <row r="13" spans="1:17" s="91" customFormat="1" ht="19.350000000000001" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="384"/>
+      <c r="B13" s="384"/>
+      <c r="C13" s="385"/>
+      <c r="D13" s="390" t="s">
         <v>75</v>
       </c>
-      <c r="E13" s="383"/>
-      <c r="F13" s="383"/>
-      <c r="G13" s="383"/>
-      <c r="H13" s="383"/>
-      <c r="I13" s="383"/>
-      <c r="J13" s="383"/>
-      <c r="K13" s="383"/>
-      <c r="L13" s="383"/>
-      <c r="M13" s="383"/>
-      <c r="N13" s="383"/>
-    </row>
-    <row r="14" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E13" s="391"/>
+      <c r="F13" s="391"/>
+      <c r="G13" s="391"/>
+      <c r="H13" s="391"/>
+      <c r="I13" s="391"/>
+      <c r="J13" s="391"/>
+      <c r="K13" s="391"/>
+      <c r="L13" s="391"/>
+      <c r="M13" s="391"/>
+      <c r="N13" s="391"/>
+    </row>
+    <row r="14" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="79"/>
       <c r="B14" s="79"/>
       <c r="C14" s="79"/>
@@ -27286,7 +27286,7 @@
       <c r="M14" s="254"/>
       <c r="N14" s="271"/>
     </row>
-    <row r="15" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="79"/>
       <c r="B15" s="99" t="s">
         <v>71</v>
@@ -27326,7 +27326,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="79"/>
       <c r="B16" s="99" t="s">
         <v>72</v>
@@ -27366,7 +27366,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="79"/>
       <c r="B17" s="99" t="s">
         <v>73</v>
@@ -27406,7 +27406,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="18" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="79"/>
       <c r="B18" s="99" t="s">
         <v>74</v>
@@ -27446,7 +27446,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="19" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="96"/>
       <c r="B19" s="96"/>
       <c r="C19" s="96"/>
@@ -27462,7 +27462,7 @@
       <c r="M19" s="255"/>
       <c r="N19" s="272"/>
     </row>
-    <row r="20" spans="1:17" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="100" t="s">
         <v>12</v>
       </c>
@@ -27504,25 +27504,25 @@
         <v>126</v>
       </c>
     </row>
-    <row r="21" spans="1:17" s="91" customFormat="1" ht="19.399999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="380"/>
-      <c r="B21" s="380"/>
-      <c r="C21" s="381"/>
-      <c r="D21" s="382" t="s">
+    <row r="21" spans="1:17" s="91" customFormat="1" ht="19.350000000000001" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="392"/>
+      <c r="B21" s="392"/>
+      <c r="C21" s="393"/>
+      <c r="D21" s="390" t="s">
         <v>76</v>
       </c>
-      <c r="E21" s="383"/>
-      <c r="F21" s="383"/>
-      <c r="G21" s="383"/>
-      <c r="H21" s="383"/>
-      <c r="I21" s="383"/>
-      <c r="J21" s="383"/>
-      <c r="K21" s="383"/>
-      <c r="L21" s="383"/>
-      <c r="M21" s="383"/>
-      <c r="N21" s="383"/>
-    </row>
-    <row r="22" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E21" s="391"/>
+      <c r="F21" s="391"/>
+      <c r="G21" s="391"/>
+      <c r="H21" s="391"/>
+      <c r="I21" s="391"/>
+      <c r="J21" s="391"/>
+      <c r="K21" s="391"/>
+      <c r="L21" s="391"/>
+      <c r="M21" s="391"/>
+      <c r="N21" s="391"/>
+    </row>
+    <row r="22" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="79"/>
       <c r="B22" s="79"/>
       <c r="C22" s="79"/>
@@ -27538,7 +27538,7 @@
       <c r="M22" s="254"/>
       <c r="N22" s="271"/>
     </row>
-    <row r="23" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="79"/>
       <c r="B23" s="99" t="s">
         <v>71</v>
@@ -27578,7 +27578,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="79"/>
       <c r="B24" s="99" t="s">
         <v>72</v>
@@ -27621,7 +27621,7 @@
       <c r="P24" s="67"/>
       <c r="Q24" s="67"/>
     </row>
-    <row r="25" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="79"/>
       <c r="B25" s="99" t="s">
         <v>73</v>
@@ -27664,7 +27664,7 @@
       <c r="P25" s="67"/>
       <c r="Q25" s="67"/>
     </row>
-    <row r="26" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="79"/>
       <c r="B26" s="99" t="s">
         <v>74</v>
@@ -27707,7 +27707,7 @@
       <c r="P26" s="68"/>
       <c r="Q26" s="68"/>
     </row>
-    <row r="27" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="96"/>
       <c r="B27" s="96"/>
       <c r="C27" s="96"/>
@@ -27723,7 +27723,7 @@
       <c r="M27" s="255"/>
       <c r="N27" s="272"/>
     </row>
-    <row r="28" spans="1:17" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:17" ht="13.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A28" s="261" t="s">
         <v>12</v>
       </c>
@@ -27765,25 +27765,25 @@
         <v>131</v>
       </c>
     </row>
-    <row r="29" spans="1:17" s="91" customFormat="1" ht="19.399999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="376"/>
-      <c r="B29" s="376"/>
-      <c r="C29" s="377"/>
-      <c r="D29" s="385" t="s">
+    <row r="29" spans="1:17" s="91" customFormat="1" ht="19.350000000000001" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="384"/>
+      <c r="B29" s="384"/>
+      <c r="C29" s="385"/>
+      <c r="D29" s="388" t="s">
         <v>77</v>
       </c>
-      <c r="E29" s="386"/>
-      <c r="F29" s="386"/>
-      <c r="G29" s="386"/>
-      <c r="H29" s="386"/>
-      <c r="I29" s="386"/>
-      <c r="J29" s="386"/>
-      <c r="K29" s="386"/>
-      <c r="L29" s="386"/>
-      <c r="M29" s="386"/>
-      <c r="N29" s="386"/>
-    </row>
-    <row r="30" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E29" s="389"/>
+      <c r="F29" s="389"/>
+      <c r="G29" s="389"/>
+      <c r="H29" s="389"/>
+      <c r="I29" s="389"/>
+      <c r="J29" s="389"/>
+      <c r="K29" s="389"/>
+      <c r="L29" s="389"/>
+      <c r="M29" s="389"/>
+      <c r="N29" s="389"/>
+    </row>
+    <row r="30" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="79"/>
       <c r="B30" s="79"/>
       <c r="C30" s="79"/>
@@ -27799,7 +27799,7 @@
       <c r="M30" s="254"/>
       <c r="N30" s="271"/>
     </row>
-    <row r="31" spans="1:17" s="92" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:17" s="92" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="94"/>
       <c r="B31" s="95" t="s">
         <v>71</v>
@@ -27840,7 +27840,7 @@
       </c>
       <c r="O31" s="93"/>
     </row>
-    <row r="32" spans="1:17" s="92" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:17" s="92" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="94"/>
       <c r="B32" s="95" t="s">
         <v>72</v>
@@ -27881,7 +27881,7 @@
       </c>
       <c r="O32" s="93"/>
     </row>
-    <row r="33" spans="1:17" s="92" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:17" s="92" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="94"/>
       <c r="B33" s="95" t="s">
         <v>73</v>
@@ -27921,7 +27921,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="34" spans="1:17" s="92" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:17" s="92" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="94"/>
       <c r="B34" s="95" t="s">
         <v>74</v>
@@ -27961,7 +27961,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="96"/>
       <c r="B35" s="96"/>
       <c r="C35" s="96"/>
@@ -27977,7 +27977,7 @@
       <c r="M35" s="255"/>
       <c r="N35" s="272"/>
     </row>
-    <row r="36" spans="1:17" s="92" customFormat="1" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:17" s="92" customFormat="1" ht="13.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A36" s="261" t="s">
         <v>12</v>
       </c>
@@ -28019,25 +28019,25 @@
         <v>100</v>
       </c>
     </row>
-    <row r="37" spans="1:17" s="91" customFormat="1" ht="19.399999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="376"/>
-      <c r="B37" s="376"/>
-      <c r="C37" s="377"/>
-      <c r="D37" s="382" t="s">
+    <row r="37" spans="1:17" s="91" customFormat="1" ht="19.350000000000001" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="384"/>
+      <c r="B37" s="384"/>
+      <c r="C37" s="385"/>
+      <c r="D37" s="390" t="s">
         <v>57</v>
       </c>
-      <c r="E37" s="383"/>
-      <c r="F37" s="383"/>
-      <c r="G37" s="383"/>
-      <c r="H37" s="383"/>
-      <c r="I37" s="383"/>
-      <c r="J37" s="383"/>
-      <c r="K37" s="383"/>
-      <c r="L37" s="383"/>
-      <c r="M37" s="383"/>
-      <c r="N37" s="383"/>
-    </row>
-    <row r="38" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E37" s="391"/>
+      <c r="F37" s="391"/>
+      <c r="G37" s="391"/>
+      <c r="H37" s="391"/>
+      <c r="I37" s="391"/>
+      <c r="J37" s="391"/>
+      <c r="K37" s="391"/>
+      <c r="L37" s="391"/>
+      <c r="M37" s="391"/>
+      <c r="N37" s="391"/>
+    </row>
+    <row r="38" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="79"/>
       <c r="B38" s="79"/>
       <c r="C38" s="79"/>
@@ -28053,7 +28053,7 @@
       <c r="M38" s="254"/>
       <c r="N38" s="271"/>
     </row>
-    <row r="39" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="79"/>
       <c r="B39" s="99" t="s">
         <v>71</v>
@@ -28093,7 +28093,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="40" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="79"/>
       <c r="B40" s="99" t="s">
         <v>72</v>
@@ -28133,7 +28133,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="41" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="79"/>
       <c r="B41" s="99" t="s">
         <v>73</v>
@@ -28173,7 +28173,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="42" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="79"/>
       <c r="B42" s="99" t="s">
         <v>74</v>
@@ -28213,7 +28213,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="96"/>
       <c r="B43" s="96"/>
       <c r="C43" s="96"/>
@@ -28229,7 +28229,7 @@
       <c r="M43" s="255"/>
       <c r="N43" s="272"/>
     </row>
-    <row r="44" spans="1:17" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A44" s="100" t="s">
         <v>12</v>
       </c>
@@ -28271,25 +28271,25 @@
         <v>131</v>
       </c>
     </row>
-    <row r="45" spans="1:17" s="91" customFormat="1" ht="19.399999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="380"/>
-      <c r="B45" s="380"/>
-      <c r="C45" s="381"/>
-      <c r="D45" s="382" t="s">
+    <row r="45" spans="1:17" s="91" customFormat="1" ht="19.350000000000001" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="392"/>
+      <c r="B45" s="392"/>
+      <c r="C45" s="393"/>
+      <c r="D45" s="390" t="s">
         <v>78</v>
       </c>
-      <c r="E45" s="383"/>
-      <c r="F45" s="383"/>
-      <c r="G45" s="383"/>
-      <c r="H45" s="383"/>
-      <c r="I45" s="383"/>
-      <c r="J45" s="383"/>
-      <c r="K45" s="383"/>
-      <c r="L45" s="383"/>
-      <c r="M45" s="383"/>
-      <c r="N45" s="383"/>
-    </row>
-    <row r="46" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E45" s="391"/>
+      <c r="F45" s="391"/>
+      <c r="G45" s="391"/>
+      <c r="H45" s="391"/>
+      <c r="I45" s="391"/>
+      <c r="J45" s="391"/>
+      <c r="K45" s="391"/>
+      <c r="L45" s="391"/>
+      <c r="M45" s="391"/>
+      <c r="N45" s="391"/>
+    </row>
+    <row r="46" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="79"/>
       <c r="B46" s="79"/>
       <c r="C46" s="79"/>
@@ -28305,7 +28305,7 @@
       <c r="M46" s="254"/>
       <c r="N46" s="271"/>
     </row>
-    <row r="47" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="79"/>
       <c r="B47" s="99" t="s">
         <v>71</v>
@@ -28345,7 +28345,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="48" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="79"/>
       <c r="B48" s="99" t="s">
         <v>72</v>
@@ -28388,7 +28388,7 @@
       <c r="P48" s="67"/>
       <c r="Q48" s="67"/>
     </row>
-    <row r="49" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="79"/>
       <c r="B49" s="99" t="s">
         <v>73</v>
@@ -28431,7 +28431,7 @@
       <c r="P49" s="67"/>
       <c r="Q49" s="67"/>
     </row>
-    <row r="50" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="79"/>
       <c r="B50" s="99" t="s">
         <v>74</v>
@@ -28474,7 +28474,7 @@
       <c r="P50" s="68"/>
       <c r="Q50" s="68"/>
     </row>
-    <row r="51" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="96"/>
       <c r="B51" s="96"/>
       <c r="C51" s="96"/>
@@ -28490,7 +28490,7 @@
       <c r="M51" s="255"/>
       <c r="N51" s="272"/>
     </row>
-    <row r="52" spans="1:17" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:17" ht="13.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A52" s="261" t="s">
         <v>12</v>
       </c>
@@ -28532,7 +28532,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="53" spans="1:17" ht="13.5" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="53" spans="1:17" ht="13.5" thickTop="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="pxY1J1YVteaxO59Cm/CeIkOxANrsyUGLI5rETuE+8bkETqmQ+jVJLyLvxCMgoPwd6EGMmoPDZ8usoAj68/4LwA==" saltValue="oE4fgJnuJEnGs9cRoEmrrA==" spinCount="100000" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <customSheetViews>
@@ -28547,12 +28547,6 @@
     </customSheetView>
   </customSheetViews>
   <mergeCells count="13">
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="D29:N29"/>
-    <mergeCell ref="A37:C37"/>
-    <mergeCell ref="D37:N37"/>
-    <mergeCell ref="A45:C45"/>
-    <mergeCell ref="D45:N45"/>
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="D21:N21"/>
     <mergeCell ref="A3:C4"/>
@@ -28560,6 +28554,12 @@
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="D13:N13"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="D29:N29"/>
+    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="D37:N37"/>
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="D45:N45"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -28575,16 +28575,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:O95"/>
-  <sheetFormatPr defaultColWidth="9.296875" defaultRowHeight="13" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" style="26" customWidth="1"/>
-    <col min="2" max="2" width="22.796875" style="26" customWidth="1"/>
-    <col min="3" max="3" width="1.796875" style="26" customWidth="1"/>
-    <col min="4" max="14" width="9.796875" style="26" customWidth="1"/>
-    <col min="15" max="16384" width="9.296875" style="26"/>
+    <col min="2" max="2" width="22.83203125" style="26" customWidth="1"/>
+    <col min="3" max="3" width="1.83203125" style="26" customWidth="1"/>
+    <col min="4" max="14" width="9.83203125" style="26" customWidth="1"/>
+    <col min="15" max="16384" width="9.33203125" style="26"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="66" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" s="66" customFormat="1" ht="33" x14ac:dyDescent="0.25">
       <c r="A1" s="74" t="s">
         <v>450</v>
       </c>
@@ -28603,7 +28603,7 @@
       <c r="N1" s="65"/>
       <c r="O1" s="90"/>
     </row>
-    <row r="2" spans="1:15" s="66" customFormat="1" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:15" s="66" customFormat="1" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="89"/>
       <c r="B2" s="65"/>
       <c r="C2" s="65"/>
@@ -28620,7 +28620,7 @@
       <c r="N2" s="65"/>
       <c r="O2" s="90"/>
     </row>
-    <row r="3" spans="1:15" s="66" customFormat="1" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" s="66" customFormat="1" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A3" s="102" t="s">
         <v>79</v>
       </c>
@@ -28649,7 +28649,7 @@
       <c r="N3" s="76"/>
       <c r="O3" s="90"/>
     </row>
-    <row r="4" spans="1:15" s="66" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:15" s="66" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="109" t="s">
         <v>80</v>
       </c>
@@ -28690,25 +28690,25 @@
       </c>
       <c r="O4" s="90"/>
     </row>
-    <row r="5" spans="1:15" s="101" customFormat="1" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="380"/>
-      <c r="B5" s="380"/>
-      <c r="C5" s="381"/>
-      <c r="D5" s="387" t="s">
+    <row r="5" spans="1:15" s="101" customFormat="1" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="392"/>
+      <c r="B5" s="392"/>
+      <c r="C5" s="393"/>
+      <c r="D5" s="397" t="s">
         <v>70</v>
       </c>
-      <c r="E5" s="388"/>
-      <c r="F5" s="388"/>
-      <c r="G5" s="388"/>
-      <c r="H5" s="388"/>
-      <c r="I5" s="388"/>
-      <c r="J5" s="388"/>
-      <c r="K5" s="388"/>
-      <c r="L5" s="388"/>
-      <c r="M5" s="388"/>
-      <c r="N5" s="388"/>
-    </row>
-    <row r="6" spans="1:15" s="66" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E5" s="398"/>
+      <c r="F5" s="398"/>
+      <c r="G5" s="398"/>
+      <c r="H5" s="398"/>
+      <c r="I5" s="398"/>
+      <c r="J5" s="398"/>
+      <c r="K5" s="398"/>
+      <c r="L5" s="398"/>
+      <c r="M5" s="398"/>
+      <c r="N5" s="398"/>
+    </row>
+    <row r="6" spans="1:15" s="66" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="78"/>
       <c r="B6" s="79"/>
       <c r="C6" s="80"/>
@@ -28725,7 +28725,7 @@
       <c r="N6" s="275"/>
       <c r="O6" s="90"/>
     </row>
-    <row r="7" spans="1:15" s="66" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" s="66" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="78"/>
       <c r="B7" s="103" t="s">
         <v>81</v>
@@ -28766,7 +28766,7 @@
       </c>
       <c r="O7" s="90"/>
     </row>
-    <row r="8" spans="1:15" s="66" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" s="66" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="104"/>
       <c r="B8" s="103" t="s">
         <v>82</v>
@@ -28807,7 +28807,7 @@
       </c>
       <c r="O8" s="90"/>
     </row>
-    <row r="9" spans="1:15" s="66" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" s="66" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="104"/>
       <c r="B9" s="103" t="s">
         <v>83</v>
@@ -28848,7 +28848,7 @@
       </c>
       <c r="O9" s="90"/>
     </row>
-    <row r="10" spans="1:15" s="66" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" s="66" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="104"/>
       <c r="B10" s="103" t="s">
         <v>84</v>
@@ -28889,7 +28889,7 @@
       </c>
       <c r="O10" s="90"/>
     </row>
-    <row r="11" spans="1:15" s="66" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" s="66" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="104"/>
       <c r="B11" s="103"/>
       <c r="C11" s="79"/>
@@ -28906,7 +28906,7 @@
       <c r="N11" s="272"/>
       <c r="O11" s="90"/>
     </row>
-    <row r="12" spans="1:15" s="66" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" s="66" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="104"/>
       <c r="B12" s="103" t="s">
         <v>85</v>
@@ -28947,7 +28947,7 @@
       </c>
       <c r="O12" s="90"/>
     </row>
-    <row r="13" spans="1:15" s="66" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" s="66" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="104"/>
       <c r="B13" s="103" t="s">
         <v>86</v>
@@ -28988,7 +28988,7 @@
       </c>
       <c r="O13" s="90"/>
     </row>
-    <row r="14" spans="1:15" s="66" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" s="66" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="78"/>
       <c r="B14" s="103" t="s">
         <v>87</v>
@@ -29029,7 +29029,7 @@
       </c>
       <c r="O14" s="90"/>
     </row>
-    <row r="15" spans="1:15" s="66" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" s="66" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="105"/>
       <c r="B15" s="103" t="s">
         <v>88</v>
@@ -29070,7 +29070,7 @@
       </c>
       <c r="O15" s="90"/>
     </row>
-    <row r="16" spans="1:15" s="66" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" s="66" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="105"/>
       <c r="B16" s="103" t="s">
         <v>89</v>
@@ -29111,7 +29111,7 @@
       </c>
       <c r="O16" s="90"/>
     </row>
-    <row r="17" spans="1:15" s="66" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:15" s="66" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="78"/>
       <c r="B17" s="103" t="s">
         <v>90</v>
@@ -29152,7 +29152,7 @@
       </c>
       <c r="O17" s="90"/>
     </row>
-    <row r="18" spans="1:15" s="66" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:15" s="66" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="104"/>
       <c r="B18" s="103" t="s">
         <v>91</v>
@@ -29193,7 +29193,7 @@
       </c>
       <c r="O18" s="90"/>
     </row>
-    <row r="19" spans="1:15" s="66" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:15" s="66" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="103"/>
       <c r="B19" s="106" t="s">
         <v>36</v>
@@ -29234,25 +29234,25 @@
       </c>
       <c r="O19" s="90"/>
     </row>
-    <row r="20" spans="1:15" s="101" customFormat="1" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="380"/>
-      <c r="B20" s="380"/>
-      <c r="C20" s="381"/>
-      <c r="D20" s="389" t="s">
+    <row r="20" spans="1:15" s="101" customFormat="1" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="392"/>
+      <c r="B20" s="392"/>
+      <c r="C20" s="393"/>
+      <c r="D20" s="395" t="s">
         <v>75</v>
       </c>
-      <c r="E20" s="390"/>
-      <c r="F20" s="390"/>
-      <c r="G20" s="390"/>
-      <c r="H20" s="390"/>
-      <c r="I20" s="390"/>
-      <c r="J20" s="390"/>
-      <c r="K20" s="390"/>
-      <c r="L20" s="390"/>
-      <c r="M20" s="390"/>
-      <c r="N20" s="390"/>
-    </row>
-    <row r="21" spans="1:15" s="66" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E20" s="396"/>
+      <c r="F20" s="396"/>
+      <c r="G20" s="396"/>
+      <c r="H20" s="396"/>
+      <c r="I20" s="396"/>
+      <c r="J20" s="396"/>
+      <c r="K20" s="396"/>
+      <c r="L20" s="396"/>
+      <c r="M20" s="396"/>
+      <c r="N20" s="396"/>
+    </row>
+    <row r="21" spans="1:15" s="66" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="78"/>
       <c r="B21" s="79"/>
       <c r="C21" s="80"/>
@@ -29269,7 +29269,7 @@
       <c r="N21" s="276"/>
       <c r="O21" s="90"/>
     </row>
-    <row r="22" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="78"/>
       <c r="B22" s="103" t="s">
         <v>81</v>
@@ -29309,7 +29309,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="23" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="104"/>
       <c r="B23" s="103" t="s">
         <v>82</v>
@@ -29349,7 +29349,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="24" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="104"/>
       <c r="B24" s="103" t="s">
         <v>83</v>
@@ -29389,7 +29389,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="104"/>
       <c r="B25" s="103" t="s">
         <v>84</v>
@@ -29429,7 +29429,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="104"/>
       <c r="B26" s="103"/>
       <c r="C26" s="79"/>
@@ -29445,7 +29445,7 @@
       <c r="M26" s="255"/>
       <c r="N26" s="272"/>
     </row>
-    <row r="27" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="104"/>
       <c r="B27" s="103" t="s">
         <v>85</v>
@@ -29485,7 +29485,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="28" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="104"/>
       <c r="B28" s="103" t="s">
         <v>86</v>
@@ -29525,7 +29525,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="29" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="78"/>
       <c r="B29" s="103" t="s">
         <v>87</v>
@@ -29565,7 +29565,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="30" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="105"/>
       <c r="B30" s="103" t="s">
         <v>88</v>
@@ -29605,7 +29605,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="31" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="105"/>
       <c r="B31" s="103" t="s">
         <v>89</v>
@@ -29645,7 +29645,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="32" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="78"/>
       <c r="B32" s="103" t="s">
         <v>90</v>
@@ -29685,7 +29685,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="33" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="104"/>
       <c r="B33" s="103" t="s">
         <v>91</v>
@@ -29725,7 +29725,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="34" spans="1:15" s="66" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:15" s="66" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="103"/>
       <c r="B34" s="106" t="s">
         <v>36</v>
@@ -29766,25 +29766,25 @@
       </c>
       <c r="O34" s="90"/>
     </row>
-    <row r="35" spans="1:15" s="101" customFormat="1" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="380"/>
-      <c r="B35" s="380"/>
-      <c r="C35" s="381"/>
-      <c r="D35" s="389" t="s">
+    <row r="35" spans="1:15" s="101" customFormat="1" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="392"/>
+      <c r="B35" s="392"/>
+      <c r="C35" s="393"/>
+      <c r="D35" s="395" t="s">
         <v>76</v>
       </c>
-      <c r="E35" s="390"/>
-      <c r="F35" s="390"/>
-      <c r="G35" s="390"/>
-      <c r="H35" s="390"/>
-      <c r="I35" s="390"/>
-      <c r="J35" s="390"/>
-      <c r="K35" s="390"/>
-      <c r="L35" s="390"/>
-      <c r="M35" s="390"/>
-      <c r="N35" s="390"/>
-    </row>
-    <row r="36" spans="1:15" s="66" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E35" s="396"/>
+      <c r="F35" s="396"/>
+      <c r="G35" s="396"/>
+      <c r="H35" s="396"/>
+      <c r="I35" s="396"/>
+      <c r="J35" s="396"/>
+      <c r="K35" s="396"/>
+      <c r="L35" s="396"/>
+      <c r="M35" s="396"/>
+      <c r="N35" s="396"/>
+    </row>
+    <row r="36" spans="1:15" s="66" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="78"/>
       <c r="B36" s="79"/>
       <c r="C36" s="80"/>
@@ -29801,7 +29801,7 @@
       <c r="N36" s="276"/>
       <c r="O36" s="90"/>
     </row>
-    <row r="37" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="78"/>
       <c r="B37" s="103" t="s">
         <v>81</v>
@@ -29841,7 +29841,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="38" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="104"/>
       <c r="B38" s="103" t="s">
         <v>82</v>
@@ -29881,7 +29881,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="39" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="104"/>
       <c r="B39" s="103" t="s">
         <v>83</v>
@@ -29921,7 +29921,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="40" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="104"/>
       <c r="B40" s="103" t="s">
         <v>84</v>
@@ -29961,7 +29961,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="41" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="104"/>
       <c r="B41" s="103"/>
       <c r="C41" s="79"/>
@@ -29977,7 +29977,7 @@
       <c r="M41" s="255"/>
       <c r="N41" s="272"/>
     </row>
-    <row r="42" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="104"/>
       <c r="B42" s="103" t="s">
         <v>85</v>
@@ -30017,7 +30017,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="43" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="104"/>
       <c r="B43" s="103" t="s">
         <v>86</v>
@@ -30057,7 +30057,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="44" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="78"/>
       <c r="B44" s="103" t="s">
         <v>87</v>
@@ -30097,7 +30097,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="45" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="105"/>
       <c r="B45" s="103" t="s">
         <v>88</v>
@@ -30137,7 +30137,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="105"/>
       <c r="B46" s="103" t="s">
         <v>89</v>
@@ -30177,7 +30177,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="47" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="78"/>
       <c r="B47" s="103" t="s">
         <v>90</v>
@@ -30217,7 +30217,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="48" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="104"/>
       <c r="B48" s="103" t="s">
         <v>91</v>
@@ -30257,7 +30257,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="49" spans="1:15" s="66" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:15" s="66" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="103"/>
       <c r="B49" s="106" t="s">
         <v>36</v>
@@ -30298,25 +30298,25 @@
       </c>
       <c r="O49" s="90"/>
     </row>
-    <row r="50" spans="1:15" s="101" customFormat="1" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="380"/>
-      <c r="B50" s="380"/>
-      <c r="C50" s="381"/>
-      <c r="D50" s="389" t="s">
+    <row r="50" spans="1:15" s="101" customFormat="1" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="392"/>
+      <c r="B50" s="392"/>
+      <c r="C50" s="393"/>
+      <c r="D50" s="395" t="s">
         <v>77</v>
       </c>
-      <c r="E50" s="390"/>
-      <c r="F50" s="390"/>
-      <c r="G50" s="390"/>
-      <c r="H50" s="390"/>
-      <c r="I50" s="390"/>
-      <c r="J50" s="390"/>
-      <c r="K50" s="390"/>
-      <c r="L50" s="390"/>
-      <c r="M50" s="390"/>
-      <c r="N50" s="390"/>
-    </row>
-    <row r="51" spans="1:15" s="66" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E50" s="396"/>
+      <c r="F50" s="396"/>
+      <c r="G50" s="396"/>
+      <c r="H50" s="396"/>
+      <c r="I50" s="396"/>
+      <c r="J50" s="396"/>
+      <c r="K50" s="396"/>
+      <c r="L50" s="396"/>
+      <c r="M50" s="396"/>
+      <c r="N50" s="396"/>
+    </row>
+    <row r="51" spans="1:15" s="66" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="78"/>
       <c r="B51" s="79"/>
       <c r="C51" s="80"/>
@@ -30333,7 +30333,7 @@
       <c r="N51" s="276"/>
       <c r="O51" s="90"/>
     </row>
-    <row r="52" spans="1:15" s="66" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:15" s="66" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="78"/>
       <c r="B52" s="103" t="s">
         <v>81</v>
@@ -30374,7 +30374,7 @@
       </c>
       <c r="O52" s="90"/>
     </row>
-    <row r="53" spans="1:15" s="66" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:15" s="66" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="104"/>
       <c r="B53" s="103" t="s">
         <v>82</v>
@@ -30415,7 +30415,7 @@
       </c>
       <c r="O53" s="90"/>
     </row>
-    <row r="54" spans="1:15" s="66" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:15" s="66" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="104"/>
       <c r="B54" s="103" t="s">
         <v>83</v>
@@ -30456,7 +30456,7 @@
       </c>
       <c r="O54" s="90"/>
     </row>
-    <row r="55" spans="1:15" s="66" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:15" s="66" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="104"/>
       <c r="B55" s="103" t="s">
         <v>84</v>
@@ -30497,7 +30497,7 @@
       </c>
       <c r="O55" s="90"/>
     </row>
-    <row r="56" spans="1:15" s="66" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:15" s="66" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="104"/>
       <c r="B56" s="103"/>
       <c r="C56" s="79"/>
@@ -30514,7 +30514,7 @@
       <c r="N56" s="272"/>
       <c r="O56" s="90"/>
     </row>
-    <row r="57" spans="1:15" s="66" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:15" s="66" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="104"/>
       <c r="B57" s="103" t="s">
         <v>85</v>
@@ -30555,7 +30555,7 @@
       </c>
       <c r="O57" s="90"/>
     </row>
-    <row r="58" spans="1:15" s="66" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:15" s="66" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="104"/>
       <c r="B58" s="103" t="s">
         <v>86</v>
@@ -30596,7 +30596,7 @@
       </c>
       <c r="O58" s="90"/>
     </row>
-    <row r="59" spans="1:15" s="66" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:15" s="66" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="78"/>
       <c r="B59" s="103" t="s">
         <v>87</v>
@@ -30637,7 +30637,7 @@
       </c>
       <c r="O59" s="90"/>
     </row>
-    <row r="60" spans="1:15" s="66" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:15" s="66" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="105"/>
       <c r="B60" s="103" t="s">
         <v>88</v>
@@ -30678,7 +30678,7 @@
       </c>
       <c r="O60" s="90"/>
     </row>
-    <row r="61" spans="1:15" s="66" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:15" s="66" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="105"/>
       <c r="B61" s="103" t="s">
         <v>89</v>
@@ -30719,7 +30719,7 @@
       </c>
       <c r="O61" s="90"/>
     </row>
-    <row r="62" spans="1:15" s="66" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:15" s="66" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="78"/>
       <c r="B62" s="103" t="s">
         <v>90</v>
@@ -30760,7 +30760,7 @@
       </c>
       <c r="O62" s="90"/>
     </row>
-    <row r="63" spans="1:15" s="66" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:15" s="66" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="104"/>
       <c r="B63" s="103" t="s">
         <v>91</v>
@@ -30801,7 +30801,7 @@
       </c>
       <c r="O63" s="90"/>
     </row>
-    <row r="64" spans="1:15" s="66" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:15" s="66" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="103"/>
       <c r="B64" s="106" t="s">
         <v>36</v>
@@ -30842,25 +30842,25 @@
       </c>
       <c r="O64" s="90"/>
     </row>
-    <row r="65" spans="1:15" s="101" customFormat="1" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="380"/>
-      <c r="B65" s="380"/>
-      <c r="C65" s="381"/>
-      <c r="D65" s="389" t="s">
+    <row r="65" spans="1:15" s="101" customFormat="1" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="392"/>
+      <c r="B65" s="392"/>
+      <c r="C65" s="393"/>
+      <c r="D65" s="395" t="s">
         <v>57</v>
       </c>
-      <c r="E65" s="390"/>
-      <c r="F65" s="390"/>
-      <c r="G65" s="390"/>
-      <c r="H65" s="390"/>
-      <c r="I65" s="390"/>
-      <c r="J65" s="390"/>
-      <c r="K65" s="390"/>
-      <c r="L65" s="390"/>
-      <c r="M65" s="390"/>
-      <c r="N65" s="390"/>
-    </row>
-    <row r="66" spans="1:15" s="66" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E65" s="396"/>
+      <c r="F65" s="396"/>
+      <c r="G65" s="396"/>
+      <c r="H65" s="396"/>
+      <c r="I65" s="396"/>
+      <c r="J65" s="396"/>
+      <c r="K65" s="396"/>
+      <c r="L65" s="396"/>
+      <c r="M65" s="396"/>
+      <c r="N65" s="396"/>
+    </row>
+    <row r="66" spans="1:15" s="66" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="78"/>
       <c r="B66" s="79"/>
       <c r="C66" s="80"/>
@@ -30877,7 +30877,7 @@
       <c r="N66" s="276"/>
       <c r="O66" s="90"/>
     </row>
-    <row r="67" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="78"/>
       <c r="B67" s="103" t="s">
         <v>81</v>
@@ -30917,7 +30917,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="68" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="104"/>
       <c r="B68" s="103" t="s">
         <v>82</v>
@@ -30957,7 +30957,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="69" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="104"/>
       <c r="B69" s="103" t="s">
         <v>83</v>
@@ -30997,7 +30997,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="70" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="104"/>
       <c r="B70" s="103" t="s">
         <v>84</v>
@@ -31037,7 +31037,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="71" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="104"/>
       <c r="B71" s="103"/>
       <c r="C71" s="79"/>
@@ -31053,7 +31053,7 @@
       <c r="M71" s="255"/>
       <c r="N71" s="272"/>
     </row>
-    <row r="72" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="104"/>
       <c r="B72" s="103" t="s">
         <v>85</v>
@@ -31093,7 +31093,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="73" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="104"/>
       <c r="B73" s="103" t="s">
         <v>86</v>
@@ -31133,7 +31133,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="74" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="78"/>
       <c r="B74" s="103" t="s">
         <v>87</v>
@@ -31173,7 +31173,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="75" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="105"/>
       <c r="B75" s="103" t="s">
         <v>88</v>
@@ -31213,7 +31213,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="105"/>
       <c r="B76" s="103" t="s">
         <v>89</v>
@@ -31253,7 +31253,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="77" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="78"/>
       <c r="B77" s="103" t="s">
         <v>90</v>
@@ -31293,7 +31293,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="78" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="104"/>
       <c r="B78" s="103" t="s">
         <v>91</v>
@@ -31333,7 +31333,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="79" spans="1:15" s="66" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:15" s="66" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="103"/>
       <c r="B79" s="106" t="s">
         <v>36</v>
@@ -31374,25 +31374,25 @@
       </c>
       <c r="O79" s="90"/>
     </row>
-    <row r="80" spans="1:15" s="101" customFormat="1" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="380"/>
-      <c r="B80" s="380"/>
-      <c r="C80" s="381"/>
-      <c r="D80" s="389" t="s">
+    <row r="80" spans="1:15" s="101" customFormat="1" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="A80" s="392"/>
+      <c r="B80" s="392"/>
+      <c r="C80" s="393"/>
+      <c r="D80" s="395" t="s">
         <v>78</v>
       </c>
-      <c r="E80" s="390"/>
-      <c r="F80" s="390"/>
-      <c r="G80" s="390"/>
-      <c r="H80" s="390"/>
-      <c r="I80" s="390"/>
-      <c r="J80" s="390"/>
-      <c r="K80" s="390"/>
-      <c r="L80" s="390"/>
-      <c r="M80" s="390"/>
-      <c r="N80" s="390"/>
-    </row>
-    <row r="81" spans="1:15" s="66" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E80" s="396"/>
+      <c r="F80" s="396"/>
+      <c r="G80" s="396"/>
+      <c r="H80" s="396"/>
+      <c r="I80" s="396"/>
+      <c r="J80" s="396"/>
+      <c r="K80" s="396"/>
+      <c r="L80" s="396"/>
+      <c r="M80" s="396"/>
+      <c r="N80" s="396"/>
+    </row>
+    <row r="81" spans="1:15" s="66" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="78"/>
       <c r="B81" s="79"/>
       <c r="C81" s="80"/>
@@ -31409,7 +31409,7 @@
       <c r="N81" s="276"/>
       <c r="O81" s="90"/>
     </row>
-    <row r="82" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="78"/>
       <c r="B82" s="103" t="s">
         <v>81</v>
@@ -31449,7 +31449,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="83" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="104"/>
       <c r="B83" s="103" t="s">
         <v>82</v>
@@ -31489,7 +31489,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="84" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="104"/>
       <c r="B84" s="103" t="s">
         <v>83</v>
@@ -31529,7 +31529,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="104"/>
       <c r="B85" s="103" t="s">
         <v>84</v>
@@ -31569,7 +31569,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="86" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="104"/>
       <c r="B86" s="103"/>
       <c r="C86" s="79"/>
@@ -31585,7 +31585,7 @@
       <c r="M86" s="255"/>
       <c r="N86" s="272"/>
     </row>
-    <row r="87" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="104"/>
       <c r="B87" s="103" t="s">
         <v>85</v>
@@ -31625,7 +31625,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="88" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="104"/>
       <c r="B88" s="103" t="s">
         <v>86</v>
@@ -31665,7 +31665,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="89" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="78"/>
       <c r="B89" s="103" t="s">
         <v>87</v>
@@ -31705,7 +31705,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="90" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="105"/>
       <c r="B90" s="103" t="s">
         <v>88</v>
@@ -31745,7 +31745,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="91" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="105"/>
       <c r="B91" s="103" t="s">
         <v>89</v>
@@ -31785,7 +31785,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="92" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="78"/>
       <c r="B92" s="103" t="s">
         <v>90</v>
@@ -31825,7 +31825,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="93" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="104"/>
       <c r="B93" s="103" t="s">
         <v>91</v>
@@ -31865,7 +31865,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="94" spans="1:15" s="66" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:15" s="66" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A94" s="281"/>
       <c r="B94" s="282" t="s">
         <v>36</v>
@@ -31906,24 +31906,24 @@
       </c>
       <c r="O94" s="90"/>
     </row>
-    <row r="95" spans="1:15" ht="14.5" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:15" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B95" s="103"/>
     </row>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="lST764eUNHrty8Y6jdW+BIqhVvIFVwAbGvYzYqWh4ljs1B48OCLnVLVSFofCL9FN38ItOtGTDNqYdCiA2v9D5A==" saltValue="KM8UguHEdtcEDs+NBFSy7A==" spinCount="100000" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <mergeCells count="12">
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:N5"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="D20:N20"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="D35:N35"/>
     <mergeCell ref="A50:C50"/>
     <mergeCell ref="D50:N50"/>
     <mergeCell ref="A65:C65"/>
     <mergeCell ref="D65:N65"/>
     <mergeCell ref="A80:C80"/>
     <mergeCell ref="D80:N80"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:N5"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="D20:N20"/>
-    <mergeCell ref="A35:C35"/>
-    <mergeCell ref="D35:N35"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.55118110236220474" bottom="0.55118110236220474" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -31932,175 +31932,27 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="OneNote Notebook" ma:contentTypeID="0x010100B33C331ECFD649848CC649FBF8E7E47A00E2AD0D5E1D5CDF47A0C1AB5F239C4340" ma:contentTypeVersion="5" ma:contentTypeDescription="This content type provides the standard OneNote usage for INSPIRE" ma:contentTypeScope="" ma:versionID="0e9b04ae20299450c241d22c3b1ddb27">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="ac3a4e0a-fb74-4c49-bf32-20bf85cdc73a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="111a569e26f220b9741aebf1ba13a652" ns3:_="">
-    <xsd:import namespace="ac3a4e0a-fb74-4c49-bf32-20bf85cdc73a"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns3:_dlc_DocId" minOccurs="0"/>
-                <xsd:element ref="ns3:_dlc_DocIdUrl" minOccurs="0"/>
-                <xsd:element ref="ns3:_dlc_DocIdPersistId" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAllLabel" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="ac3a4e0a-fb74-4c49-bf32-20bf85cdc73a" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="_dlc_DocId" ma:index="8" nillable="true" ma:displayName="Document ID Value" ma:description="The value of the document ID assigned to this item." ma:internalName="_dlc_DocId" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="_dlc_DocIdUrl" ma:index="9" nillable="true" ma:displayName="Document ID" ma:description="Permanent link to this document." ma:hidden="true" ma:internalName="_dlc_DocIdUrl" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:URL">
-            <xsd:sequence>
-              <xsd:element name="Url" type="dms:ValidUrl" minOccurs="0" nillable="true"/>
-              <xsd:element name="Description" type="xsd:string" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="_dlc_DocIdPersistId" ma:index="10" nillable="true" ma:displayName="Persist ID" ma:description="Keep ID on add." ma:hidden="true" ma:internalName="_dlc_DocIdPersistId" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Boolean"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="11" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:description="" ma:hidden="true" ma:list="{5357920a-29d2-4256-b462-610f62726553}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="ac3a4e0a-fb74-4c49-bf32-20bf85cdc73a">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAllLabel" ma:index="12" nillable="true" ma:displayName="Taxonomy Catch All Column1" ma:description="" ma:hidden="true" ma:list="{5357920a-29d2-4256-b462-610f62726553}" ma:internalName="TaxCatchAllLabel" ma:readOnly="true" ma:showField="CatchAllDataLabel" ma:web="ac3a4e0a-fb74-4c49-bf32-20bf85cdc73a">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="14" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="1" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="169790d1-2515-4ac1-9eec-fd681341ee56" xsi:nil="true"/>
+    <Desc xmlns="66f9a793-747d-4527-b970-6e44627a40d5" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="66f9a793-747d-4527-b970-6e44627a40d5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100AB200F5EC8B57F448AC7FBC953140B2E" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c1e4130f12dd0e8d913a71502150fcad">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="66f9a793-747d-4527-b970-6e44627a40d5" xmlns:ns3="169790d1-2515-4ac1-9eec-fd681341ee56" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c6ecdc3a20f93a9816e91aa819d5fb4b" ns2:_="" ns3:_="">
     <xsd:import namespace="66f9a793-747d-4527-b970-6e44627a40d5"/>
@@ -32341,39 +32193,39 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="169790d1-2515-4ac1-9eec-fd681341ee56" xsi:nil="true"/>
-    <Desc xmlns="66f9a793-747d-4527-b970-6e44627a40d5" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="66f9a793-747d-4527-b970-6e44627a40d5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item5.xml><?xml version="1.0" encoding="utf-8"?>
 <LongProperties xmlns="http://schemas.microsoft.com/office/2006/metadata/longProperties"/>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{63471D31-9DB7-4AEB-AACD-075DCB0113F0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FFFB444E-57AD-4800-9D23-7B260B4893C3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C5C2BD03-FF4F-43E2-851C-94773C22DD32}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="ac3a4e0a-fb74-4c49-bf32-20bf85cdc73a"/>
+    <ds:schemaRef ds:uri="169790d1-2515-4ac1-9eec-fd681341ee56"/>
+    <ds:schemaRef ds:uri="66f9a793-747d-4527-b970-6e44627a40d5"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BFB86E59-6A45-4EF0-A852-83365FD51929}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="ac3a4e0a-fb74-4c49-bf32-20bf85cdc73a"/>
+    <ds:schemaRef ds:uri="66f9a793-747d-4527-b970-6e44627a40d5"/>
+    <ds:schemaRef ds:uri="169790d1-2515-4ac1-9eec-fd681341ee56"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
@@ -32384,29 +32236,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BFB86E59-6A45-4EF0-A852-83365FD51929}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C5C2BD03-FF4F-43E2-851C-94773C22DD32}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="ac3a4e0a-fb74-4c49-bf32-20bf85cdc73a"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FFFB444E-57AD-4800-9D23-7B260B4893C3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps5.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B721D6EB-D724-4E80-B24C-3AED73FD812E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/longProperties"/>
